--- a/sample_portfolio.xlsx
+++ b/sample_portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\chanmainvest\portfolio_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91E4ACE-D1E8-4043-BA5A-1E8D1163D057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279AE8AC-71BD-48D2-A2D7-5AA98E7BA8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{C3C23AD8-DF51-43CD-B973-8860122C8980}"/>
+    <workbookView xWindow="57825" yWindow="270" windowWidth="21375" windowHeight="15375" activeTab="1" xr2:uid="{C3C23AD8-DF51-43CD-B973-8860122C8980}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
+          <xlrd:rvb i="3"/>
         </ext>
       </extLst>
     </bk>
@@ -700,6 +700,7 @@
         </key>
         <key name="%IsRefreshable">
           <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
           <flag name="ShowInAutoComplete" value="0"/>
           <flag name="ExcludeFromCalcComparison" value="1"/>
         </key>
@@ -730,556 +731,8 @@
 </rvTypesInfo>
 </file>
 
-<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="181">
-  <a r="1">
-    <v t="i">0</v>
-  </a>
-  <a r="1">
-    <v>330.34</v>
-  </a>
-  <a r="1">
-    <v>309.37</v>
-  </a>
-  <a r="1">
-    <v>284.95999999999998</v>
-  </a>
-  <a r="1">
-    <v>437.5</v>
-  </a>
-  <a r="1">
-    <v>401.25</v>
-  </a>
-  <a r="1">
-    <v>417.07</v>
-  </a>
-  <a r="1">
-    <v>0.86329999999999996</v>
-  </a>
-  <a r="1">
-    <v>0.90669999999999995</v>
-  </a>
-  <a r="1">
-    <v>0.95709999999999995</v>
-  </a>
-  <a r="1">
-    <v>0.84230000000000005</v>
-  </a>
-  <a r="1">
-    <v>0.93500000000000005</v>
-  </a>
-  <a r="1">
-    <v>0.86199999999999999</v>
-  </a>
-  <a r="1">
-    <v>0.88300000000000001</v>
-  </a>
-  <a r="1">
-    <v>0.92779999999999996</v>
-  </a>
-  <a r="1">
-    <v>7.1643999999999997</v>
-  </a>
-  <a r="1">
-    <v>7.1928999999999998</v>
-  </a>
-  <a r="1">
-    <v>6.9680999999999997</v>
-  </a>
-  <a r="1">
-    <v>6.3250999999999999</v>
-  </a>
-  <a r="1">
-    <v>7.1074000000000002</v>
-  </a>
-  <a r="1">
-    <v>7.2786</v>
-  </a>
-  <a r="1">
-    <v>6.9009999999999998</v>
-  </a>
-  <a r="1">
-    <v>47.94</v>
-  </a>
-  <a r="1">
-    <v>156.16</v>
-  </a>
-  <a r="1">
-    <v>153.62</v>
-  </a>
-  <a r="1">
-    <v>182.4</v>
-  </a>
-  <a r="1">
-    <v>166.26</v>
-  </a>
-  <a r="1">
-    <v>255.53</v>
-  </a>
-  <a r="1">
-    <v>261.73</v>
-  </a>
-  <a r="1">
-    <v>244.47</v>
-  </a>
-  <a r="1">
-    <v>267.44</v>
-  </a>
-  <a r="1">
-    <v>27.841000000000001</v>
-  </a>
-  <a r="1">
-    <v>31.35</v>
-  </a>
-  <a r="1">
-    <v>32.731000000000002</v>
-  </a>
-  <a r="1">
-    <v>30.381</v>
-  </a>
-  <a r="1">
-    <v>31.103000000000002</v>
-  </a>
-  <a r="1">
-    <v>32.131999999999998</v>
-  </a>
-  <a r="1">
-    <v>31.398</v>
-  </a>
-  <a r="1">
-    <v>31.608000000000001</v>
-  </a>
-  <a r="1">
-    <v>1.3414999999999999</v>
-  </a>
-  <a r="1">
-    <v>1.2887</v>
-  </a>
-  <a r="1">
-    <v>1.3454999999999999</v>
-  </a>
-  <a r="1">
-    <v>1.3016000000000001</v>
-  </a>
-  <a r="1">
-    <v>1.3458000000000001</v>
-  </a>
-  <a r="1">
-    <v>1.3363</v>
-  </a>
-  <a r="1">
-    <v>1.2618</v>
-  </a>
-  <a r="1">
-    <v>1.3152999999999999</v>
-  </a>
-  <a r="1">
-    <v>87.8</v>
-  </a>
-  <a r="1">
-    <v>68</v>
-  </a>
-  <a r="1">
-    <v>158.43</v>
-  </a>
-  <a r="1">
-    <v>116.48</v>
-  </a>
-  <a r="1">
-    <v>162.06</v>
-  </a>
-  <a r="1">
-    <v>186.23</v>
-  </a>
-  <a r="1">
-    <v>139.4</v>
-  </a>
-  <a r="1">
-    <v>186.94</v>
-  </a>
-  <a r="1">
-    <v>181.36</v>
-  </a>
-  <a r="1">
-    <v>88.522999999999996</v>
-  </a>
-  <a r="1">
-    <v>86.867000000000004</v>
-  </a>
-  <a r="1">
-    <v>83.013000000000005</v>
-  </a>
-  <a r="1">
-    <v>90.543999999999997</v>
-  </a>
-  <a r="1">
-    <v>90.682000000000002</v>
-  </a>
-  <a r="1">
-    <v>74.670100000000005</v>
-  </a>
-  <a r="1">
-    <v>82.75</v>
-  </a>
-  <a r="1">
-    <v>83.88</v>
-  </a>
-  <a r="1">
-    <v>24.88</v>
-  </a>
-  <a r="1">
-    <v>23.59</v>
-  </a>
-  <a r="1">
-    <v>19.899999999999999</v>
-  </a>
-  <a r="1">
-    <v>14.46</v>
-  </a>
-  <a r="1">
-    <v>110.14</v>
-  </a>
-  <a r="1">
-    <v>119.03</v>
-  </a>
-  <a r="1">
-    <v>149.93</v>
-  </a>
-  <a r="1">
-    <v>129.88999999999999</v>
-  </a>
-  <a r="1">
-    <v>147.58000000000001</v>
-  </a>
-  <a r="1">
-    <v>158.09</v>
-  </a>
-  <a r="1">
-    <v>150.21</v>
-  </a>
-  <a r="1">
-    <v>152.05000000000001</v>
-  </a>
-  <a r="1">
-    <v>115</v>
-  </a>
-  <a r="1">
-    <v>155.5</v>
-  </a>
-  <a r="1">
-    <v>152.72999999999999</v>
-  </a>
-  <a r="1">
-    <v>134.15</v>
-  </a>
-  <a r="1">
-    <v>611.49</v>
-  </a>
-  <a r="1">
-    <v>681.27</v>
-  </a>
-  <a r="1">
-    <v>660.08</v>
-  </a>
-  <a r="1">
-    <v>691.66</v>
-  </a>
-  <a r="1">
-    <v>1006.1</v>
-  </a>
-  <a r="1">
-    <v>921.4</v>
-  </a>
-  <a r="1">
-    <v>2322.6999999999998</v>
-  </a>
-  <a r="1">
-    <v>2021.7</v>
-  </a>
-  <a r="1">
-    <v>1076.8</v>
-  </a>
-  <a r="1">
-    <v>913.5</v>
-  </a>
-  <a r="1">
-    <v>962.4</v>
-  </a>
-  <a r="1">
-    <v>1555.2</v>
-  </a>
-  <a r="1">
-    <v>1693.3</v>
-  </a>
-  <a r="1">
-    <v>3292.3</v>
-  </a>
-  <a r="1">
-    <v>2651.7</v>
-  </a>
-  <a r="1">
-    <v>1922.7</v>
-  </a>
-  <a r="1">
-    <v>2790.93</v>
-  </a>
-  <a r="1">
-    <v>2608.4</v>
-  </a>
-  <a r="1">
-    <v>3096.83</v>
-  </a>
-  <a r="1">
-    <v>2783.04</v>
-  </a>
-  <a r="1">
-    <v>1.4197</v>
-  </a>
-  <a r="1">
-    <v>1.3607</v>
-  </a>
-  <a r="1">
-    <v>1.3675999999999999</v>
-  </a>
-  <a r="1">
-    <v>1.347</v>
-  </a>
-  <a r="1">
-    <v>1.2748999999999999</v>
-  </a>
-  <a r="1">
-    <v>1.3484</v>
-  </a>
-  <a r="1">
-    <v>1.3986000000000001</v>
-  </a>
-  <a r="1">
-    <v>1.3915</v>
-  </a>
-  <a r="1">
-    <v>54.24</v>
-  </a>
-  <a r="1">
-    <v>37.049999999999997</v>
-  </a>
-  <a r="1">
-    <v>53.51</v>
-  </a>
-  <a r="1">
-    <v>55.2</v>
-  </a>
-  <a r="1">
-    <v>54.59</v>
-  </a>
-  <a r="1">
-    <v>4.3710000000000004</v>
-  </a>
-  <a r="1">
-    <v>4.431</v>
-  </a>
-  <a r="1">
-    <v>2.2749999999999999</v>
-  </a>
-  <a r="1">
-    <v>4.0069999999999997</v>
-  </a>
-  <a r="1">
-    <v>3.1030000000000002</v>
-  </a>
-  <a r="1">
-    <v>1.609</v>
-  </a>
-  <a r="1">
-    <v>3.2170000000000001</v>
-  </a>
-  <a r="1">
-    <v>2.1230000000000002</v>
-  </a>
-  <a r="1">
-    <v>36.254899999999999</v>
-  </a>
-  <a r="1">
-    <v>33.663200000000003</v>
-  </a>
-  <a r="1">
-    <v>43.273499999999999</v>
-  </a>
-  <a r="1">
-    <v>42.338500000000003</v>
-  </a>
-  <a r="1">
-    <v>30.818200000000001</v>
-  </a>
-  <a r="1">
-    <v>43.643500000000003</v>
-  </a>
-  <a r="1">
-    <v>13.6426</v>
-  </a>
-  <a r="1">
-    <v>18.8247</v>
-  </a>
-  <a r="1">
-    <v>24482</v>
-  </a>
-  <a r="1">
-    <v>39978.1</v>
-  </a>
-  <a r="1">
-    <v>65802.02</v>
-  </a>
-  <a r="1">
-    <v>52005</v>
-  </a>
-  <a r="1">
-    <v>95474.77</v>
-  </a>
-  <a r="1">
-    <v>59278</v>
-  </a>
-  <a r="1">
-    <v>92461.78</v>
-  </a>
-  <a r="1">
-    <v>95038.01</v>
-  </a>
-  <a r="1">
-    <v>231.83</v>
-  </a>
-  <a r="1">
-    <v>114.28</v>
-  </a>
-  <a r="1">
-    <v>230.29</v>
-  </a>
-  <a r="1">
-    <v>205.94</v>
-  </a>
-  <a r="1">
-    <v>621.26</v>
-  </a>
-  <a r="1">
-    <v>600.64</v>
-  </a>
-  <a r="1">
-    <v>596.30999999999995</v>
-  </a>
-  <a r="1">
-    <v>4066.5</v>
-  </a>
-  <a r="1">
-    <v>4595.3999999999996</v>
-  </a>
-  <a r="1">
-    <v>4948.3999999999996</v>
-  </a>
-  <a r="1">
-    <v>2949</v>
-  </a>
-  <a r="1">
-    <v>1840.4</v>
-  </a>
-  <a r="1">
-    <v>1899.8</v>
-  </a>
-  <a r="1">
-    <v>2537.8000000000002</v>
-  </a>
-  <a r="1">
-    <v>2024.1</v>
-  </a>
-  <a r="1">
-    <v>81.02</v>
-  </a>
-  <a r="1">
-    <v>46.1</v>
-  </a>
-  <a r="1">
-    <v>58.71</v>
-  </a>
-  <a r="1">
-    <v>40</v>
-  </a>
-  <a r="1">
-    <v>39.299999999999997</v>
-  </a>
-  <a r="1">
-    <v>50.521000000000001</v>
-  </a>
-  <a r="1">
-    <v>33.372999999999998</v>
-  </a>
-  <a r="1">
-    <v>75.682000000000002</v>
-  </a>
-  <a r="1">
-    <v>88.537000000000006</v>
-  </a>
-  <a r="1">
-    <v>23.475000000000001</v>
-  </a>
-  <a r="1">
-    <v>28.849</v>
-  </a>
-  <a r="1">
-    <v>23.992000000000001</v>
-  </a>
-  <a r="1">
-    <v>21.715</v>
-  </a>
-  <a r="1">
-    <v>20.89</v>
-  </a>
-  <a r="1">
-    <v>26.54</v>
-  </a>
-  <a r="1">
-    <v>5.56</v>
-  </a>
-  <a r="1">
-    <v>14.06</v>
-  </a>
-  <a r="1">
-    <v>39.130000000000003</v>
-  </a>
-  <a r="1">
-    <v>44.89</v>
-  </a>
-  <a r="1">
-    <v>48.64</v>
-  </a>
-  <a r="1">
-    <v>47.79</v>
-  </a>
-  <a r="1">
-    <v>199.63</v>
-  </a>
-  <a r="1">
-    <v>272.94</v>
-  </a>
-  <a r="1">
-    <v>326.12</v>
-  </a>
-  <a r="1">
-    <v>338.77</v>
-  </a>
-  <a r="1">
-    <v>172.49</v>
-  </a>
-  <a r="1">
-    <v>189.81</v>
-  </a>
-  <a r="1">
-    <v>116.76</v>
-  </a>
-  <a r="1">
-    <v>246.35</v>
-  </a>
-</arrayData>
-</file>
-
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="276">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="96">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23hqh&amp;q=ARCX%3aSPY&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -1289,6 +742,7 @@
     <v>a23hqh</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>0</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
@@ -1323,15 +777,20 @@
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>9</v>
+    <v>1</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a21mim&amp;q=XNAS%3aQQQ&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>en-CA</v>
     <v>a21mim</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>5</v>
     <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
@@ -1353,7 +812,7 @@
     <v>609.77099999999996</v>
     <v>ETF</v>
     <v>46072.041605323437</v>
-    <v>3</v>
+    <v>4</v>
     <v>600.72</v>
     <v>411778069059.48999</v>
     <v>Invesco QQQ Trust 1</v>
@@ -1367,11 +826,7 @@
     <v>62275053</v>
   </rv>
   <rv s="2">
-    <v>4</v>
-  </rv>
-  <rv s="4">
-    <v>9</v>
-    <v>1</v>
+    <v>5</v>
   </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=ab1y3m&amp;q=XTSE%3aXIU&amp;form=skydnc</v>
@@ -1382,6 +837,7 @@
     <v>ab1y3m</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>8</v>
     <v>iShares S&amp;P/TSX 60 Index ETF (XTSE:XIU)</v>
@@ -1419,11 +875,12 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a24b5r&amp;q=XNAS%3aTLT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>en-CA</v>
     <v>a24b5r</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>5</v>
     <v>iShares:20+ Trs Bd ETF (XNAS:TLT)</v>
@@ -1466,6 +923,7 @@
     <v>cfzfpr</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>12</v>
     <v>Sprott Active Au &amp; Ag (XNAS:GBUG)</v>
@@ -1510,6 +968,7 @@
     <v>aay9k2</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>Franco-Nevada Corporation (XTSE:FNV)</v>
@@ -1564,6 +1023,7 @@
     <v>ab1tfr</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>Wheaton Precious Metals Corp. (XTSE:WPM)</v>
@@ -1618,6 +1078,7 @@
     <v>aaxdur</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>CAMECO CORPORATION (XTSE:CCO)</v>
@@ -1672,6 +1133,7 @@
     <v>a1yv52</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
@@ -1726,6 +1188,7 @@
     <v>a1ndww</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
@@ -1780,6 +1243,7 @@
     <v>a1u3p2</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
@@ -1834,6 +1298,7 @@
     <v>a269ec</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>EXXON MOBIL CORPORATION (XNYS:XOM)</v>
@@ -1888,6 +1353,7 @@
     <v>a1qlz2</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>CHEVRON CORPORATION (XNYS:CVX)</v>
@@ -1938,6 +1404,7 @@
     <v>cc5pdm</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>12</v>
     <v>iShares Bitcoin Trust (XNAS:IBIT)</v>
@@ -1978,6 +1445,7 @@
     <v>ce8mrw</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>12</v>
     <v>iShares Ethereum Trust (XNAS:ETHA)</v>
@@ -2022,6 +1490,7 @@
     <v>a1sp52</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>FREEPORT-MCMORAN INC. (XNYS:FCX)</v>
@@ -2076,6 +1545,7 @@
     <v>a1upz2</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>HECLA MINING COMPANY (XNYS:HL)</v>
@@ -2125,11 +1595,12 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a233ur&amp;q=ARCX%3aSLV&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>en-CA</v>
     <v>a233ur</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>5</v>
     <v>IShares:Silver Trust (ARCX:SLV)</v>
@@ -2176,6 +1647,7 @@
     <v>a1mou2</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
@@ -2230,6 +1702,7 @@
     <v>a1zfec</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>Pan American Silver Corp. (XNYS:PAAS)</v>
@@ -2284,6 +1757,7 @@
     <v>ab1ic7</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>THOMSON REUTERS CORPORATION (XTSE:TRI)</v>
@@ -2338,6 +1812,7 @@
     <v>a24kar</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>15</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
@@ -2388,6 +1863,7 @@
     <v>avylur</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>USD/CAD</v>
@@ -2420,6 +1896,7 @@
     <v>bo8l6h</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>BTC/USD</v>
@@ -2452,6 +1929,7 @@
     <v>brjcfr</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>ETH/USD</v>
@@ -2484,6 +1962,7 @@
     <v>avyn9c</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>USD/EUR</v>
@@ -2516,6 +1995,7 @@
     <v>avyomw</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>USD/JPY</v>
@@ -2548,6 +2028,7 @@
     <v>avym77</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>29</v>
     <v>USD/CNY</v>
@@ -2577,6 +2058,7 @@
     <v>avytp2</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>USD/TRY</v>
@@ -2609,6 +2091,7 @@
     <v>avyo8m</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>USD/INR</v>
@@ -2641,6 +2124,7 @@
     <v>avyspr</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>USD/SGD</v>
@@ -2673,6 +2157,7 @@
     <v>avytar</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>23</v>
     <v>USD/TWD</v>
@@ -2709,6 +2194,7 @@
     <v>auvwoc</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>35</v>
     <v>Gold</v>
@@ -2744,6 +2230,7 @@
     <v>auvwr7</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>35</v>
     <v>Silver</v>
@@ -2779,6 +2266,7 @@
     <v>auvwu2</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>35</v>
     <v>Platinum</v>
@@ -2814,6 +2302,7 @@
     <v>auvx6h</v>
     <v>268435456</v>
     <v>1</v>
+    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>35</v>
     <v>Natural Gas</v>
@@ -2840,2531 +2329,11 @@
   <rv s="2">
     <v>94</v>
   </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1u3p2</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844565634126,0</v>
-    <v>0</v>
-    <v>a1u3p2</v>
-    <v>XNAS:GOOG</v>
-    <v>1</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1u3p2</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848010234311,0</v>
-    <v>0</v>
-    <v>a1u3p2</v>
-    <v>XNAS:GOOG</v>
-    <v>2</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1u3p2</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848013994767,0</v>
-    <v>0</v>
-    <v>a1u3p2</v>
-    <v>XNAS:GOOG</v>
-    <v>3</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a24kar</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844648044872,0</v>
-    <v>0</v>
-    <v>a24kar</v>
-    <v>XNAS:TSLA</v>
-    <v>4</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a24kar</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848012675213,0</v>
-    <v>0</v>
-    <v>a24kar</v>
-    <v>XNAS:TSLA</v>
-    <v>5</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a24kar</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848011375679,0</v>
-    <v>0</v>
-    <v>a24kar</v>
-    <v>XNAS:TSLA</v>
-    <v>6</v>
-  </rv>
-  <rv s="11">
-    <v>38</v>
-    <v>avyn9c</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848009474225,0</v>
-    <v>0</v>
-    <v>avyn9c</v>
-    <v>USDEUR</v>
-    <v>7</v>
-  </rv>
-  <rv s="11">
-    <v>38</v>
-    <v>avyn9c</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844570265080,0</v>
-    <v>0</v>
-    <v>avyn9c</v>
-    <v>USDEUR</v>
-    <v>8</v>
-  </rv>
-  <rv s="11">
-    <v>38</v>
-    <v>avyn9c</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070850758885632,0</v>
-    <v>0</v>
-    <v>avyn9c</v>
-    <v>USDEUR</v>
-    <v>9</v>
-  </rv>
-  <rv s="11">
-    <v>38</v>
-    <v>avyn9c</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848012119562,0</v>
-    <v>0</v>
-    <v>avyn9c</v>
-    <v>USDEUR</v>
-    <v>10</v>
-  </rv>
-  <rv s="11">
-    <v>38</v>
-    <v>avyn9c</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844592324057,0</v>
-    <v>0</v>
-    <v>avyn9c</v>
-    <v>USDEUR</v>
-    <v>11</v>
-  </rv>
-  <rv s="11">
-    <v>38</v>
-    <v>avyn9c</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844597981701,0</v>
-    <v>0</v>
-    <v>avyn9c</v>
-    <v>USDEUR</v>
-    <v>12</v>
-  </rv>
-  <rv s="11">
-    <v>38</v>
-    <v>avyn9c</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848010250831,0</v>
-    <v>0</v>
-    <v>avyn9c</v>
-    <v>USDEUR</v>
-    <v>13</v>
-  </rv>
-  <rv s="11">
-    <v>38</v>
-    <v>avyn9c</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844645406946,0</v>
-    <v>0</v>
-    <v>avyn9c</v>
-    <v>USDEUR</v>
-    <v>14</v>
-  </rv>
-  <rv s="11">
-    <v>39</v>
-    <v>avym77</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844564405709,0</v>
-    <v>0</v>
-    <v>avym77</v>
-    <v>USDCNY</v>
-    <v>15</v>
-  </rv>
-  <rv s="11">
-    <v>39</v>
-    <v>avym77</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844574658946,0</v>
-    <v>0</v>
-    <v>avym77</v>
-    <v>USDCNY</v>
-    <v>16</v>
-  </rv>
-  <rv s="11">
-    <v>39</v>
-    <v>avym77</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844650972054,0</v>
-    <v>0</v>
-    <v>avym77</v>
-    <v>USDCNY</v>
-    <v>17</v>
-  </rv>
-  <rv s="11">
-    <v>39</v>
-    <v>avym77</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848013775469,0</v>
-    <v>0</v>
-    <v>avym77</v>
-    <v>USDCNY</v>
-    <v>18</v>
-  </rv>
-  <rv s="11">
-    <v>39</v>
-    <v>avym77</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848010017817,0</v>
-    <v>0</v>
-    <v>avym77</v>
-    <v>USDCNY</v>
-    <v>19</v>
-  </rv>
-  <rv s="11">
-    <v>39</v>
-    <v>avym77</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848013615270,0</v>
-    <v>0</v>
-    <v>avym77</v>
-    <v>USDCNY</v>
-    <v>20</v>
-  </rv>
-  <rv s="11">
-    <v>39</v>
-    <v>avym77</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848014382874,0</v>
-    <v>0</v>
-    <v>avym77</v>
-    <v>USDCNY</v>
-    <v>21</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>cfzfpr</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070847124972672,0</v>
-    <v>0</v>
-    <v>cfzfpr</v>
-    <v>XNAS:GBUG</v>
-    <v>22</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1qlz2</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070852303489543,0</v>
-    <v>0</v>
-    <v>a1qlz2</v>
-    <v>XNYS:CVX</v>
-    <v>23</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1qlz2</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070852303664538,0</v>
-    <v>0</v>
-    <v>a1qlz2</v>
-    <v>XNYS:CVX</v>
-    <v>24</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1qlz2</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070852303833780,0</v>
-    <v>0</v>
-    <v>a1qlz2</v>
-    <v>XNYS:CVX</v>
-    <v>25</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1qlz2</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070852303993095,0</v>
-    <v>0</v>
-    <v>a1qlz2</v>
-    <v>XNYS:CVX</v>
-    <v>26</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1mou2</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844574962804,0</v>
-    <v>0</v>
-    <v>a1mou2</v>
-    <v>XNAS:AAPL</v>
-    <v>27</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1mou2</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848008823365,0</v>
-    <v>0</v>
-    <v>a1mou2</v>
-    <v>XNAS:AAPL</v>
-    <v>28</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1mou2</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848014129006,0</v>
-    <v>0</v>
-    <v>a1mou2</v>
-    <v>XNAS:AAPL</v>
-    <v>29</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1mou2</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848009974938,0</v>
-    <v>0</v>
-    <v>a1mou2</v>
-    <v>XNAS:AAPL</v>
-    <v>30</v>
-  </rv>
-  <rv s="11">
-    <v>40</v>
-    <v>avytar</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848008932454,0</v>
-    <v>0</v>
-    <v>avytar</v>
-    <v>USDTWD</v>
-    <v>31</v>
-  </rv>
-  <rv s="11">
-    <v>40</v>
-    <v>avytar</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844579671834,0</v>
-    <v>0</v>
-    <v>avytar</v>
-    <v>USDTWD</v>
-    <v>32</v>
-  </rv>
-  <rv s="11">
-    <v>40</v>
-    <v>avytar</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848014716442,0</v>
-    <v>0</v>
-    <v>avytar</v>
-    <v>USDTWD</v>
-    <v>33</v>
-  </rv>
-  <rv s="11">
-    <v>40</v>
-    <v>avytar</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844643088707,0</v>
-    <v>0</v>
-    <v>avytar</v>
-    <v>USDTWD</v>
-    <v>34</v>
-  </rv>
-  <rv s="11">
-    <v>40</v>
-    <v>avytar</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848013185331,0</v>
-    <v>0</v>
-    <v>avytar</v>
-    <v>USDTWD</v>
-    <v>35</v>
-  </rv>
-  <rv s="11">
-    <v>40</v>
-    <v>avytar</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070847661304743,0</v>
-    <v>0</v>
-    <v>avytar</v>
-    <v>USDTWD</v>
-    <v>36</v>
-  </rv>
-  <rv s="11">
-    <v>40</v>
-    <v>avytar</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848013931451,0</v>
-    <v>0</v>
-    <v>avytar</v>
-    <v>USDTWD</v>
-    <v>37</v>
-  </rv>
-  <rv s="11">
-    <v>40</v>
-    <v>avytar</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844648823485,0</v>
-    <v>0</v>
-    <v>avytar</v>
-    <v>USDTWD</v>
-    <v>38</v>
-  </rv>
-  <rv s="11">
-    <v>41</v>
-    <v>avyspr</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848009044119,0</v>
-    <v>0</v>
-    <v>avyspr</v>
-    <v>USDSGD</v>
-    <v>39</v>
-  </rv>
-  <rv s="11">
-    <v>41</v>
-    <v>avyspr</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844564842099,0</v>
-    <v>0</v>
-    <v>avyspr</v>
-    <v>USDSGD</v>
-    <v>40</v>
-  </rv>
-  <rv s="11">
-    <v>41</v>
-    <v>avyspr</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848013408948,0</v>
-    <v>0</v>
-    <v>avyspr</v>
-    <v>USDSGD</v>
-    <v>41</v>
-  </rv>
-  <rv s="11">
-    <v>41</v>
-    <v>avyspr</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070850759026761,0</v>
-    <v>0</v>
-    <v>avyspr</v>
-    <v>USDSGD</v>
-    <v>42</v>
-  </rv>
-  <rv s="11">
-    <v>41</v>
-    <v>avyspr</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844586318913,0</v>
-    <v>0</v>
-    <v>avyspr</v>
-    <v>USDSGD</v>
-    <v>43</v>
-  </rv>
-  <rv s="11">
-    <v>41</v>
-    <v>avyspr</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844638704384,0</v>
-    <v>0</v>
-    <v>avyspr</v>
-    <v>USDSGD</v>
-    <v>44</v>
-  </rv>
-  <rv s="11">
-    <v>41</v>
-    <v>avyspr</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848012178674,0</v>
-    <v>0</v>
-    <v>avyspr</v>
-    <v>USDSGD</v>
-    <v>45</v>
-  </rv>
-  <rv s="11">
-    <v>41</v>
-    <v>avyspr</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844644349654,0</v>
-    <v>0</v>
-    <v>avyspr</v>
-    <v>USDSGD</v>
-    <v>46</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a24b5r</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070847898465141,0</v>
-    <v>0</v>
-    <v>a24b5r</v>
-    <v>XNAS:TLT</v>
-    <v>47</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>aaxdur</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070851142033246,0</v>
-    <v>0</v>
-    <v>aaxdur</v>
-    <v>XTSE:CCO</v>
-    <v>48</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>aaxdur</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070851142518768,0</v>
-    <v>0</v>
-    <v>aaxdur</v>
-    <v>XTSE:CCO</v>
-    <v>49</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>aaxdur</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070851142993466,0</v>
-    <v>0</v>
-    <v>aaxdur</v>
-    <v>XTSE:CCO</v>
-    <v>50</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>aaxdur</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070851143463580,0</v>
-    <v>0</v>
-    <v>aaxdur</v>
-    <v>XTSE:CCO</v>
-    <v>51</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1yv52</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844586466077,0</v>
-    <v>0</v>
-    <v>a1yv52</v>
-    <v>XNAS:NVDA</v>
-    <v>52</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1yv52</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848010799048,0</v>
-    <v>0</v>
-    <v>a1yv52</v>
-    <v>XNAS:NVDA</v>
-    <v>53</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1yv52</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848012810262,0</v>
-    <v>0</v>
-    <v>a1yv52</v>
-    <v>XNAS:NVDA</v>
-    <v>54</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1yv52</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848014862293,0</v>
-    <v>0</v>
-    <v>a1yv52</v>
-    <v>XNAS:NVDA</v>
-    <v>55</v>
-  </rv>
-  <rv s="11">
-    <v>43</v>
-    <v>avyo8m</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848013048871,0</v>
-    <v>0</v>
-    <v>avyo8m</v>
-    <v>USDINR</v>
-    <v>56</v>
-  </rv>
-  <rv s="11">
-    <v>43</v>
-    <v>avyo8m</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070850758604687,0</v>
-    <v>0</v>
-    <v>avyo8m</v>
-    <v>USDINR</v>
-    <v>57</v>
-  </rv>
-  <rv s="11">
-    <v>43</v>
-    <v>avyo8m</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844636504247,0</v>
-    <v>0</v>
-    <v>avyo8m</v>
-    <v>USDINR</v>
-    <v>58</v>
-  </rv>
-  <rv s="11">
-    <v>43</v>
-    <v>avyo8m</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848010710422,0</v>
-    <v>0</v>
-    <v>avyo8m</v>
-    <v>USDINR</v>
-    <v>59</v>
-  </rv>
-  <rv s="11">
-    <v>43</v>
-    <v>avyo8m</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844637767264,0</v>
-    <v>0</v>
-    <v>avyo8m</v>
-    <v>USDINR</v>
-    <v>60</v>
-  </rv>
-  <rv s="11">
-    <v>43</v>
-    <v>avyo8m</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848011704532,0</v>
-    <v>0</v>
-    <v>avyo8m</v>
-    <v>USDINR</v>
-    <v>61</v>
-  </rv>
-  <rv s="11">
-    <v>43</v>
-    <v>avyo8m</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844651979757,0</v>
-    <v>0</v>
-    <v>avyo8m</v>
-    <v>USDINR</v>
-    <v>62</v>
-  </rv>
-  <rv s="11">
-    <v>43</v>
-    <v>avyo8m</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844655070656,0</v>
-    <v>0</v>
-    <v>avyo8m</v>
-    <v>USDINR</v>
-    <v>63</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>ce8mrw</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070846790730532,0</v>
-    <v>0</v>
-    <v>ce8mrw</v>
-    <v>XNAS:ETHA</v>
-    <v>64</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>ce8mrw</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848011745765,0</v>
-    <v>0</v>
-    <v>ce8mrw</v>
-    <v>XNAS:ETHA</v>
-    <v>65</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>ce8mrw</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848012855255,0</v>
-    <v>0</v>
-    <v>ce8mrw</v>
-    <v>XNAS:ETHA</v>
-    <v>66</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>ce8mrw</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848010117365,0</v>
-    <v>0</v>
-    <v>ce8mrw</v>
-    <v>XNAS:ETHA</v>
-    <v>67</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a269ec</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070851851202236,0</v>
-    <v>0</v>
-    <v>a269ec</v>
-    <v>XNYS:XOM</v>
-    <v>68</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a269ec</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070851851451128,0</v>
-    <v>0</v>
-    <v>a269ec</v>
-    <v>XNYS:XOM</v>
-    <v>69</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a269ec</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070851851690078,0</v>
-    <v>0</v>
-    <v>a269ec</v>
-    <v>XNYS:XOM</v>
-    <v>70</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a269ec</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070851851919073,0</v>
-    <v>0</v>
-    <v>a269ec</v>
-    <v>XNYS:XOM</v>
-    <v>71</v>
-  </rv>
-  <rv s="11">
-    <v>44</v>
-    <v>avyomw</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844583760213,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>72</v>
-  </rv>
-  <rv s="11">
-    <v>44</v>
-    <v>avyomw</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844586834135,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>73</v>
-  </rv>
-  <rv s="11">
-    <v>44</v>
-    <v>avyomw</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844591812265,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>74</v>
-  </rv>
-  <rv s="11">
-    <v>44</v>
-    <v>avyomw</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848010600876,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>75</v>
-  </rv>
-  <rv s="11">
-    <v>44</v>
-    <v>avyomw</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848014690109,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>76</v>
-  </rv>
-  <rv s="11">
-    <v>44</v>
-    <v>avyomw</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070850759307145,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>77</v>
-  </rv>
-  <rv s="11">
-    <v>44</v>
-    <v>avyomw</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070850759592522,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>78</v>
-  </rv>
-  <rv s="11">
-    <v>44</v>
-    <v>avyomw</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844653155774,0</v>
-    <v>0</v>
-    <v>avyomw</v>
-    <v>USDJPY</v>
-    <v>79</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a23hqh</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070853871461444,0</v>
-    <v>0</v>
-    <v>a23hqh</v>
-    <v>ARCX:SPY</v>
-    <v>80</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a23hqh</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848012661942,0</v>
-    <v>0</v>
-    <v>a23hqh</v>
-    <v>ARCX:SPY</v>
-    <v>81</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a23hqh</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070853871941697,0</v>
-    <v>0</v>
-    <v>a23hqh</v>
-    <v>ARCX:SPY</v>
-    <v>82</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a23hqh</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844633827978,0</v>
-    <v>0</v>
-    <v>a23hqh</v>
-    <v>ARCX:SPY</v>
-    <v>83</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwu2</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848011191607,0</v>
-    <v>0</v>
-    <v>auvwu2</v>
-    <v>Platinum</v>
-    <v>84</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwu2</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844581873234,0</v>
-    <v>0</v>
-    <v>auvwu2</v>
-    <v>Platinum</v>
-    <v>85</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwu2</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844631352319,0</v>
-    <v>0</v>
-    <v>auvwu2</v>
-    <v>Platinum</v>
-    <v>86</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwu2</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848010005442,0</v>
-    <v>0</v>
-    <v>auvwu2</v>
-    <v>Platinum</v>
-    <v>87</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwu2</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848010053897,0</v>
-    <v>0</v>
-    <v>auvwu2</v>
-    <v>Platinum</v>
-    <v>88</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwu2</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844596414752,0</v>
-    <v>0</v>
-    <v>auvwu2</v>
-    <v>Platinum</v>
-    <v>89</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwu2</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844635762331,0</v>
-    <v>0</v>
-    <v>auvwu2</v>
-    <v>Platinum</v>
-    <v>90</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwu2</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848014746022,0</v>
-    <v>0</v>
-    <v>auvwu2</v>
-    <v>Platinum</v>
-    <v>91</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>brjcfr</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844623140624,0</v>
-    <v>0</v>
-    <v>brjcfr</v>
-    <v>ETHUSD</v>
-    <v>92</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>brjcfr</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844566945594,0</v>
-    <v>0</v>
-    <v>brjcfr</v>
-    <v>ETHUSD</v>
-    <v>93</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>brjcfr</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848011939523,0</v>
-    <v>0</v>
-    <v>brjcfr</v>
-    <v>ETHUSD</v>
-    <v>94</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>brjcfr</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070850758749818,0</v>
-    <v>0</v>
-    <v>brjcfr</v>
-    <v>ETHUSD</v>
-    <v>95</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>brjcfr</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844594916717,0</v>
-    <v>0</v>
-    <v>brjcfr</v>
-    <v>ETHUSD</v>
-    <v>96</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>brjcfr</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844643184579,0</v>
-    <v>0</v>
-    <v>brjcfr</v>
-    <v>ETHUSD</v>
-    <v>97</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>brjcfr</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848014945984,0</v>
-    <v>0</v>
-    <v>brjcfr</v>
-    <v>ETHUSD</v>
-    <v>98</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>brjcfr</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848015131210,0</v>
-    <v>0</v>
-    <v>brjcfr</v>
-    <v>ETHUSD</v>
-    <v>99</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>avylur</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848009802795,0</v>
-    <v>0</v>
-    <v>avylur</v>
-    <v>USDCAD</v>
-    <v>100</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>avylur</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848013229799,0</v>
-    <v>0</v>
-    <v>avylur</v>
-    <v>USDCAD</v>
-    <v>101</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>avylur</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844582303979,0</v>
-    <v>0</v>
-    <v>avylur</v>
-    <v>USDCAD</v>
-    <v>102</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>avylur</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844590938699,0</v>
-    <v>0</v>
-    <v>avylur</v>
-    <v>USDCAD</v>
-    <v>103</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>avylur</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848010501311,0</v>
-    <v>0</v>
-    <v>avylur</v>
-    <v>USDCAD</v>
-    <v>104</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>avylur</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844642916682,0</v>
-    <v>0</v>
-    <v>avylur</v>
-    <v>USDCAD</v>
-    <v>105</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>avylur</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848015067000,0</v>
-    <v>0</v>
-    <v>avylur</v>
-    <v>USDCAD</v>
-    <v>106</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>avylur</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844645136020,0</v>
-    <v>0</v>
-    <v>avylur</v>
-    <v>USDCAD</v>
-    <v>107</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>cc5pdm</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070846725906122,0</v>
-    <v>0</v>
-    <v>cc5pdm</v>
-    <v>XNAS:IBIT</v>
-    <v>108</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>cc5pdm</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848014319728,0</v>
-    <v>0</v>
-    <v>cc5pdm</v>
-    <v>XNAS:IBIT</v>
-    <v>109</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>cc5pdm</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848014198711,0</v>
-    <v>0</v>
-    <v>cc5pdm</v>
-    <v>XNAS:IBIT</v>
-    <v>110</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1zfec</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844635541744,0</v>
-    <v>0</v>
-    <v>a1zfec</v>
-    <v>XNYS:PAAS</v>
-    <v>111</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1zfec</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848014859867,0</v>
-    <v>0</v>
-    <v>a1zfec</v>
-    <v>XNYS:PAAS</v>
-    <v>112</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvx6h</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848013600451,0</v>
-    <v>0</v>
-    <v>auvx6h</v>
-    <v>Natural Gas</v>
-    <v>113</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvx6h</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848013977362,0</v>
-    <v>0</v>
-    <v>auvx6h</v>
-    <v>Natural Gas</v>
-    <v>114</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvx6h</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844631607998,0</v>
-    <v>0</v>
-    <v>auvx6h</v>
-    <v>Natural Gas</v>
-    <v>115</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvx6h</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070850759168842,0</v>
-    <v>0</v>
-    <v>auvx6h</v>
-    <v>Natural Gas</v>
-    <v>116</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvx6h</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844597605580,0</v>
-    <v>0</v>
-    <v>auvx6h</v>
-    <v>Natural Gas</v>
-    <v>117</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvx6h</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844638424289,0</v>
-    <v>0</v>
-    <v>auvx6h</v>
-    <v>Natural Gas</v>
-    <v>118</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvx6h</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848015547720,0</v>
-    <v>0</v>
-    <v>auvx6h</v>
-    <v>Natural Gas</v>
-    <v>119</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvx6h</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844649280492,0</v>
-    <v>0</v>
-    <v>auvx6h</v>
-    <v>Natural Gas</v>
-    <v>120</v>
-  </rv>
-  <rv s="11">
-    <v>45</v>
-    <v>avytp2</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848012307736,0</v>
-    <v>0</v>
-    <v>avytp2</v>
-    <v>USDTRY</v>
-    <v>121</v>
-  </rv>
-  <rv s="11">
-    <v>45</v>
-    <v>avytp2</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844576580403,0</v>
-    <v>0</v>
-    <v>avytp2</v>
-    <v>USDTRY</v>
-    <v>122</v>
-  </rv>
-  <rv s="11">
-    <v>45</v>
-    <v>avytp2</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844587016918,0</v>
-    <v>0</v>
-    <v>avytp2</v>
-    <v>USDTRY</v>
-    <v>123</v>
-  </rv>
-  <rv s="11">
-    <v>45</v>
-    <v>avytp2</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848014109024,0</v>
-    <v>0</v>
-    <v>avytp2</v>
-    <v>USDTRY</v>
-    <v>124</v>
-  </rv>
-  <rv s="11">
-    <v>45</v>
-    <v>avytp2</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070847661269575,0</v>
-    <v>0</v>
-    <v>avytp2</v>
-    <v>USDTRY</v>
-    <v>125</v>
-  </rv>
-  <rv s="11">
-    <v>45</v>
-    <v>avytp2</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070850759454533,0</v>
-    <v>0</v>
-    <v>avytp2</v>
-    <v>USDTRY</v>
-    <v>126</v>
-  </rv>
-  <rv s="11">
-    <v>45</v>
-    <v>avytp2</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070850759196162,0</v>
-    <v>0</v>
-    <v>avytp2</v>
-    <v>USDTRY</v>
-    <v>127</v>
-  </rv>
-  <rv s="11">
-    <v>45</v>
-    <v>avytp2</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844649043738,0</v>
-    <v>0</v>
-    <v>avytp2</v>
-    <v>USDTRY</v>
-    <v>128</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>bo8l6h</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070847661182169,0</v>
-    <v>0</v>
-    <v>bo8l6h</v>
-    <v>BTCUSD</v>
-    <v>129</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>bo8l6h</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848011749726,0</v>
-    <v>0</v>
-    <v>bo8l6h</v>
-    <v>BTCUSD</v>
-    <v>130</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>bo8l6h</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848012139167,0</v>
-    <v>0</v>
-    <v>bo8l6h</v>
-    <v>BTCUSD</v>
-    <v>131</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>bo8l6h</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844578813331,0</v>
-    <v>0</v>
-    <v>bo8l6h</v>
-    <v>BTCUSD</v>
-    <v>132</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>bo8l6h</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844575779536,0</v>
-    <v>0</v>
-    <v>bo8l6h</v>
-    <v>BTCUSD</v>
-    <v>133</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>bo8l6h</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844646860045,0</v>
-    <v>0</v>
-    <v>bo8l6h</v>
-    <v>BTCUSD</v>
-    <v>134</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>bo8l6h</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070850759726859,0</v>
-    <v>0</v>
-    <v>bo8l6h</v>
-    <v>BTCUSD</v>
-    <v>135</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>bo8l6h</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848015305259,0</v>
-    <v>0</v>
-    <v>bo8l6h</v>
-    <v>BTCUSD</v>
-    <v>136</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1ndww</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844591442499,0</v>
-    <v>0</v>
-    <v>a1ndww</v>
-    <v>XNAS:AMD</v>
-    <v>137</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1ndww</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848009693269,0</v>
-    <v>0</v>
-    <v>a1ndww</v>
-    <v>XNAS:AMD</v>
-    <v>138</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1ndww</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848010929434,0</v>
-    <v>0</v>
-    <v>a1ndww</v>
-    <v>XNAS:AMD</v>
-    <v>139</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1ndww</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848015807157,0</v>
-    <v>0</v>
-    <v>a1ndww</v>
-    <v>XNAS:AMD</v>
-    <v>140</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a21mim</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844598129607,0</v>
-    <v>0</v>
-    <v>a21mim</v>
-    <v>XNAS:QQQ</v>
-    <v>141</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a21mim</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848012488606,0</v>
-    <v>0</v>
-    <v>a21mim</v>
-    <v>XNAS:QQQ</v>
-    <v>142</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a21mim</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848010389588,0</v>
-    <v>0</v>
-    <v>a21mim</v>
-    <v>XNAS:QQQ</v>
-    <v>143</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwoc</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070850758453140,0</v>
-    <v>0</v>
-    <v>auvwoc</v>
-    <v>Gold</v>
-    <v>144</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwoc</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844632936114,0</v>
-    <v>0</v>
-    <v>auvwoc</v>
-    <v>Gold</v>
-    <v>145</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwoc</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848010172554,0</v>
-    <v>0</v>
-    <v>auvwoc</v>
-    <v>Gold</v>
-    <v>146</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwoc</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848011146716,0</v>
-    <v>0</v>
-    <v>auvwoc</v>
-    <v>Gold</v>
-    <v>147</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwoc</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844640630708,0</v>
-    <v>0</v>
-    <v>auvwoc</v>
-    <v>Gold</v>
-    <v>148</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwoc</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070850759026213,0</v>
-    <v>0</v>
-    <v>auvwoc</v>
-    <v>Gold</v>
-    <v>149</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwoc</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070844654598138,0</v>
-    <v>0</v>
-    <v>auvwoc</v>
-    <v>Gold</v>
-    <v>150</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwoc</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844651047638,0</v>
-    <v>0</v>
-    <v>auvwoc</v>
-    <v>Gold</v>
-    <v>151</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a233ur</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844622370762,0</v>
-    <v>0</v>
-    <v>a233ur</v>
-    <v>ARCX:SLV</v>
-    <v>152</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a233ur</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848012516085,0</v>
-    <v>0</v>
-    <v>a233ur</v>
-    <v>ARCX:SLV</v>
-    <v>153</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1sp52</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844576074078,0</v>
-    <v>0</v>
-    <v>a1sp52</v>
-    <v>XNYS:FCX</v>
-    <v>154</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1sp52</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848013618985,0</v>
-    <v>0</v>
-    <v>a1sp52</v>
-    <v>XNYS:FCX</v>
-    <v>155</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1sp52</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848015434882,0</v>
-    <v>0</v>
-    <v>a1sp52</v>
-    <v>XNYS:FCX</v>
-    <v>156</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwr7</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848010989340,0</v>
-    <v>0</v>
-    <v>auvwr7</v>
-    <v>Silver</v>
-    <v>157</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwr7</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848012329713,0</v>
-    <v>0</v>
-    <v>auvwr7</v>
-    <v>Silver</v>
-    <v>158</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwr7</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848015230222,0</v>
-    <v>0</v>
-    <v>auvwr7</v>
-    <v>Silver</v>
-    <v>159</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwr7</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844584125999,0</v>
-    <v>0</v>
-    <v>auvwr7</v>
-    <v>Silver</v>
-    <v>160</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwr7</v>
-    <v>Daily</v>
-    <v>45338</v>
-    <v>45338</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638436384000000000,639070844594956536,0</v>
-    <v>0</v>
-    <v>auvwr7</v>
-    <v>Silver</v>
-    <v>161</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwr7</v>
-    <v>Daily</v>
-    <v>45520</v>
-    <v>45520</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638593632000000000,639070847661239365,0</v>
-    <v>0</v>
-    <v>auvwr7</v>
-    <v>Silver</v>
-    <v>162</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwr7</v>
-    <v>Daily</v>
-    <v>44610</v>
-    <v>44610</v>
-    <v>0</v>
-    <v>1</v>
-    <v>637807392000000000,639070848015068779,0</v>
-    <v>0</v>
-    <v>auvwr7</v>
-    <v>Silver</v>
-    <v>163</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>auvwr7</v>
-    <v>Daily</v>
-    <v>44974</v>
-    <v>44974</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638121888000000000,639070844654335621,0</v>
-    <v>0</v>
-    <v>auvwr7</v>
-    <v>Silver</v>
-    <v>164</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1upz2</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848014498652,0</v>
-    <v>0</v>
-    <v>a1upz2</v>
-    <v>XNYS:HL</v>
-    <v>165</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1upz2</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844577699242,0</v>
-    <v>0</v>
-    <v>a1upz2</v>
-    <v>XNYS:HL</v>
-    <v>166</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1upz2</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070853872427289,0</v>
-    <v>0</v>
-    <v>a1upz2</v>
-    <v>XNYS:HL</v>
-    <v>167</v>
-  </rv>
-  <rv s="11">
-    <v>37</v>
-    <v>a1upz2</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848010086577,0</v>
-    <v>0</v>
-    <v>a1upz2</v>
-    <v>XNYS:HL</v>
-    <v>168</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>ab1y3m</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848799843895,0</v>
-    <v>0</v>
-    <v>ab1y3m</v>
-    <v>XTSE:XIU</v>
-    <v>169</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>ab1y3m</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848799990413,0</v>
-    <v>0</v>
-    <v>ab1y3m</v>
-    <v>XTSE:XIU</v>
-    <v>170</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>ab1y3m</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070848800131812,0</v>
-    <v>0</v>
-    <v>ab1y3m</v>
-    <v>XTSE:XIU</v>
-    <v>171</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>ab1y3m</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848800251290,0</v>
-    <v>0</v>
-    <v>ab1y3m</v>
-    <v>XTSE:XIU</v>
-    <v>172</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>aay9k2</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070850161590933,0</v>
-    <v>0</v>
-    <v>aay9k2</v>
-    <v>XTSE:FNV</v>
-    <v>173</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>aay9k2</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070850162067698,0</v>
-    <v>0</v>
-    <v>aay9k2</v>
-    <v>XTSE:FNV</v>
-    <v>174</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>aay9k2</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070850162544601,0</v>
-    <v>0</v>
-    <v>aay9k2</v>
-    <v>XTSE:FNV</v>
-    <v>175</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>aay9k2</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070850163037923,0</v>
-    <v>0</v>
-    <v>aay9k2</v>
-    <v>XTSE:FNV</v>
-    <v>176</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>ab1ic7</v>
-    <v>Daily</v>
-    <v>46038</v>
-    <v>46038</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639041184000000000,639070844590906510,0</v>
-    <v>0</v>
-    <v>ab1ic7</v>
-    <v>XTSE:TRI</v>
-    <v>177</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>ab1ic7</v>
-    <v>Daily</v>
-    <v>45979</v>
-    <v>45979</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638990208000000000,639070848009151492,0</v>
-    <v>0</v>
-    <v>ab1ic7</v>
-    <v>XTSE:TRI</v>
-    <v>178</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>ab1ic7</v>
-    <v>Daily</v>
-    <v>46065</v>
-    <v>46065</v>
-    <v>0</v>
-    <v>1</v>
-    <v>639064512000000000,639070848009251053,0</v>
-    <v>0</v>
-    <v>ab1ic7</v>
-    <v>XTSE:TRI</v>
-    <v>179</v>
-  </rv>
-  <rv s="11">
-    <v>42</v>
-    <v>ab1ic7</v>
-    <v>Daily</v>
-    <v>45706</v>
-    <v>45706</v>
-    <v>0</v>
-    <v>1</v>
-    <v>638754336000000000,639070848009361158,0</v>
-    <v>0</v>
-    <v>ab1ic7</v>
-    <v>XTSE:TRI</v>
-    <v>180</v>
-  </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="12">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="11">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -5374,6 +2343,7 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
+    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -5408,11 +2378,16 @@
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
   </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
+    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -5447,15 +2422,12 @@
     <k n="Volume"/>
     <k n="Volume average"/>
   </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
+    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -5491,6 +2463,7 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
+    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -5528,6 +2501,7 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
+    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -5575,6 +2549,7 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
+    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -5604,6 +2579,7 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
+    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -5630,6 +2606,7 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
+    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -5653,27 +2630,13 @@
     <k n="UniqueName" t="s"/>
     <k n="Year"/>
   </s>
-  <s t="_stockhistorycache">
-    <k n="_Format" t="spb"/>
-    <k n="Symbol" t="s"/>
-    <k n="Interval" t="s"/>
-    <k n="StartDate" t="i"/>
-    <k n="EndDate" t="i"/>
-    <k n="f1904" t="b"/>
-    <k n="fdcompat" t="b"/>
-    <k n="etag" t="s"/>
-    <k n="Date" t="a"/>
-    <k n="EntityId" t="s"/>
-    <k n="Instrument" t="s"/>
-    <k n="Close" t="a"/>
-  </s>
 </rvStructures>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="8">
-    <a count="34">
+    <a count="35">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -5708,8 +2671,9 @@
       <v t="s">_DisplayString</v>
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
+      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="37">
+    <a count="38">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -5747,8 +2711,9 @@
       <v t="s">_DisplayString</v>
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
+      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="33">
+    <a count="34">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -5782,8 +2747,9 @@
       <v t="s">_DisplayString</v>
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
+      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="35">
+    <a count="36">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -5819,8 +2785,9 @@
       <v t="s">UniqueName</v>
       <v t="s">_DisplayString</v>
       <v t="s">%ProviderInfo</v>
+      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="45">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -5866,8 +2833,9 @@
       <v t="s">LearnMoreOnLink</v>
       <v t="s">ExchangeID</v>
       <v t="s">%ProviderInfo</v>
+      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="27">
+    <a count="28">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -5895,8 +2863,9 @@
       <v t="s">UniqueName</v>
       <v t="s">_DisplayString</v>
       <v t="s">%ProviderInfo</v>
+      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="24">
+    <a count="25">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -5921,8 +2890,9 @@
       <v t="s">UniqueName</v>
       <v t="s">_DisplayString</v>
       <v t="s">%ProviderInfo</v>
+      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="26">
+    <a count="27">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -5949,9 +2919,10 @@
       <v t="s">_DisplayString</v>
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
+      <v t="s">%OutdatedReason</v>
     </a>
   </spbArrays>
-  <spbData count="46">
+  <spbData count="37">
     <spb s="0">
       <v>0</v>
       <v>Name</v>
@@ -6363,48 +3334,12 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>1</v>
-    </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>12</v>
-    </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>14</v>
-    </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>18</v>
-    </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>17</v>
-    </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>9</v>
-    </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>16</v>
-    </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>13</v>
-    </spb>
-    <spb s="20">
-      <v>19</v>
-      <v>15</v>
-    </spb>
   </spbData>
 </supportingPropertyBags>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="21">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="20">
   <s>
     <k n="^Order" t="spba"/>
     <k n="TitleProperty" t="s"/>
@@ -6619,10 +3554,6 @@
     <k n="Expiration Date" t="i"/>
     <k n="Last trade time" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
-  </s>
-  <s>
-    <k n="Date" t="i"/>
-    <k n="Close" t="i"/>
   </s>
 </spbStructures>
 </file>
@@ -7056,19 +3987,19 @@
       </c>
       <c r="I1" s="8">
         <f ca="1">WORKDAY(TODAY(),-5)</f>
-        <v>46065</v>
+        <v>46132</v>
       </c>
       <c r="J1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-1),-1)</f>
-        <v>46038</v>
+        <v>46107</v>
       </c>
       <c r="K1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-3),-1)</f>
-        <v>45979</v>
+        <v>46048</v>
       </c>
       <c r="L1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-12),-1)</f>
-        <v>45706</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7101,25 +4032,25 @@
         <f ca="1">IF(F2="CAD",G2,(G2*Currency!$B$2))</f>
         <v>93891.356800000009</v>
       </c>
-      <c r="I2" s="2" cm="1">
+      <c r="I2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I2" ca="1">($E2 - _xlfn.STOCKHISTORY($A2, I$1,I$1,0,0,1))/$E2</f>
-        <v>7.2423641874563233E-3</v>
-      </c>
-      <c r="J2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J2" ca="1">($E2 - _xlfn.STOCKHISTORY($A2, J$1,J$1,0,0,1))/$E2</f>
-        <v>-7.8981114478898912E-3</v>
-      </c>
-      <c r="K2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K2" ca="1">($E2 - _xlfn.STOCKHISTORY($A2, K$1,K$1,0,0,1))/$E2</f>
-        <v>3.8120774073210489E-2</v>
-      </c>
-      <c r="L2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L2" ca="1">($E2 - _xlfn.STOCKHISTORY($A2, L$1,L$1,0,0,1))/$E2</f>
-        <v>0.10892690603870366</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="e" vm="2">
+      <c r="A3" s="5" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -7148,19 +4079,19 @@
         <f ca="1">IF(F3="CAD",G3,(G3*Currency!$B$2))</f>
         <v>82884.1878</v>
       </c>
-      <c r="I3" s="2" cm="1">
+      <c r="I3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I3" ca="1">($E3 - _xlfn.STOCKHISTORY($A3, I$1,I$1,0,0,1))/$E3</f>
-        <v>8.5012958285874268E-3</v>
-      </c>
-      <c r="J3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J3" ca="1">($E3 - _xlfn.STOCKHISTORY($A3, J$1,J$1,0,0,1))/$E3</f>
-        <v>-2.5536902226844332E-2</v>
-      </c>
-      <c r="K3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K3" ca="1">($E3 - _xlfn.STOCKHISTORY($A3, K$1,K$1,0,0,1))/$E3</f>
-        <v>1.5648987272817345E-2</v>
-      </c>
-      <c r="L3" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L3" ca="1">($E3 - _xlfn.STOCKHISTORY($A3, L$1,L$1,0,0,1))/$E3</f>
         <v>#VALUE!</v>
       </c>
@@ -7195,21 +4126,21 @@
         <f ca="1">IF(F4="CAD",G4,(G4*Currency!$B$2))</f>
         <v>98160</v>
       </c>
-      <c r="I4" s="2" cm="1">
+      <c r="I4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I4" ca="1">($E4 - _xlfn.STOCKHISTORY($A4, I$1,I$1,0,0,1))/$E4</f>
-        <v>2.6283618581907073E-2</v>
-      </c>
-      <c r="J4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J4" ca="1">($E4 - _xlfn.STOCKHISTORY($A4, J$1,J$1,0,0,1))/$E4</f>
-        <v>8.9649551752240784E-3</v>
-      </c>
-      <c r="K4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K4" ca="1">($E4 - _xlfn.STOCKHISTORY($A4, K$1,K$1,0,0,1))/$E4</f>
-        <v>8.5370823145884234E-2</v>
-      </c>
-      <c r="L4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L4" ca="1">($E4 - _xlfn.STOCKHISTORY($A4, L$1,L$1,0,0,1))/$E4</f>
-        <v>0.20273023634881818</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -7242,19 +4173,19 @@
         <f ca="1">IF(F5="CAD",G5,(G5*Currency!$B$2))</f>
         <v>97995.9568</v>
       </c>
-      <c r="I5" s="2" t="e" cm="1" vm="3">
+      <c r="I5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I5" ca="1">($E5 - _xlfn.STOCKHISTORY($A5, I$1,I$1,0,0,1))/$E5</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J5" s="2" cm="1">
+      <c r="J5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J5" ca="1">($E5 - _xlfn.STOCKHISTORY($A5, J$1,J$1,0,0,1))/$E5</f>
-        <v>1.93231319110913E-2</v>
-      </c>
-      <c r="K5" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K5" ca="1">($E5 - _xlfn.STOCKHISTORY($A5, K$1,K$1,0,0,1))/$E5</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L5" s="2" t="e" cm="1" vm="3">
+      <c r="L5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L5" ca="1">($E5 - _xlfn.STOCKHISTORY($A5, L$1,L$1,0,0,1))/$E5</f>
         <v>#VALUE!</v>
       </c>
@@ -7289,19 +4220,19 @@
         <f ca="1">IF(F6="CAD",G6,(G6*Currency!$B$2))</f>
         <v>69266.630019999997</v>
       </c>
-      <c r="I6" s="2" t="e" cm="1" vm="3">
+      <c r="I6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I6" ca="1">($E6 - _xlfn.STOCKHISTORY($A6, I$1,I$1,0,0,1))/$E6</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J6" s="2" cm="1">
+      <c r="J6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J6" ca="1">($E6 - _xlfn.STOCKHISTORY($A6, J$1,J$1,0,0,1))/$E6</f>
-        <v>5.3057612575331758E-2</v>
-      </c>
-      <c r="K6" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K6" ca="1">($E6 - _xlfn.STOCKHISTORY($A6, K$1,K$1,0,0,1))/$E6</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L6" s="2" t="e" cm="1" vm="3">
+      <c r="L6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L6" ca="1">($E6 - _xlfn.STOCKHISTORY($A6, L$1,L$1,0,0,1))/$E6</f>
         <v>#VALUE!</v>
       </c>
@@ -7336,21 +4267,21 @@
         <f ca="1">IF(F7="CAD",G7,(G7*Currency!$B$2))</f>
         <v>69620</v>
       </c>
-      <c r="I7" s="2" cm="1">
+      <c r="I7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I7" ca="1">($E7 - _xlfn.STOCKHISTORY($A7, I$1,I$1,0,0,1))/$E7</f>
-        <v>6.3142775064636641E-2</v>
-      </c>
-      <c r="J7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J7" ca="1">($E7 - _xlfn.STOCKHISTORY($A7, J$1,J$1,0,0,1))/$E7</f>
-        <v>2.6802642918701637E-2</v>
-      </c>
-      <c r="K7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K7" ca="1">($E7 - _xlfn.STOCKHISTORY($A7, K$1,K$1,0,0,1))/$E7</f>
-        <v>0.21591496696351628</v>
-      </c>
-      <c r="L7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L7" ca="1">($E7 - _xlfn.STOCKHISTORY($A7, L$1,L$1,0,0,1))/$E7</f>
-        <v>0.42651536914679694</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -7383,19 +4314,19 @@
         <f ca="1">IF(F8="CAD",G8,(G8*Currency!$B$2))</f>
         <v>79360</v>
       </c>
-      <c r="I8" s="2" t="e" cm="1" vm="3">
+      <c r="I8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I8" ca="1">($E8 - _xlfn.STOCKHISTORY($A8, I$1,I$1,0,0,1))/$E8</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J8" s="2" t="e" cm="1" vm="3">
+      <c r="J8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J8" ca="1">($E8 - _xlfn.STOCKHISTORY($A8, J$1,J$1,0,0,1))/$E8</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K8" s="2" t="e" cm="1" vm="3">
+      <c r="K8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K8" ca="1">($E8 - _xlfn.STOCKHISTORY($A8, K$1,K$1,0,0,1))/$E8</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L8" s="2" t="e" cm="1" vm="3">
+      <c r="L8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L8" ca="1">($E8 - _xlfn.STOCKHISTORY($A8, L$1,L$1,0,0,1))/$E8</f>
         <v>#VALUE!</v>
       </c>
@@ -7430,21 +4361,21 @@
         <f ca="1">IF(F9="CAD",G9,(G9*Currency!$B$2))</f>
         <v>79760</v>
       </c>
-      <c r="I9" s="2" cm="1">
+      <c r="I9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I9" ca="1">($E9 - _xlfn.STOCKHISTORY($A9, I$1,I$1,0,0,1))/$E9</f>
-        <v>6.832998996990994E-3</v>
-      </c>
-      <c r="J9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J9" ca="1">($E9 - _xlfn.STOCKHISTORY($A9, J$1,J$1,0,0,1))/$E9</f>
-        <v>-1.5922768304914695E-2</v>
-      </c>
-      <c r="K9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K9" ca="1">($E9 - _xlfn.STOCKHISTORY($A9, K$1,K$1,0,0,1))/$E9</f>
-        <v>0.2698094282848546</v>
-      </c>
-      <c r="L9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L9" ca="1">($E9 - _xlfn.STOCKHISTORY($A9, L$1,L$1,0,0,1))/$E9</f>
-        <v>0.57372116349047142</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -7477,21 +4408,21 @@
         <f ca="1">IF(F10="CAD",G10,(G10*Currency!$B$2))</f>
         <v>51438.847200000004</v>
       </c>
-      <c r="I10" s="2" cm="1">
+      <c r="I10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I10" ca="1">($E10 - _xlfn.STOCKHISTORY($A10, I$1,I$1,0,0,1))/$E10</f>
-        <v>5.5325034578146189E-3</v>
-      </c>
-      <c r="J10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J10" ca="1">($E10 - _xlfn.STOCKHISTORY($A10, J$1,J$1,0,0,1))/$E10</f>
-        <v>9.3095010107458239E-3</v>
-      </c>
-      <c r="K10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K10" ca="1">($E10 - _xlfn.STOCKHISTORY($A10, K$1,K$1,0,0,1))/$E10</f>
-        <v>3.5216512394935506E-2</v>
-      </c>
-      <c r="L10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L10" ca="1">($E10 - _xlfn.STOCKHISTORY($A10, L$1,L$1,0,0,1))/$E10</f>
-        <v>0.25843174805830399</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -7524,21 +4455,21 @@
         <f ca="1">IF(F11="CAD",G11,(G11*Currency!$B$2))</f>
         <v>54760.836800000005</v>
       </c>
-      <c r="I11" s="2" cm="1">
+      <c r="I11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I11" ca="1">($E11 - _xlfn.STOCKHISTORY($A11, I$1,I$1,0,0,1))/$E11</f>
-        <v>-2.9082550469718135E-2</v>
-      </c>
-      <c r="J11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J11" ca="1">($E11 - _xlfn.STOCKHISTORY($A11, J$1,J$1,0,0,1))/$E11</f>
-        <v>-0.15845492704377379</v>
-      </c>
-      <c r="K11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K11" ca="1">($E11 - _xlfn.STOCKHISTORY($A11, K$1,K$1,0,0,1))/$E11</f>
-        <v>-0.15075954427343588</v>
-      </c>
-      <c r="L11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L11" ca="1">($E11 - _xlfn.STOCKHISTORY($A11, L$1,L$1,0,0,1))/$E11</f>
-        <v>0.42894263441934838</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -7571,19 +4502,19 @@
         <f ca="1">IF(F12="CAD",G12,(G12*Currency!$B$2))</f>
         <v>62377.606200000002</v>
       </c>
-      <c r="I12" s="2" cm="1">
+      <c r="I12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I12" ca="1">($E12 - _xlfn.STOCKHISTORY($A12, I$1,I$1,0,0,1))/$E12</f>
-        <v>-1.7865368164769385E-2</v>
-      </c>
-      <c r="J12" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J12" ca="1">($E12 - _xlfn.STOCKHISTORY($A12, J$1,J$1,0,0,1))/$E12</f>
-        <v>-8.6859248535895162E-2</v>
-      </c>
-      <c r="K12" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K12" ca="1">($E12 - _xlfn.STOCKHISTORY($A12, K$1,K$1,0,0,1))/$E12</f>
-        <v>6.2446535500427773E-2</v>
-      </c>
-      <c r="L12" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L12" ca="1">($E12 - _xlfn.STOCKHISTORY($A12, L$1,L$1,0,0,1))/$E12</f>
         <v>#VALUE!</v>
       </c>
@@ -7618,21 +4549,21 @@
         <f ca="1">IF(F13="CAD",G13,(G13*Currency!$B$2))</f>
         <v>41232.075199999999</v>
       </c>
-      <c r="I13" s="2" cm="1">
+      <c r="I13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I13" ca="1">($E13 - _xlfn.STOCKHISTORY($A13, I$1,I$1,0,0,1))/$E13</f>
-        <v>4.9774356251659144E-3</v>
-      </c>
-      <c r="J13" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J13" ca="1">($E13 - _xlfn.STOCKHISTORY($A13, J$1,J$1,0,0,1))/$E13</f>
-        <v>0.13797451552959927</v>
-      </c>
-      <c r="K13" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K13" ca="1">($E13 - _xlfn.STOCKHISTORY($A13, K$1,K$1,0,0,1))/$E13</f>
-        <v>0.21004778338200161</v>
-      </c>
-      <c r="L13" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L13" ca="1">($E13 - _xlfn.STOCKHISTORY($A13, L$1,L$1,0,0,1))/$E13</f>
-        <v>0.26904698699230162</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -7665,21 +4596,21 @@
         <f ca="1">IF(F14="CAD",G14,(G14*Currency!$B$2))</f>
         <v>50314.186800000003</v>
       </c>
-      <c r="I14" s="2" cm="1">
+      <c r="I14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I14" ca="1">($E14 - _xlfn.STOCKHISTORY($A14, I$1,I$1,0,0,1))/$E14</f>
-        <v>7.9947789198890461E-3</v>
-      </c>
-      <c r="J14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J14" ca="1">($E14 - _xlfn.STOCKHISTORY($A14, J$1,J$1,0,0,1))/$E14</f>
-        <v>9.5774188285201567E-2</v>
-      </c>
-      <c r="K14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K14" ca="1">($E14 - _xlfn.STOCKHISTORY($A14, K$1,K$1,0,0,1))/$E14</f>
-        <v>0.1645184097460162</v>
-      </c>
-      <c r="L14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L14" ca="1">($E14 - _xlfn.STOCKHISTORY($A14, L$1,L$1,0,0,1))/$E14</f>
-        <v>0.15070430195246645</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -7712,21 +4643,21 @@
         <f ca="1">IF(F15="CAD",G15,(G15*Currency!$B$2))</f>
         <v>51362.228000000003</v>
       </c>
-      <c r="I15" s="2" cm="1">
+      <c r="I15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I15" ca="1">($E15 - _xlfn.STOCKHISTORY($A15, I$1,I$1,0,0,1))/$E15</f>
-        <v>1.3052743740010709E-2</v>
-      </c>
-      <c r="J15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J15" ca="1">($E15 - _xlfn.STOCKHISTORY($A15, J$1,J$1,0,0,1))/$E15</f>
-        <v>-0.44485881726158771</v>
-      </c>
-      <c r="K15" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K15" ca="1">($E15 - _xlfn.STOCKHISTORY($A15, K$1,K$1,0,0,1))/$E15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L15" s="2" cm="1">
+      <c r="L15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L15" ca="1">($E15 - _xlfn.STOCKHISTORY($A15, L$1,L$1,0,0,1))/$E15</f>
-        <v>-0.42541289291422479</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -7759,21 +4690,21 @@
         <f ca="1">IF(F16="CAD",G16,(G16*Currency!$B$2))</f>
         <v>10008.383</v>
       </c>
-      <c r="I16" s="2" cm="1">
+      <c r="I16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I16" ca="1">($E16 - _xlfn.STOCKHISTORY($A16, I$1,I$1,0,0,1))/$E16</f>
-        <v>1.1619958988380035E-2</v>
-      </c>
-      <c r="J16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J16" ca="1">($E16 - _xlfn.STOCKHISTORY($A16, J$1,J$1,0,0,1))/$E16</f>
-        <v>-0.70061517429938469</v>
-      </c>
-      <c r="K16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K16" ca="1">($E16 - _xlfn.STOCKHISTORY($A16, K$1,K$1,0,0,1))/$E16</f>
-        <v>-0.61244019138755967</v>
-      </c>
-      <c r="L16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="L16" ca="1">($E16 - _xlfn.STOCKHISTORY($A16, L$1,L$1,0,0,1))/$E16</f>
-        <v>-0.36021872863978111</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
@@ -8005,19 +4936,19 @@
       </c>
       <c r="O1" s="8">
         <f ca="1">WORKDAY(TODAY(),-5)</f>
-        <v>46065</v>
+        <v>46132</v>
       </c>
       <c r="P1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-1),-1)</f>
-        <v>46038</v>
+        <v>46107</v>
       </c>
       <c r="Q1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-3),-1)</f>
-        <v>45979</v>
+        <v>46048</v>
       </c>
       <c r="R1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-12),-1)</f>
-        <v>45706</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
@@ -8052,7 +4983,7 @@
         <v>USD</v>
       </c>
       <c r="J2" s="9">
-        <f ca="1">IF(E2="PUT",IF((H2-F2)&lt;0,(F2-H2)*G2,0),IF((H2-F2)&gt;0,(H2-F2)*G2,0))</f>
+        <f t="shared" ref="J2:J17" ca="1" si="0">IF(E2="PUT",IF((H2-F2)&lt;0,(F2-H2)*G2,0),IF((H2-F2)&gt;0,(H2-F2)*G2,0))</f>
         <v>0</v>
       </c>
       <c r="K2" s="9">
@@ -8063,28 +4994,28 @@
         <v>36</v>
       </c>
       <c r="M2" s="9">
-        <f>L2*-G2</f>
+        <f t="shared" ref="M2:M17" si="1">L2*-G2</f>
         <v>180000</v>
       </c>
       <c r="N2" s="9">
         <f ca="1">IF(I2="CAD",M2,(M2*Currency!$B$2))</f>
         <v>246276.00000000003</v>
       </c>
-      <c r="O2" s="2" t="e" cm="1" vm="3">
+      <c r="O2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O2" ca="1">($H2 - _xlfn.STOCKHISTORY($A2, O$1,O$1,0,0,1))/$H2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P2" s="2" cm="1">
+      <c r="P2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P2" ca="1">(H2 - _xlfn.STOCKHISTORY($A2, P$1,P$1,0,0,1))/$H2</f>
-        <v>6.1390887290167812E-2</v>
-      </c>
-      <c r="Q2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q2" ca="1">($H2 - _xlfn.STOCKHISTORY($A2, Q$1,Q$1,0,0,1))/$H2</f>
-        <v>0.36051159072741806</v>
-      </c>
-      <c r="R2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R2" ca="1">($H2 - _xlfn.STOCKHISTORY($A2, R$1,R$1,0,0,1))/$H2</f>
-        <v>0.37170263788968827</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
@@ -8119,7 +5050,7 @@
         <v>USD</v>
       </c>
       <c r="J3" s="9">
-        <f ca="1">IF(E3="PUT",IF((H3-F3)&lt;0,(F3-H3)*G3,0),IF((H3-F3)&gt;0,(H3-F3)*G3,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K3" s="9">
@@ -8131,28 +5062,28 @@
         <v>0</v>
       </c>
       <c r="M3" s="9">
-        <f>L3*-G3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N3" s="9">
         <f ca="1">IF(I3="CAD",M3,(M3*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O3" s="2" t="e" cm="1" vm="3">
+      <c r="O3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O3" ca="1">($H3 - _xlfn.STOCKHISTORY($A3, O$1,O$1,0,0,1))/$H3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P3" s="2" cm="1">
+      <c r="P3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P3" ca="1">(H3 - _xlfn.STOCKHISTORY($A3, P$1,P$1,0,0,1))/$H3</f>
-        <v>6.1390887290167812E-2</v>
-      </c>
-      <c r="Q3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q3" ca="1">($H3 - _xlfn.STOCKHISTORY($A3, Q$1,Q$1,0,0,1))/$H3</f>
-        <v>0.36051159072741806</v>
-      </c>
-      <c r="R3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R3" ca="1">($H3 - _xlfn.STOCKHISTORY($A3, R$1,R$1,0,0,1))/$H3</f>
-        <v>0.37170263788968827</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -8187,7 +5118,7 @@
         <v>USD</v>
       </c>
       <c r="J4" s="9">
-        <f ca="1">IF(E4="PUT",IF((H4-F4)&lt;0,(F4-H4)*G4,0),IF((H4-F4)&gt;0,(H4-F4)*G4,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K4" s="9">
@@ -8198,28 +5129,28 @@
         <v>18</v>
       </c>
       <c r="M4" s="9">
-        <f>L4*-G4</f>
+        <f t="shared" si="1"/>
         <v>90000</v>
       </c>
       <c r="N4" s="9">
         <f ca="1">IF(I4="CAD",M4,(M4*Currency!$B$2))</f>
         <v>123138.00000000001</v>
       </c>
-      <c r="O4" s="2" cm="1">
+      <c r="O4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O4" ca="1">($H4 - _xlfn.STOCKHISTORY($A4, O$1,O$1,0,0,1))/$H4</f>
-        <v>5.1316984559491324E-2</v>
-      </c>
-      <c r="P4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P4" ca="1">(H4 - _xlfn.STOCKHISTORY($A4, P$1,P$1,0,0,1))/$H4</f>
-        <v>-0.20526793823796546</v>
-      </c>
-      <c r="Q4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q4" ca="1">($H4 - _xlfn.STOCKHISTORY($A4, Q$1,Q$1,0,0,1))/$H4</f>
-        <v>0.36148955495004537</v>
-      </c>
-      <c r="R4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R4" ca="1">($H4 - _xlfn.STOCKHISTORY($A4, R$1,R$1,0,0,1))/$H4</f>
-        <v>0.74750227066303365</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
@@ -8254,7 +5185,7 @@
         <v>USD</v>
       </c>
       <c r="J5" s="9">
-        <f ca="1">IF(E5="PUT",IF((H5-F5)&lt;0,(F5-H5)*G5,0),IF((H5-F5)&gt;0,(H5-F5)*G5,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>14950.000000000002</v>
       </c>
       <c r="K5" s="9">
@@ -8266,28 +5197,28 @@
         <v>0</v>
       </c>
       <c r="M5" s="9">
-        <f>L5*-G5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N5" s="9">
         <f ca="1">IF(I5="CAD",M5,(M5*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O5" s="2" cm="1">
+      <c r="O5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O5" ca="1">($H5 - _xlfn.STOCKHISTORY($A5, O$1,O$1,0,0,1))/$H5</f>
-        <v>5.1316984559491324E-2</v>
-      </c>
-      <c r="P5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P5" ca="1">(H5 - _xlfn.STOCKHISTORY($A5, P$1,P$1,0,0,1))/$H5</f>
-        <v>-0.20526793823796546</v>
-      </c>
-      <c r="Q5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q5" ca="1">($H5 - _xlfn.STOCKHISTORY($A5, Q$1,Q$1,0,0,1))/$H5</f>
-        <v>0.36148955495004537</v>
-      </c>
-      <c r="R5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R5" ca="1">($H5 - _xlfn.STOCKHISTORY($A5, R$1,R$1,0,0,1))/$H5</f>
-        <v>0.74750227066303365</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -8302,7 +5233,7 @@
         <v>SLV</v>
       </c>
       <c r="D6" s="7">
-        <v>46129</v>
+        <v>46191</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
@@ -8322,7 +5253,7 @@
         <v>USD</v>
       </c>
       <c r="J6" s="9">
-        <f ca="1">IF(E6="PUT",IF((H6-F6)&lt;0,(F6-H6)*G6,0),IF((H6-F6)&gt;0,(H6-F6)*G6,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K6" s="9">
@@ -8333,26 +5264,26 @@
         <v>55.5</v>
       </c>
       <c r="M6" s="9">
-        <f>L6*-G6</f>
+        <f t="shared" si="1"/>
         <v>277500</v>
       </c>
       <c r="N6" s="9">
         <f ca="1">IF(I6="CAD",M6,(M6*Currency!$B$2))</f>
         <v>379675.5</v>
       </c>
-      <c r="O6" s="2" t="e" cm="1" vm="3">
+      <c r="O6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O6" ca="1">($H6 - _xlfn.STOCKHISTORY($A6, O$1,O$1,0,0,1))/$H6</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P6" s="2" cm="1">
+      <c r="P6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P6" ca="1">(H6 - _xlfn.STOCKHISTORY($A6, P$1,P$1,0,0,1))/$H6</f>
-        <v>-0.15594235982308449</v>
-      </c>
-      <c r="Q6" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q6" ca="1">($H6 - _xlfn.STOCKHISTORY($A6, Q$1,Q$1,0,0,1))/$H6</f>
-        <v>0.34227421886146386</v>
-      </c>
-      <c r="R6" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R6" ca="1">($H6 - _xlfn.STOCKHISTORY($A6, R$1,R$1,0,0,1))/$H6</f>
         <v>#VALUE!</v>
       </c>
@@ -8369,13 +5300,13 @@
         <v>SLV</v>
       </c>
       <c r="D7" s="7">
-        <v>46129</v>
+        <v>46191</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>70.5</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>2500</v>
@@ -8389,37 +5320,37 @@
         <v>USD</v>
       </c>
       <c r="J7" s="9">
-        <f ca="1">IF(E7="PUT",IF((H7-F7)&lt;0,(F7-H7)*G7,0),IF((H7-F7)&gt;0,(H7-F7)*G7,0))</f>
-        <v>1024.9999999999914</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
       </c>
       <c r="K7" s="9">
         <f ca="1">IF(I7="CAD",J7,(J7*Currency!$B$2))</f>
-        <v>1402.4049999999884</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
       </c>
       <c r="M7" s="9">
-        <f>L7*-G7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N7" s="9">
         <f ca="1">IF(I7="CAD",M7,(M7*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="2" t="e" cm="1" vm="3">
+      <c r="O7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O7" ca="1">($H7 - _xlfn.STOCKHISTORY($A7, O$1,O$1,0,0,1))/$H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P7" s="2" cm="1">
+      <c r="P7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P7" ca="1">(H7 - _xlfn.STOCKHISTORY($A7, P$1,P$1,0,0,1))/$H7</f>
-        <v>-0.15594235982308449</v>
-      </c>
-      <c r="Q7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q7" ca="1">($H7 - _xlfn.STOCKHISTORY($A7, Q$1,Q$1,0,0,1))/$H7</f>
-        <v>0.34227421886146386</v>
-      </c>
-      <c r="R7" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R7" ca="1">($H7 - _xlfn.STOCKHISTORY($A7, R$1,R$1,0,0,1))/$H7</f>
         <v>#VALUE!</v>
       </c>
@@ -8456,7 +5387,7 @@
         <v>USD</v>
       </c>
       <c r="J8" s="9">
-        <f ca="1">IF(E8="PUT",IF((H8-F8)&lt;0,(F8-H8)*G8,0),IF((H8-F8)&gt;0,(H8-F8)*G8,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K8" s="9">
@@ -8467,28 +5398,28 @@
         <v>0</v>
       </c>
       <c r="M8" s="9">
-        <f>L8*-G8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N8" s="9">
         <f ca="1">IF(I8="CAD",M8,(M8*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="2" cm="1">
+      <c r="O8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O8" ca="1">($H8 - _xlfn.STOCKHISTORY($A8, O$1,O$1,0,0,1))/$H8</f>
-        <v>9.9111027047475101E-3</v>
-      </c>
-      <c r="P8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P8" ca="1">(H8 - _xlfn.STOCKHISTORY($A8, P$1,P$1,0,0,1))/$H8</f>
-        <v>3.3364857196898128E-2</v>
-      </c>
-      <c r="Q8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q8" ca="1">($H8 - _xlfn.STOCKHISTORY($A8, Q$1,Q$1,0,0,1))/$H8</f>
-        <v>-1.1689048609797522E-2</v>
-      </c>
-      <c r="R8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R8" ca="1">($H8 - _xlfn.STOCKHISTORY($A8, R$1,R$1,0,0,1))/$H8</f>
-        <v>7.5203328919992513E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
@@ -8523,7 +5454,7 @@
         <v>USD</v>
       </c>
       <c r="J9" s="9">
-        <f ca="1">IF(E9="PUT",IF((H9-F9)&lt;0,(F9-H9)*G9,0),IF((H9-F9)&gt;0,(H9-F9)*G9,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="9">
@@ -8534,28 +5465,28 @@
         <v>200</v>
       </c>
       <c r="M9" s="9">
-        <f>L9*-G9</f>
+        <f t="shared" si="1"/>
         <v>180000</v>
       </c>
       <c r="N9" s="9">
         <f ca="1">IF(I9="CAD",M9,(M9*Currency!$B$2))</f>
         <v>246276.00000000003</v>
       </c>
-      <c r="O9" s="2" cm="1">
+      <c r="O9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O9" ca="1">($H9 - _xlfn.STOCKHISTORY($A9, O$1,O$1,0,0,1))/$H9</f>
-        <v>9.9111027047475101E-3</v>
-      </c>
-      <c r="P9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P9" ca="1">(H9 - _xlfn.STOCKHISTORY($A9, P$1,P$1,0,0,1))/$H9</f>
-        <v>3.3364857196898128E-2</v>
-      </c>
-      <c r="Q9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q9" ca="1">($H9 - _xlfn.STOCKHISTORY($A9, Q$1,Q$1,0,0,1))/$H9</f>
-        <v>-1.1689048609797522E-2</v>
-      </c>
-      <c r="R9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R9" ca="1">($H9 - _xlfn.STOCKHISTORY($A9, R$1,R$1,0,0,1))/$H9</f>
-        <v>7.5203328919992513E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
@@ -8590,7 +5521,7 @@
         <v>USD</v>
       </c>
       <c r="J10" s="9">
-        <f ca="1">IF(E10="PUT",IF((H10-F10)&lt;0,(F10-H10)*G10,0),IF((H10-F10)&gt;0,(H10-F10)*G10,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="9">
@@ -8601,28 +5532,28 @@
         <v>0</v>
       </c>
       <c r="M10" s="9">
-        <f>L10*-G10</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N10" s="9">
         <f ca="1">IF(I10="CAD",M10,(M10*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O10" s="2" cm="1">
+      <c r="O10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O10" ca="1">($H10 - _xlfn.STOCKHISTORY($A10, O$1,O$1,0,0,1))/$H10</f>
-        <v>9.9111027047475101E-3</v>
-      </c>
-      <c r="P10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P10" ca="1">(H10 - _xlfn.STOCKHISTORY($A10, P$1,P$1,0,0,1))/$H10</f>
-        <v>3.3364857196898128E-2</v>
-      </c>
-      <c r="Q10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q10" ca="1">($H10 - _xlfn.STOCKHISTORY($A10, Q$1,Q$1,0,0,1))/$H10</f>
-        <v>-1.1689048609797522E-2</v>
-      </c>
-      <c r="R10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R10" ca="1">($H10 - _xlfn.STOCKHISTORY($A10, R$1,R$1,0,0,1))/$H10</f>
-        <v>7.5203328919992513E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -8657,7 +5588,7 @@
         <v>USD</v>
       </c>
       <c r="J11" s="9">
-        <f ca="1">IF(E11="PUT",IF((H11-F11)&lt;0,(F11-H11)*G11,0),IF((H11-F11)&gt;0,(H11-F11)*G11,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="9">
@@ -8668,26 +5599,26 @@
         <v>0</v>
       </c>
       <c r="M11" s="9">
-        <f>L11*-G11</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N11" s="9">
         <f ca="1">IF(I11="CAD",M11,(M11*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O11" s="2" cm="1">
+      <c r="O11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O11" ca="1">($H11 - _xlfn.STOCKHISTORY($A11, O$1,O$1,0,0,1))/$H11</f>
-        <v>5.8955352525426559E-2</v>
-      </c>
-      <c r="P11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P11" ca="1">(H11 - _xlfn.STOCKHISTORY($A11, P$1,P$1,0,0,1))/$H11</f>
-        <v>4.8439924151008368E-2</v>
-      </c>
-      <c r="Q11" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q11" ca="1">($H11 - _xlfn.STOCKHISTORY($A11, Q$1,Q$1,0,0,1))/$H11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R11" s="2" t="e" cm="1" vm="3">
+      <c r="R11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R11" ca="1">($H11 - _xlfn.STOCKHISTORY($A11, R$1,R$1,0,0,1))/$H11</f>
         <v>#VALUE!</v>
       </c>
@@ -8724,7 +5655,7 @@
         <v>USD</v>
       </c>
       <c r="J12" s="9">
-        <f ca="1">IF(E12="PUT",IF((H12-F12)&lt;0,(F12-H12)*G12,0),IF((H12-F12)&gt;0,(H12-F12)*G12,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K12" s="9">
@@ -8735,26 +5666,26 @@
         <v>100</v>
       </c>
       <c r="M12" s="9">
-        <f>L12*-G12</f>
+        <f t="shared" si="1"/>
         <v>400000</v>
       </c>
       <c r="N12" s="9">
         <f ca="1">IF(I12="CAD",M12,(M12*Currency!$B$2))</f>
         <v>547280</v>
       </c>
-      <c r="O12" s="2" cm="1">
+      <c r="O12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O12" ca="1">($H12 - _xlfn.STOCKHISTORY($A12, O$1,O$1,0,0,1))/$H12</f>
-        <v>5.8955352525426559E-2</v>
-      </c>
-      <c r="P12" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P12" ca="1">(H12 - _xlfn.STOCKHISTORY($A12, P$1,P$1,0,0,1))/$H12</f>
-        <v>4.8439924151008368E-2</v>
-      </c>
-      <c r="Q12" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q12" ca="1">($H12 - _xlfn.STOCKHISTORY($A12, Q$1,Q$1,0,0,1))/$H12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R12" s="2" t="e" cm="1" vm="3">
+      <c r="R12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R12" ca="1">($H12 - _xlfn.STOCKHISTORY($A12, R$1,R$1,0,0,1))/$H12</f>
         <v>#VALUE!</v>
       </c>
@@ -8791,7 +5722,7 @@
         <v>USD</v>
       </c>
       <c r="J13" s="9">
-        <f ca="1">IF(E13="PUT",IF((H13-F13)&lt;0,(F13-H13)*G13,0),IF((H13-F13)&gt;0,(H13-F13)*G13,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K13" s="9">
@@ -8802,28 +5733,28 @@
         <v>0</v>
       </c>
       <c r="M13" s="9">
-        <f>L13*-G13</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N13" s="9">
         <f ca="1">IF(I13="CAD",M13,(M13*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O13" s="2" cm="1">
+      <c r="O13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O13" ca="1">($H13 - _xlfn.STOCKHISTORY($A13, O$1,O$1,0,0,1))/$H13</f>
-        <v>7.2423641874563233E-3</v>
-      </c>
-      <c r="P13" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P13" ca="1">(H13 - _xlfn.STOCKHISTORY($A13, P$1,P$1,0,0,1))/$H13</f>
-        <v>-7.8981114478898912E-3</v>
-      </c>
-      <c r="Q13" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q13" ca="1">($H13 - _xlfn.STOCKHISTORY($A13, Q$1,Q$1,0,0,1))/$H13</f>
-        <v>3.8120774073210489E-2</v>
-      </c>
-      <c r="R13" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R13" ca="1">($H13 - _xlfn.STOCKHISTORY($A13, R$1,R$1,0,0,1))/$H13</f>
-        <v>0.10892690603870366</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -8858,7 +5789,7 @@
         <v>USD</v>
       </c>
       <c r="J14" s="9">
-        <f ca="1">IF(E14="PUT",IF((H14-F14)&lt;0,(F14-H14)*G14,0),IF((H14-F14)&gt;0,(H14-F14)*G14,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K14" s="9">
@@ -8869,28 +5800,28 @@
         <v>0</v>
       </c>
       <c r="M14" s="9">
-        <f>L14*-G14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N14" s="9">
         <f ca="1">IF(I14="CAD",M14,(M14*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O14" s="2" cm="1">
+      <c r="O14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O14" ca="1">($H14 - _xlfn.STOCKHISTORY($A14, O$1,O$1,0,0,1))/$H14</f>
-        <v>7.2423641874563233E-3</v>
-      </c>
-      <c r="P14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P14" ca="1">(H14 - _xlfn.STOCKHISTORY($A14, P$1,P$1,0,0,1))/$H14</f>
-        <v>-7.8981114478898912E-3</v>
-      </c>
-      <c r="Q14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q14" ca="1">($H14 - _xlfn.STOCKHISTORY($A14, Q$1,Q$1,0,0,1))/$H14</f>
-        <v>3.8120774073210489E-2</v>
-      </c>
-      <c r="R14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R14" ca="1">($H14 - _xlfn.STOCKHISTORY($A14, R$1,R$1,0,0,1))/$H14</f>
-        <v>0.10892690603870366</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="26" x14ac:dyDescent="0.35">
@@ -8925,7 +5856,7 @@
         <v>CAD</v>
       </c>
       <c r="J15" s="9">
-        <f ca="1">IF(E15="PUT",IF((H15-F15)&lt;0,(F15-H15)*G15,0),IF((H15-F15)&gt;0,(H15-F15)*G15,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>-262.00000000000045</v>
       </c>
       <c r="K15" s="9">
@@ -8936,28 +5867,28 @@
         <v>120</v>
       </c>
       <c r="M15" s="9">
-        <f>L15*-G15</f>
+        <f t="shared" si="1"/>
         <v>12000</v>
       </c>
       <c r="N15" s="9">
         <f ca="1">IF(I15="CAD",M15,(M15*Currency!$B$2))</f>
         <v>12000</v>
       </c>
-      <c r="O15" s="2" cm="1">
+      <c r="O15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O15" ca="1">($H15 - _xlfn.STOCKHISTORY($A15, O$1,O$1,0,0,1))/$H15</f>
-        <v>5.2819901175667943E-3</v>
-      </c>
-      <c r="P15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P15" ca="1">(H15 - _xlfn.STOCKHISTORY($A15, P$1,P$1,0,0,1))/$H15</f>
-        <v>-0.46950076674050106</v>
-      </c>
-      <c r="Q15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q15" ca="1">($H15 - _xlfn.STOCKHISTORY($A15, Q$1,Q$1,0,0,1))/$H15</f>
-        <v>-0.61705571647640156</v>
-      </c>
-      <c r="R15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R15" ca="1">($H15 - _xlfn.STOCKHISTORY($A15, R$1,R$1,0,0,1))/$H15</f>
-        <v>-1.0987391378429034</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -8992,7 +5923,7 @@
         <v>USD</v>
       </c>
       <c r="J16" s="9">
-        <f ca="1">IF(E16="PUT",IF((H16-F16)&lt;0,(F16-H16)*G16,0),IF((H16-F16)&gt;0,(H16-F16)*G16,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K16" s="9">
@@ -9003,26 +5934,26 @@
         <v>0</v>
       </c>
       <c r="M16" s="9">
-        <f>L16*-G16</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N16" s="9">
         <f ca="1">IF(I16="CAD",M16,(M16*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O16" s="2" cm="1">
+      <c r="O16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O16" ca="1">($H16 - _xlfn.STOCKHISTORY($A16, O$1,O$1,0,0,1))/$H16</f>
-        <v>-1.3979383448409998E-2</v>
-      </c>
-      <c r="P16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P16" ca="1">(H16 - _xlfn.STOCKHISTORY($A16, P$1,P$1,0,0,1))/$H16</f>
-        <v>-6.3648740639891094E-2</v>
-      </c>
-      <c r="Q16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q16" ca="1">($H16 - _xlfn.STOCKHISTORY($A16, Q$1,Q$1,0,0,1))/$H16</f>
-        <v>2.4482155013128448E-2</v>
-      </c>
-      <c r="R16" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R16" ca="1">($H16 - _xlfn.STOCKHISTORY($A16, R$1,R$1,0,0,1))/$H16</f>
         <v>#VALUE!</v>
       </c>
@@ -9059,7 +5990,7 @@
         <v>USD</v>
       </c>
       <c r="J17" s="9">
-        <f ca="1">IF(E17="PUT",IF((H17-F17)&lt;0,(F17-H17)*G17,0),IF((H17-F17)&gt;0,(H17-F17)*G17,0))</f>
+        <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
       <c r="K17" s="9">
@@ -9070,26 +6001,26 @@
         <v>0</v>
       </c>
       <c r="M17" s="9">
-        <f>L17*-G17</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N17" s="9">
         <f ca="1">IF(I17="CAD",M17,(M17*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O17" s="2" cm="1">
+      <c r="O17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="O17" ca="1">($H17 - _xlfn.STOCKHISTORY($A17, O$1,O$1,0,0,1))/$H17</f>
-        <v>-1.3979383448409998E-2</v>
-      </c>
-      <c r="P17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="P17" ca="1">(H17 - _xlfn.STOCKHISTORY($A17, P$1,P$1,0,0,1))/$H17</f>
-        <v>-6.3648740639891094E-2</v>
-      </c>
-      <c r="Q17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q17" ca="1">($H17 - _xlfn.STOCKHISTORY($A17, Q$1,Q$1,0,0,1))/$H17</f>
-        <v>2.4482155013128448E-2</v>
-      </c>
-      <c r="R17" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="R17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="R17" ca="1">($H17 - _xlfn.STOCKHISTORY($A17, R$1,R$1,0,0,1))/$H17</f>
         <v>#VALUE!</v>
       </c>
@@ -9192,35 +6123,35 @@
       </c>
       <c r="D1" s="8">
         <f ca="1">WORKDAY(TODAY(),-5)</f>
-        <v>46065</v>
+        <v>46132</v>
       </c>
       <c r="E1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-1),-1)</f>
-        <v>46038</v>
+        <v>46107</v>
       </c>
       <c r="F1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-3),-1)</f>
-        <v>45979</v>
+        <v>46048</v>
       </c>
       <c r="G1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-12),-1)</f>
-        <v>45706</v>
+        <v>45772</v>
       </c>
       <c r="H1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-18),-1)</f>
-        <v>45520</v>
+        <v>45590</v>
       </c>
       <c r="I1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-24),-1)</f>
-        <v>45338</v>
+        <v>45408</v>
       </c>
       <c r="J1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-36),-1)</f>
-        <v>44974</v>
+        <v>45042</v>
       </c>
       <c r="K1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-48),-1)</f>
-        <v>44610</v>
+        <v>44677</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9235,37 +6166,37 @@
         <f t="array" aca="1" ref="C2" ca="1">_FV(A2,"Change (%)",TRUE)</f>
         <v>-9.4930000000000004E-4</v>
       </c>
-      <c r="D2" s="2" cm="1">
+      <c r="D2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, D$1,D$1,0,0,1))/$B2</f>
-        <v>5.4816547288408582E-3</v>
-      </c>
-      <c r="E2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, E$1,E$1,0,0,1))/$B2</f>
-        <v>-1.7029674024265366E-2</v>
-      </c>
-      <c r="F2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, F$1,F$1,0,0,1))/$B2</f>
-        <v>-2.2218973834234747E-2</v>
-      </c>
-      <c r="G2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, G$1,G$1,0,0,1))/$B2</f>
-        <v>-3.7640695804706824E-2</v>
-      </c>
-      <c r="H2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, H$1,H$1,0,0,1))/$B2</f>
-        <v>4.3853237830737896E-4</v>
-      </c>
-      <c r="I2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, I$1,I$1,0,0,1))/$B2</f>
-        <v>1.4471568484139774E-2</v>
-      </c>
-      <c r="J2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, J$1,J$1,0,0,1))/$B2</f>
-        <v>1.5494810700190109E-2</v>
-      </c>
-      <c r="K2" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, K$1,K$1,0,0,1))/$B2</f>
-        <v>6.819178482677983E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -9280,37 +6211,37 @@
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Change (%)",TRUE)</f>
         <v>1.1647000000000001E-2</v>
       </c>
-      <c r="D3" s="2" cm="1">
+      <c r="D3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, D$1,D$1,0,0,1))/$B3</f>
-        <v>1.9296171363343519E-2</v>
-      </c>
-      <c r="E3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, E$1,E$1,0,0,1))/$B3</f>
-        <v>-0.42294222088021294</v>
-      </c>
-      <c r="F3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, F$1,F$1,0,0,1))/$B3</f>
-        <v>-0.37803705188017367</v>
-      </c>
-      <c r="G3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, G$1,G$1,0,0,1))/$B3</f>
-        <v>-0.41643281274661226</v>
-      </c>
-      <c r="H3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, H$1,H$1,0,0,1))/$B3</f>
-        <v>0.11652922579088425</v>
-      </c>
-      <c r="I3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, I$1,I$1,0,0,1))/$B3</f>
-        <v>0.22492497026308134</v>
-      </c>
-      <c r="J3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, J$1,J$1,0,0,1))/$B3</f>
-        <v>0.63512379813442466</v>
-      </c>
-      <c r="K3" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, K$1,K$1,0,0,1))/$B3</f>
-        <v>0.40417215563262171</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -9325,37 +6256,37 @@
         <f t="array" aca="1" ref="C4" ca="1">_FV(A4,"Change (%)",TRUE)</f>
         <v>1.8963000000000001E-2</v>
       </c>
-      <c r="D4" s="2" cm="1">
+      <c r="D4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, D$1,D$1,0,0,1))/$B4</f>
-        <v>2.8217919364376547E-2</v>
-      </c>
-      <c r="E4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, E$1,E$1,0,0,1))/$B4</f>
-        <v>-0.66401318150343958</v>
-      </c>
-      <c r="F4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, F$1,F$1,0,0,1))/$B4</f>
-        <v>-0.56521761105467194</v>
-      </c>
-      <c r="G4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, G$1,G$1,0,0,1))/$B4</f>
-        <v>-0.34023744901517788</v>
-      </c>
-      <c r="H4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, H$1,H$1,0,0,1))/$B4</f>
-        <v>-0.31835251424037042</v>
-      </c>
-      <c r="I4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, I$1,I$1,0,0,1))/$B4</f>
-        <v>-0.41060787554396438</v>
-      </c>
-      <c r="J4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, J$1,J$1,0,0,1))/$B4</f>
-        <v>0.14416258535377277</v>
-      </c>
-      <c r="K4" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, K$1,K$1,0,0,1))/$B4</f>
-        <v>-0.40662006641294296</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -9370,37 +6301,37 @@
         <f t="array" aca="1" ref="C5" ca="1">_FV(A5,"Change (%)",TRUE)</f>
         <v>-1.4139999999999999E-3</v>
       </c>
-      <c r="D5" s="2" cm="1">
+      <c r="D5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, D$1,D$1,0,0,1))/$B5</f>
-        <v>5.9010976041543777E-3</v>
-      </c>
-      <c r="E5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, E$1,E$1,0,0,1))/$B5</f>
-        <v>-1.7349226956213777E-2</v>
-      </c>
-      <c r="F5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, F$1,F$1,0,0,1))/$B5</f>
-        <v>-1.8883512333293877E-2</v>
-      </c>
-      <c r="G5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, G$1,G$1,0,0,1))/$B5</f>
-        <v>-0.1295881033872299</v>
-      </c>
-      <c r="H5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, H$1,H$1,0,0,1))/$B5</f>
-        <v>-7.0105039537353822E-2</v>
-      </c>
-      <c r="I5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, I$1,I$1,0,0,1))/$B5</f>
-        <v>-9.5007671426885279E-2</v>
-      </c>
-      <c r="J5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, J$1,J$1,0,0,1))/$B5</f>
-        <v>-0.10350525197686769</v>
-      </c>
-      <c r="K5" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, K$1,K$1,0,0,1))/$B5</f>
-        <v>-4.2133836893662166E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -9415,37 +6346,37 @@
         <f t="array" aca="1" ref="C6" ca="1">_FV(A6,"Change (%)",TRUE)</f>
         <v>7.1049999999999998E-4</v>
       </c>
-      <c r="D6" s="2" cm="1">
+      <c r="D6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, D$1,D$1,0,0,1))/$B6</f>
-        <v>1.4199961272833002E-2</v>
-      </c>
-      <c r="E6" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, E$1,E$1,0,0,1))/$B6</f>
-        <v>-2.0396308010069041E-2</v>
-      </c>
-      <c r="F6" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, F$1,F$1,0,0,1))/$B6</f>
-        <v>-3.6790808752339326E-3</v>
-      </c>
-      <c r="G6" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, G$1,G$1,0,0,1))/$B6</f>
-        <v>1.8589040211708482E-2</v>
-      </c>
-      <c r="H6" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, H$1,H$1,0,0,1))/$B6</f>
-        <v>4.7440779706964399E-2</v>
-      </c>
-      <c r="I6" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, I$1,I$1,0,0,1))/$B6</f>
-        <v>3.0465371458077834E-2</v>
-      </c>
-      <c r="J6" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, J$1,J$1,0,0,1))/$B6</f>
-        <v>0.13412508874975795</v>
-      </c>
-      <c r="K6" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, K$1,K$1,0,0,1))/$B6</f>
-        <v>0.25772929710191705</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -9460,37 +6391,37 @@
         <f t="array" aca="1" ref="C7" ca="1">_FV(A7,"Change (%)",TRUE)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="2" cm="1">
+      <c r="D7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, D$1,D$1,0,0,1))/$B7</f>
-        <v>1.0133178922988651E-3</v>
-      </c>
-      <c r="E7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, E$1,E$1,0,0,1))/$B7</f>
-        <v>-8.7000579038794684E-3</v>
-      </c>
-      <c r="F7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, F$1,F$1,0,0,1))/$B7</f>
-        <v>-2.8865083960625332E-2</v>
-      </c>
-      <c r="G7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, G$1,G$1,0,0,1))/$B7</f>
-        <v>-5.3647944412275564E-2</v>
-      </c>
-      <c r="H7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, H$1,H$1,0,0,1))/$B7</f>
-        <v>-3.7116386797915353E-2</v>
-      </c>
-      <c r="I7" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, I$1,I$1,0,0,1))/$B7</f>
-        <v>-4.1242038216560431E-2</v>
-      </c>
-      <c r="J7" s="2" t="e" cm="1" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, J$1,J$1,0,0,1))/$B7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="2" cm="1">
+      <c r="K7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, K$1,K$1,0,0,1))/$B7</f>
-        <v>8.4380428488708803E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -9505,37 +6436,37 @@
         <f t="array" aca="1" ref="C8" ca="1">_FV(A8,"Change (%)",TRUE)</f>
         <v>6.4250000000000006E-4</v>
       </c>
-      <c r="D8" s="2" cm="1">
+      <c r="D8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, D$1,D$1,0,0,1))/$B8</f>
-        <v>2.8194823028360847E-3</v>
-      </c>
-      <c r="E8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, E$1,E$1,0,0,1))/$B8</f>
-        <v>1.1273359547968926E-2</v>
-      </c>
-      <c r="F8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, F$1,F$1,0,0,1))/$B8</f>
-        <v>3.2636535829588031E-2</v>
-      </c>
-      <c r="G8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, G$1,G$1,0,0,1))/$B8</f>
-        <v>0.17163655639307332</v>
-      </c>
-      <c r="H8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, H$1,H$1,0,0,1))/$B8</f>
-        <v>0.23085253924769625</v>
-      </c>
-      <c r="I8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, I$1,I$1,0,0,1))/$B8</f>
-        <v>0.29585600076770341</v>
-      </c>
-      <c r="J8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, J$1,J$1,0,0,1))/$B8</f>
-        <v>0.56988728925283716</v>
-      </c>
-      <c r="K8" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, K$1,K$1,0,0,1))/$B8</f>
-        <v>0.68828955215014087</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -9550,37 +6481,37 @@
         <f t="array" aca="1" ref="C9" ca="1">_FV(A9,"Change (%)",TRUE)</f>
         <v>2.9740000000000001E-3</v>
       </c>
-      <c r="D9" s="2" cm="1">
+      <c r="D9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, D$1,D$1,0,0,1))/$B9</f>
-        <v>5.5027733538360671E-3</v>
-      </c>
-      <c r="E9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, E$1,E$1,0,0,1))/$B9</f>
-        <v>3.9870393761326766E-3</v>
-      </c>
-      <c r="F9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, F$1,F$1,0,0,1))/$B9</f>
-        <v>2.7700587621505908E-2</v>
-      </c>
-      <c r="G9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, G$1,G$1,0,0,1))/$B9</f>
-        <v>4.5889395353945824E-2</v>
-      </c>
-      <c r="H9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, H$1,H$1,0,0,1))/$B9</f>
-        <v>7.869734746553908E-2</v>
-      </c>
-      <c r="I9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, I$1,I$1,0,0,1))/$B9</f>
-        <v>8.8220110934153398E-2</v>
-      </c>
-      <c r="J9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, J$1,J$1,0,0,1))/$B9</f>
-        <v>9.1108792355428653E-2</v>
-      </c>
-      <c r="K9" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, K$1,K$1,0,0,1))/$B9</f>
-        <v>0.17985501674995877</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -9595,37 +6526,37 @@
         <f t="array" aca="1" ref="C10" ca="1">_FV(A10,"Change (%)",TRUE)</f>
         <v>7.8949999999999995E-5</v>
       </c>
-      <c r="D10" s="2" cm="1">
+      <c r="D10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, D$1,D$1,0,0,1))/$B10</f>
-        <v>3.9469529523207241E-3</v>
-      </c>
-      <c r="E10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, E$1,E$1,0,0,1))/$B10</f>
-        <v>-1.7287653931165166E-2</v>
-      </c>
-      <c r="F10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, F$1,F$1,0,0,1))/$B10</f>
-        <v>-2.7470792548152958E-2</v>
-      </c>
-      <c r="G10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, G$1,G$1,0,0,1))/$B10</f>
-        <v>-5.8967477107672868E-2</v>
-      </c>
-      <c r="H10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, H$1,H$1,0,0,1))/$B10</f>
-        <v>-3.828544363751183E-2</v>
-      </c>
-      <c r="I10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, I$1,I$1,0,0,1))/$B10</f>
-        <v>-6.236185664666892E-2</v>
-      </c>
-      <c r="J10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, J$1,J$1,0,0,1))/$B10</f>
-        <v>-5.4862646037259329E-2</v>
-      </c>
-      <c r="K10" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, K$1,K$1,0,0,1))/$B10</f>
-        <v>-6.2125039469529519E-2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -9640,37 +6571,37 @@
         <f t="array" aca="1" ref="C11" ca="1">_FV(A11,"Change (%)",TRUE)</f>
         <v>2.5369999999999999E-4</v>
       </c>
-      <c r="D11" s="2" cm="1">
+      <c r="D11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, D$1,D$1,0,0,1))/$B11</f>
-        <v>4.4075213241589039E-3</v>
-      </c>
-      <c r="E11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, E$1,E$1,0,0,1))/$B11</f>
-        <v>-2.2513238418366208E-3</v>
-      </c>
-      <c r="F11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, F$1,F$1,0,0,1))/$B11</f>
-        <v>1.3761613343057283E-2</v>
-      </c>
-      <c r="G11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, G$1,G$1,0,0,1))/$B11</f>
-        <v>-3.7860291086660197E-2</v>
-      </c>
-      <c r="H11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, H$1,H$1,0,0,1))/$B11</f>
-        <v>-1.8866727970320539E-2</v>
-      </c>
-      <c r="I11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, I$1,I$1,0,0,1))/$B11</f>
-        <v>5.9295430763863909E-3</v>
-      </c>
-      <c r="J11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, J$1,J$1,0,0,1))/$B11</f>
-        <v>3.6655357199479939E-2</v>
-      </c>
-      <c r="K11" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, K$1,K$1,0,0,1))/$B11</f>
-        <v>0.11719567492152069</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -9698,37 +6629,37 @@
         <f t="array" aca="1" ref="C14" ca="1">_FV(A14,"Change (%)",TRUE)</f>
         <v>3.8529999999999997E-3</v>
       </c>
-      <c r="D14" s="2" cm="1">
+      <c r="D14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, D$1,D$1,0,0,1))/$B14</f>
-        <v>1.5987909640470997E-2</v>
-      </c>
-      <c r="E14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, E$1,E$1,0,0,1))/$B14</f>
-        <v>8.6183582564428998E-2</v>
-      </c>
-      <c r="F14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, F$1,F$1,0,0,1))/$B14</f>
-        <v>0.19135777919185495</v>
-      </c>
-      <c r="G14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, G$1,G$1,0,0,1))/$B14</f>
-        <v>0.41357779191854915</v>
-      </c>
-      <c r="H14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, H$1,H$1,0,0,1))/$B14</f>
-        <v>0.49534680241807189</v>
-      </c>
-      <c r="I14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, I$1,I$1,0,0,1))/$B14</f>
-        <v>0.59749840916321983</v>
-      </c>
-      <c r="J14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, J$1,J$1,0,0,1))/$B14</f>
-        <v>0.63402799872733062</v>
-      </c>
-      <c r="K14" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, K$1,K$1,0,0,1))/$B14</f>
-        <v>0.62221603563474381</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -9743,37 +6674,37 @@
         <f t="array" aca="1" ref="C15" ca="1">_FV(A15,"Change (%)",TRUE)</f>
         <v>1.5361E-2</v>
       </c>
-      <c r="D15" s="2" cm="1">
+      <c r="D15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, D$1,D$1,0,0,1))/$B15</f>
-        <v>3.9446630283030894E-2</v>
-      </c>
-      <c r="E15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, E$1,E$1,0,0,1))/$B15</f>
-        <v>-0.1237085924609722</v>
-      </c>
-      <c r="F15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, F$1,F$1,0,0,1))/$B15</f>
-        <v>0.35878918644498037</v>
-      </c>
-      <c r="G15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, G$1,G$1,0,0,1))/$B15</f>
-        <v>0.57643101916486872</v>
-      </c>
-      <c r="H15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, H$1,H$1,0,0,1))/$B15</f>
-        <v>0.63384947328341157</v>
-      </c>
-      <c r="I15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, I$1,I$1,0,0,1))/$B15</f>
-        <v>0.702056098489656</v>
-      </c>
-      <c r="J15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, J$1,J$1,0,0,1))/$B15</f>
-        <v>0.72439395862419087</v>
-      </c>
-      <c r="K15" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, K$1,K$1,0,0,1))/$B15</f>
-        <v>0.69549435207513643</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -9788,37 +6719,37 @@
         <f t="array" aca="1" ref="C16" ca="1">_FV(A16,"Change (%)",TRUE)</f>
         <v>-3.029E-3</v>
       </c>
-      <c r="D16" s="2" cm="1">
+      <c r="D16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, D$1,D$1,0,0,1))/$B16</f>
-        <v>4.0256349394730571E-2</v>
-      </c>
-      <c r="E16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, E$1,E$1,0,0,1))/$B16</f>
-        <v>-0.10263470211250882</v>
-      </c>
-      <c r="F16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, F$1,F$1,0,0,1))/$B16</f>
-        <v>0.26171374317588414</v>
-      </c>
-      <c r="G16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, G$1,G$1,0,0,1))/$B16</f>
-        <v>0.52238309992879184</v>
-      </c>
-      <c r="H16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, H$1,H$1,0,0,1))/$B16</f>
-        <v>0.54312841205791595</v>
-      </c>
-      <c r="I16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, I$1,I$1,0,0,1))/$B16</f>
-        <v>0.56634227391407543</v>
-      </c>
-      <c r="J16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, J$1,J$1,0,0,1))/$B16</f>
-        <v>0.56259197721338705</v>
-      </c>
-      <c r="K16" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, K$1,K$1,0,0,1))/$B16</f>
-        <v>0.48882031806313792</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -9833,37 +6764,37 @@
         <f t="array" aca="1" ref="C17" ca="1">_FV(A17,"Change (%)",TRUE)</f>
         <v>6.642000000000001E-4</v>
       </c>
-      <c r="D17" s="2" cm="1">
+      <c r="D17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, D$1,D$1,0,0,1))/$B17</f>
-        <v>-6.770660471291079E-2</v>
-      </c>
-      <c r="E17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="E17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, E$1,E$1,0,0,1))/$B17</f>
-        <v>-2.987056090275483E-2</v>
-      </c>
-      <c r="F17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="F17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, F$1,F$1,0,0,1))/$B17</f>
-        <v>-0.45071357451045491</v>
-      </c>
-      <c r="G17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="G17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, G$1,G$1,0,0,1))/$B17</f>
-        <v>-0.32990375041486886</v>
-      </c>
-      <c r="H17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="H17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, H$1,H$1,0,0,1))/$B17</f>
-        <v>0.29538665781612999</v>
-      </c>
-      <c r="I17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="I17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, I$1,I$1,0,0,1))/$B17</f>
-        <v>0.46598075008297379</v>
-      </c>
-      <c r="J17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="J17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, J$1,J$1,0,0,1))/$B17</f>
-        <v>0.24493859940258877</v>
-      </c>
-      <c r="K17" s="2" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, K$1,K$1,0,0,1))/$B17</f>
-        <v>-0.47062728177895791</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">

--- a/sample_portfolio.xlsx
+++ b/sample_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\chanmainvest\portfolio_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279AE8AC-71BD-48D2-A2D7-5AA98E7BA8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA12500-A770-464C-A34C-547F5CCEFBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57825" yWindow="270" windowWidth="21375" windowHeight="15375" activeTab="1" xr2:uid="{C3C23AD8-DF51-43CD-B973-8860122C8980}"/>
+    <workbookView xWindow="12820" yWindow="160" windowWidth="25470" windowHeight="19440" activeTab="1" xr2:uid="{C3C23AD8-DF51-43CD-B973-8860122C8980}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="37">
+  <futureMetadata name="XLRICHVALUE" count="38">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -298,21 +298,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="89"/>
+          <xlrd:rvb i="87"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="92"/>
+          <xlrd:rvb i="90"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="95"/>
+          <xlrd:rvb i="93"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="96"/>
         </ext>
       </extLst>
     </bk>
@@ -322,7 +329,7 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="37">
+  <valueMetadata count="38">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -433,6 +440,9 @@
     </bk>
     <bk>
       <rc t="2" v="36"/>
+    </bk>
+    <bk>
+      <rc t="2" v="37"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -731,8 +741,535 @@
 </rvTypesInfo>
 </file>
 
+<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="174">
+  <a r="1">
+    <v t="i">0</v>
+  </a>
+  <a r="1">
+    <v>29.76</v>
+  </a>
+  <a r="1">
+    <v>30.202999999999999</v>
+  </a>
+  <a r="1">
+    <v>31.559000000000001</v>
+  </a>
+  <a r="1">
+    <v>31.353000000000002</v>
+  </a>
+  <a r="1">
+    <v>32.158999999999999</v>
+  </a>
+  <a r="1">
+    <v>32.485999999999997</v>
+  </a>
+  <a r="1">
+    <v>30.835999999999999</v>
+  </a>
+  <a r="1">
+    <v>31.35</v>
+  </a>
+  <a r="1">
+    <v>86.3</v>
+  </a>
+  <a r="1">
+    <v>86.28</v>
+  </a>
+  <a r="1">
+    <v>85.56</v>
+  </a>
+  <a r="1">
+    <v>1.2994000000000001</v>
+  </a>
+  <a r="1">
+    <v>1.3402000000000001</v>
+  </a>
+  <a r="1">
+    <v>1.3913</v>
+  </a>
+  <a r="1">
+    <v>1.3458000000000001</v>
+  </a>
+  <a r="1">
+    <v>1.2723</v>
+  </a>
+  <a r="1">
+    <v>1.262</v>
+  </a>
+  <a r="1">
+    <v>1.2682</v>
+  </a>
+  <a r="1">
+    <v>1.3426</v>
+  </a>
+  <a r="1">
+    <v>0.84370000000000001</v>
+  </a>
+  <a r="1">
+    <v>0.84860000000000002</v>
+  </a>
+  <a r="1">
+    <v>0.89570000000000005</v>
+  </a>
+  <a r="1">
+    <v>0.9486</v>
+  </a>
+  <a r="1">
+    <v>0.8488</v>
+  </a>
+  <a r="1">
+    <v>0.9204</v>
+  </a>
+  <a r="1">
+    <v>0.95830000000000004</v>
+  </a>
+  <a r="1">
+    <v>0.92</v>
+  </a>
+  <a r="1">
+    <v>7.2309000000000001</v>
+  </a>
+  <a r="1">
+    <v>6.9080000000000004</v>
+  </a>
+  <a r="1">
+    <v>7.2180999999999997</v>
+  </a>
+  <a r="1">
+    <v>7.2089999999999996</v>
+  </a>
+  <a r="1">
+    <v>6.9786000000000001</v>
+  </a>
+  <a r="1">
+    <v>6.7948000000000004</v>
+  </a>
+  <a r="1">
+    <v>6.7821999999999996</v>
+  </a>
+  <a r="1">
+    <v>6.8208000000000002</v>
+  </a>
+  <a r="1">
+    <v>62.29</v>
+  </a>
+  <a r="1">
+    <v>56.51</v>
+  </a>
+  <a r="1">
+    <v>22.74</v>
+  </a>
+  <a r="1">
+    <v>267.55</v>
+  </a>
+  <a r="1">
+    <v>122.02</v>
+  </a>
+  <a r="1">
+    <v>127.55</v>
+  </a>
+  <a r="1">
+    <v>71.239999999999995</v>
+  </a>
+  <a r="1">
+    <v>78</v>
+  </a>
+  <a r="1">
+    <v>29.3</v>
+  </a>
+  <a r="1">
+    <v>142.1</v>
+  </a>
+  <a r="1">
+    <v>188.15</v>
+  </a>
+  <a r="1">
+    <v>184.74</v>
+  </a>
+  <a r="1">
+    <v>167.43</v>
+  </a>
+  <a r="1">
+    <v>386.77</v>
+  </a>
+  <a r="1">
+    <v>332.77</v>
+  </a>
+  <a r="1">
+    <v>64.37</v>
+  </a>
+  <a r="1">
+    <v>68.28</v>
+  </a>
+  <a r="1">
+    <v>38.020000000000003</v>
+  </a>
+  <a r="1">
+    <v>22.76</v>
+  </a>
+  <a r="1">
+    <v>49.02</v>
+  </a>
+  <a r="1">
+    <v>48.384300000000003</v>
+  </a>
+  <a r="1">
+    <v>135.4</v>
+  </a>
+  <a r="1">
+    <v>219.44</v>
+  </a>
+  <a r="1">
+    <v>198.35</v>
+  </a>
+  <a r="1">
+    <v>39.604999999999997</v>
+  </a>
+  <a r="1">
+    <v>50.07</v>
+  </a>
+  <a r="1">
+    <v>50.06</v>
+  </a>
+  <a r="1">
+    <v>85.49</v>
+  </a>
+  <a r="1">
+    <v>82.263999999999996</v>
+  </a>
+  <a r="1">
+    <v>83.45</v>
+  </a>
+  <a r="1">
+    <v>84.424000000000007</v>
+  </a>
+  <a r="1">
+    <v>77.810500000000005</v>
+  </a>
+  <a r="1">
+    <v>90.759</v>
+  </a>
+  <a r="1">
+    <v>95.31</v>
+  </a>
+  <a r="1">
+    <v>93.025000000000006</v>
+  </a>
+  <a r="1">
+    <v>117.17</v>
+  </a>
+  <a r="1">
+    <v>278.26</v>
+  </a>
+  <a r="1">
+    <v>458.79</v>
+  </a>
+  <a r="1">
+    <v>594.20000000000005</v>
+  </a>
+  <a r="1">
+    <v>701.66</v>
+  </a>
+  <a r="1">
+    <v>739.3</v>
+  </a>
+  <a r="1">
+    <v>29902.25</v>
+  </a>
+  <a r="1">
+    <v>68845.62</v>
+  </a>
+  <a r="1">
+    <v>26957</v>
+  </a>
+  <a r="1">
+    <v>81803.17</v>
+  </a>
+  <a r="1">
+    <v>65282</v>
+  </a>
+  <a r="1">
+    <v>75236.42</v>
+  </a>
+  <a r="1">
+    <v>91750</v>
+  </a>
+  <a r="1">
+    <v>103740.65</v>
+  </a>
+  <a r="1">
+    <v>32.353999999999999</v>
+  </a>
+  <a r="1">
+    <v>78.709999999999994</v>
+  </a>
+  <a r="1">
+    <v>23.893000000000001</v>
+  </a>
+  <a r="1">
+    <v>-99999901</v>
+  </a>
+  <a r="1">
+    <v>85.947999999999993</v>
+  </a>
+  <a r="1">
+    <v>29.664999999999999</v>
+  </a>
+  <a r="1">
+    <v>30.431999999999999</v>
+  </a>
+  <a r="1">
+    <v>21.550999999999998</v>
+  </a>
+  <a r="1">
+    <v>34.418500000000002</v>
+  </a>
+  <a r="1">
+    <v>44.804000000000002</v>
+  </a>
+  <a r="1">
+    <v>45.337499999999999</v>
+  </a>
+  <a r="1">
+    <v>38.852699999999999</v>
+  </a>
+  <a r="1">
+    <v>15.539300000000001</v>
+  </a>
+  <a r="1">
+    <v>19.722899999999999</v>
+  </a>
+  <a r="1">
+    <v>32.271599999999999</v>
+  </a>
+  <a r="1">
+    <v>43.704099999999997</v>
+  </a>
+  <a r="1">
+    <v>990.2</v>
+  </a>
+  <a r="1">
+    <v>2126.3000000000002</v>
+  </a>
+  <a r="1">
+    <v>1066.9000000000001</v>
+  </a>
+  <a r="1">
+    <v>945.1</v>
+  </a>
+  <a r="1">
+    <v>2112.1999999999998</v>
+  </a>
+  <a r="1">
+    <v>925.3</v>
+  </a>
+  <a r="1">
+    <v>1071.3</v>
+  </a>
+  <a r="1">
+    <v>292.68</v>
+  </a>
+  <a r="1">
+    <v>263.39999999999998</v>
+  </a>
+  <a r="1">
+    <v>211.26</v>
+  </a>
+  <a r="1">
+    <v>445</v>
+  </a>
+  <a r="1">
+    <v>349.98</v>
+  </a>
+  <a r="1">
+    <v>388.9</v>
+  </a>
+  <a r="1">
+    <v>20.67</v>
+  </a>
+  <a r="1">
+    <v>19.11</v>
+  </a>
+  <a r="1">
+    <v>4.87</v>
+  </a>
+  <a r="1">
+    <v>108.19</v>
+  </a>
+  <a r="1">
+    <v>151.97999999999999</v>
+  </a>
+  <a r="1">
+    <v>149.68</v>
+  </a>
+  <a r="1">
+    <v>222.68</v>
+  </a>
+  <a r="1">
+    <v>324.98</v>
+  </a>
+  <a r="1">
+    <v>353.66</v>
+  </a>
+  <a r="1">
+    <v>71.72</v>
+  </a>
+  <a r="1">
+    <v>164.96</v>
+  </a>
+  <a r="1">
+    <v>164.54</v>
+  </a>
+  <a r="1">
+    <v>2.3759999999999999</v>
+  </a>
+  <a r="1">
+    <v>7.9560000000000004</v>
+  </a>
+  <a r="1">
+    <v>3.3340000000000001</v>
+  </a>
+  <a r="1">
+    <v>2.823</v>
+  </a>
+  <a r="1">
+    <v>2.4950000000000001</v>
+  </a>
+  <a r="1">
+    <v>2938.11</v>
+  </a>
+  <a r="1">
+    <v>1821.2</v>
+  </a>
+  <a r="1">
+    <v>2350.73</v>
+  </a>
+  <a r="1">
+    <v>2572</v>
+  </a>
+  <a r="1">
+    <v>1998.88</v>
+  </a>
+  <a r="1">
+    <v>2337.61</v>
+  </a>
+  <a r="1">
+    <v>2032.4</v>
+  </a>
+  <a r="1">
+    <v>3091.5</v>
+  </a>
+  <a r="1">
+    <v>59.2</v>
+  </a>
+  <a r="1">
+    <v>46.47</v>
+  </a>
+  <a r="1">
+    <v>42.73</v>
+  </a>
+  <a r="1">
+    <v>1.3676999999999999</v>
+  </a>
+  <a r="1">
+    <v>1.3617999999999999</v>
+  </a>
+  <a r="1">
+    <v>1.3703000000000001</v>
+  </a>
+  <a r="1">
+    <v>1.3965000000000001</v>
+  </a>
+  <a r="1">
+    <v>1.4088000000000001</v>
+  </a>
+  <a r="1">
+    <v>1.3482000000000001</v>
+  </a>
+  <a r="1">
+    <v>1.2843</v>
+  </a>
+  <a r="1">
+    <v>1.3633999999999999</v>
+  </a>
+  <a r="1">
+    <v>196.75</v>
+  </a>
+  <a r="1">
+    <v>109.77</v>
+  </a>
+  <a r="1">
+    <v>198.48</v>
+  </a>
+  <a r="1">
+    <v>4808.3</v>
+  </a>
+  <a r="1">
+    <v>1814</v>
+  </a>
+  <a r="1">
+    <v>2570.1</v>
+  </a>
+  <a r="1">
+    <v>4728.7</v>
+  </a>
+  <a r="1">
+    <v>2385.5</v>
+  </a>
+  <a r="1">
+    <v>3187.2</v>
+  </a>
+  <a r="1">
+    <v>1993</v>
+  </a>
+  <a r="1">
+    <v>19.649999999999999</v>
+  </a>
+  <a r="1">
+    <v>17.670000000000002</v>
+  </a>
+  <a r="1">
+    <v>17.82</v>
+  </a>
+  <a r="1">
+    <v>521.51</v>
+  </a>
+  <a r="1">
+    <v>713.29</v>
+  </a>
+  <a r="1">
+    <v>640.47</v>
+  </a>
+  <a r="1">
+    <v>145.62</v>
+  </a>
+  <a r="1">
+    <v>154.34</v>
+  </a>
+  <a r="1">
+    <v>159.18</v>
+  </a>
+  <a r="1">
+    <v>153.51</v>
+  </a>
+  <a r="1">
+    <v>157.16</v>
+  </a>
+  <a r="1">
+    <v>136.37</v>
+  </a>
+  <a r="1">
+    <v>155.38</v>
+  </a>
+  <a r="1">
+    <v>129.16</v>
+  </a>
+</arrayData>
+</file>
+
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="96">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="273">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23hqh&amp;q=ARCX%3aSPY&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -742,7 +1279,6 @@
     <v>a23hqh</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
     <v>0</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
@@ -750,123 +1286,125 @@
     <v>3</v>
     <v>Finance</v>
     <v>4</v>
-    <v>697.84</v>
-    <v>481.8</v>
-    <v>0.99860000000000004</v>
-    <v>3.39</v>
-    <v>4.9639999999999997E-3</v>
+    <v>749.53</v>
+    <v>575.6</v>
+    <v>0.99870000000000003</v>
+    <v>-9</v>
+    <v>-2.5840000000000004E-3</v>
+    <v>-1.2029000000000001E-2</v>
+    <v>-1.9103000000000001</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
-    <v>8.9999999999999998E-4</v>
-    <v>689.15</v>
+    <v>9.4499999999999998E-4</v>
+    <v>743.46</v>
     <v>ETF</v>
-    <v>46072.041657210153</v>
-    <v>0</v>
-    <v>682.83</v>
-    <v>708919250698.56995</v>
+    <v>46157.999991481251</v>
+    <v>0</v>
+    <v>737.96</v>
+    <v>735060829033.51001</v>
     <v>State Street SPDR S&amp;P500</v>
-    <v>684.02</v>
-    <v>682.85</v>
-    <v>686.24</v>
+    <v>741.79</v>
+    <v>748.17</v>
+    <v>739.17</v>
+    <v>737.25969999999995</v>
     <v>SPY</v>
     <v>State Street SPDR S&amp;P500 (ARCX:SPY)</v>
-    <v>73570341</v>
-    <v>80598035</v>
+    <v>60410771</v>
+    <v>49696080</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
   <rv s="3">
-    <v>9</v>
-    <v>1</v>
+    <v>2</v>
+    <v>4</v>
+    <v>11</v>
   </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a21mim&amp;q=XNAS%3aQQQ&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="1">
     <v>en-CA</v>
     <v>a21mim</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>722.03</v>
+    <v>505.58</v>
+    <v>0.99850000000000005</v>
+    <v>-10.86</v>
+    <v>-3.6820000000000004E-3</v>
+    <v>-1.5087999999999999E-2</v>
+    <v>-2.61</v>
+    <v>USD</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>1.8E-3</v>
+    <v>715.13</v>
+    <v>ETF</v>
+    <v>46157.999997464845</v>
+    <v>4</v>
+    <v>705.55</v>
+    <v>440257379466.70001</v>
+    <v>Invesco QQQ Trust 1</v>
+    <v>710.14</v>
+    <v>719.79</v>
+    <v>708.93</v>
+    <v>706.32</v>
+    <v>QQQ</v>
+    <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
+    <v>51792656</v>
+    <v>39789272</v>
+  </rv>
+  <rv s="2">
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=ab1y3m&amp;q=XTSE%3aXIU&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="4">
+    <v>en-CA</v>
+    <v>ab1y3m</v>
+    <v>268435456</v>
+    <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>5</v>
-    <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
+    <v>iShares S&amp;P/TSX 60 Index ETF (XTSE:XIU)</v>
     <v>2</v>
     <v>6</v>
     <v>Finance</v>
     <v>7</v>
-    <v>637.01</v>
-    <v>402.39</v>
-    <v>0.97619999999999996</v>
-    <v>4.49</v>
-    <v>-5.6130000000000004E-4</v>
-    <v>7.4670000000000005E-3</v>
-    <v>-0.34</v>
-    <v>USD</v>
-    <v>Nasdaq Stock Market</v>
-    <v>XNAS</v>
-    <v>1.8E-3</v>
-    <v>609.77099999999996</v>
-    <v>ETF</v>
-    <v>46072.041605323437</v>
-    <v>4</v>
-    <v>600.72</v>
-    <v>411778069059.48999</v>
-    <v>Invesco QQQ Trust 1</v>
-    <v>602.11</v>
-    <v>601.29999999999995</v>
-    <v>605.79</v>
-    <v>605.45000000000005</v>
-    <v>QQQ</v>
-    <v>Invesco QQQ Trust 1 (XNAS:QQQ)</v>
-    <v>64250668</v>
-    <v>62275053</v>
-  </rv>
-  <rv s="2">
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>https://www.bing.com/financeapi/forcetrigger?t=ab1y3m&amp;q=XTSE%3aXIU&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="5">
-    <v>en-CA</v>
-    <v>ab1y3m</v>
-    <v>268435456</v>
-    <v>1</v>
-    <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>8</v>
-    <v>iShares S&amp;P/TSX 60 Index ETF (XTSE:XIU)</v>
-    <v>2</v>
-    <v>9</v>
-    <v>Finance</v>
-    <v>10</v>
-    <v>49.38</v>
-    <v>33.869999999999997</v>
-    <v>1.0166999999999999</v>
-    <v>0.7</v>
-    <v>1.4469000000000001E-2</v>
+    <v>50.62</v>
+    <v>38.799999999999997</v>
+    <v>0.97809999999999997</v>
+    <v>-0.49</v>
+    <v>-9.7400000000000004E-3</v>
     <v>CAD</v>
     <v>Toronto Stock Exchange</v>
     <v>XTSE</v>
     <v>1.8E-3</v>
-    <v>49.21</v>
+    <v>49.854999999999997</v>
     <v>ETF</v>
-    <v>46071.874988425923</v>
+    <v>46157.833321759259</v>
     <v>7</v>
-    <v>48.56</v>
-    <v>21058987695.360001</v>
+    <v>49.59</v>
+    <v>21964156830.830002</v>
     <v>iShares S&amp;P/TSX 60 Index ETF</v>
-    <v>48.6</v>
-    <v>48.38</v>
-    <v>49.08</v>
+    <v>49.84</v>
+    <v>50.31</v>
+    <v>49.82</v>
     <v>XIU</v>
     <v>iShares S&amp;P/TSX 60 Index ETF (XTSE:XIU)</v>
-    <v>3247918</v>
+    <v>5396586</v>
   </rv>
   <rv s="2">
     <v>8</v>
@@ -875,86 +1413,84 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a24b5r&amp;q=XNAS%3aTLT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="1">
     <v>en-CA</v>
     <v>a24b5r</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>5</v>
+    <v>0</v>
     <v>iShares:20+ Trs Bd ETF (XNAS:TLT)</v>
     <v>2</v>
-    <v>6</v>
+    <v>3</v>
     <v>Finance</v>
-    <v>11</v>
-    <v>94.09</v>
+    <v>4</v>
+    <v>92.185000000000002</v>
     <v>83.295000000000002</v>
-    <v>1.0980000000000001</v>
-    <v>-0.34</v>
-    <v>-1.1169999999999999E-4</v>
-    <v>-3.7830000000000003E-3</v>
-    <v>-0.01</v>
+    <v>1.1047</v>
+    <v>-1.26</v>
+    <v>1.4199999999999998E-3</v>
+    <v>-1.4836999999999999E-2</v>
+    <v>0.1188</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>1.5E-3</v>
-    <v>89.86</v>
+    <v>83.97</v>
     <v>ETF</v>
-    <v>46072.041562245315</v>
+    <v>46157.999903911717</v>
     <v>10</v>
-    <v>89.47</v>
-    <v>45213559490.599998</v>
+    <v>83.59</v>
+    <v>42905041871.43</v>
     <v>iShares:20+ Trs Bd ETF</v>
-    <v>89.685000000000002</v>
-    <v>89.87</v>
-    <v>89.53</v>
-    <v>89.52</v>
+    <v>83.87</v>
+    <v>84.92</v>
+    <v>83.66</v>
+    <v>83.778800000000004</v>
     <v>TLT</v>
     <v>iShares:20+ Trs Bd ETF (XNAS:TLT)</v>
-    <v>35415364</v>
-    <v>40482541</v>
+    <v>50795960</v>
+    <v>21132317</v>
   </rv>
   <rv s="2">
     <v>11</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>en-CA</v>
     <v>cfzfpr</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>8</v>
+    <v>Sprott Active Au &amp; Ag (XNAS:GBUG)</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>12</v>
-    <v>Sprott Active Au &amp; Ag (XNAS:GBUG)</v>
-    <v>13</v>
-    <v>14</v>
+    <v>10</v>
     <v>Finance</v>
-    <v>7</v>
-    <v>57</v>
-    <v>18.39</v>
-    <v>1.0083</v>
-    <v>0</v>
-    <v>2.0320999999999999E-2</v>
+    <v>4</v>
+    <v>59.02</v>
+    <v>23.03</v>
+    <v>-3.2703000000000002</v>
+    <v>0</v>
+    <v>-6.8616999999999997E-2</v>
     <v>0</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>8.8999999999999999E-3</v>
-    <v>51.189900000000002</v>
+    <v>45.62</v>
     <v>ETF</v>
-    <v>46071.885416793753</v>
-    <v>49.91</v>
-    <v>197879529.25</v>
+    <v>46157.888591620314</v>
+    <v>43.820099999999996</v>
+    <v>164232725.78999999</v>
     <v>Sprott Active Au &amp; Ag</v>
-    <v>49.97</v>
-    <v>49.617800000000003</v>
-    <v>50.626100000000001</v>
-    <v>50.626100000000001</v>
+    <v>45.58</v>
+    <v>47.660299999999999</v>
+    <v>44.39</v>
+    <v>44.39</v>
     <v>GBUG</v>
     <v>Sprott Active Au &amp; Ag (XNAS:GBUG)</v>
-    <v>69023</v>
-    <v>182329</v>
+    <v>74227</v>
+    <v>51085</v>
   </rv>
   <rv s="2">
     <v>13</v>
@@ -963,25 +1499,24 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=aay9k2&amp;q=XTSE%3aFNV&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>aay9k2</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>15</v>
+    <v>11</v>
     <v>Franco-Nevada Corporation (XTSE:FNV)</v>
-    <v>16</v>
-    <v>17</v>
+    <v>12</v>
+    <v>13</v>
     <v>Finance</v>
-    <v>18</v>
-    <v>368.63</v>
-    <v>196.16</v>
-    <v>0.83879999999999999</v>
-    <v>7.74</v>
-    <v>0</v>
-    <v>2.2740999999999997E-2</v>
+    <v>14</v>
+    <v>388.22</v>
+    <v>210.19</v>
+    <v>0.88929999999999998</v>
+    <v>-16.649999999999999</v>
+    <v>0</v>
+    <v>-5.0967000000000005E-2</v>
     <v>0</v>
     <v>CAD</v>
     <v>Franco-Nevada Corporation is a Canada-based gold-focused royalty and streaming company. The Company’s segments include precious metals, other mining and energy. The Company’s portfolio is diversified by commodity, geography and asset. Its assets include Candelaria, Antapaccay, Antamina, Condestable, Tocantinzinho, Cerro Moro, Salares Norte, Cascabel (Alpala), Posse (Mara Rosa), CentroGold (Gurupi), Calcatreu, and San Jorge. Its other mining assets include NuevaUnion, Taca Taca, Caserones, Copper World Project, Ring of Fire, Mt Keith, Crawford, Robinson, EaglePicher, Copper World Project, and Milpillas. Its United States assets include Stillwater, Goldstrike, Gold Quarry, Marigold, Bald Mountain, South Arturo, Mesquite, Castle Mountain, Stibnite Gold, Sterling, Granite Creek (Pinson) and Arthur Gold Project. Its Canadian assets include Detour Lake, Sudbury, Hemlo, Brucejack, Macassa (Kirkland Lake), Dublin Gulch (Eagle), Musselwhite, and Timmins West.</v>
@@ -990,25 +1525,25 @@
     <v>XTSE</v>
     <v>XTSE</v>
     <v>199 Bay Street, Suite 2000, P.O. Box 285, Commerce Court Postal Station, TORONTO, ON, M5L 1G9 CA</v>
-    <v>350.6</v>
+    <v>318.06</v>
     <v>Metals &amp; Mining</v>
     <v>Stock</v>
-    <v>46071.875</v>
+    <v>46157.833333333336</v>
     <v>15</v>
-    <v>341.83</v>
-    <v>67105708510</v>
+    <v>306.54000000000002</v>
+    <v>59790990664</v>
     <v>Franco-Nevada Corporation</v>
     <v>Franco-Nevada Corporation</v>
-    <v>344.4</v>
-    <v>52.460700000000003</v>
-    <v>340.36</v>
-    <v>348.1</v>
-    <v>348.1</v>
-    <v>192777100</v>
+    <v>317.76</v>
+    <v>33.079300000000003</v>
+    <v>326.68</v>
+    <v>310.02999999999997</v>
+    <v>310.02999999999997</v>
+    <v>192855500</v>
     <v>FNV</v>
     <v>Franco-Nevada Corporation (XTSE:FNV)</v>
-    <v>326283</v>
-    <v>374520</v>
+    <v>372689</v>
+    <v>342500</v>
     <v>2008</v>
   </rv>
   <rv s="2">
@@ -1018,52 +1553,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=ab1tfr&amp;q=XTSE%3aWPM&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>ab1tfr</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>15</v>
+    <v>11</v>
     <v>Wheaton Precious Metals Corp. (XTSE:WPM)</v>
-    <v>16</v>
-    <v>17</v>
+    <v>12</v>
+    <v>13</v>
     <v>Finance</v>
-    <v>18</v>
-    <v>214.41</v>
-    <v>95.96</v>
-    <v>0.99309999999999998</v>
-    <v>4.42</v>
-    <v>0</v>
-    <v>2.2786000000000001E-2</v>
-    <v>0</v>
+    <v>14</v>
+    <v>226.68</v>
+    <v>105.36</v>
+    <v>1.1519999999999999</v>
+    <v>-11.66</v>
+    <v>4.9059999999999998E-3</v>
+    <v>-6.1031000000000002E-2</v>
+    <v>0.88</v>
     <v>CAD</v>
-    <v>Wheaton Precious Metals Corp. is a Canada-based precious metals streaming company. The Company, through strategic streaming agreements, partners with mining companies to secure a portion of their future precious metal production. The Company has approximately 35 streaming agreements. It also has approximately five royalty agreements. Its portfolio includes a diverse mix of gold, silver, palladium, platinum and cobalt streams from 18 operating mines and 28 development projects. Its operating portfolio includes Antamina, Blackwater, Constancia, Cozamin, Los Filos, Marmato, Neves-Corvo, Penasquito, Salobo, San Dimas, Stillwater &amp; East Boulder, Sudbury, Voisey's Bay, and Zinkgruvan. The Company has also entered into a definitive agreement to acquire the Spring Valley Project located in Nevada, United States of America.</v>
+    <v>Wheaton Precious Metals Corp. is a Canada-based precious metals streaming company. The Company, through strategic streaming agreements, partners with mining companies to secure a portion of their future precious metal production. The Company has approximately 35 streaming agreements. Its segments include Gold, Silver, Palladium, Platinum and Cobalt. Its gold segment includes Salobo, Sudbury, Constancia, San Dimas, Stillwater, Blackwater, Platreef and others. Its Silver segment includes Penasquito, Antamina, Constancia, Blackwater and others. Its Palladium segment includes Stillwater and Platreef. Its Platinum segment includes Marathon and Platreef. Its Cobalt segment includes Voisey's Bay. The Company has also entered into a definitive agreement to acquire the Spring Valley Project located in Nevada, United States of America.</v>
     <v>42</v>
     <v>Toronto Stock Exchange</v>
     <v>XTSE</v>
     <v>XTSE</v>
-    <v>Suite 3500 - 1021 West Hastings St., VANCOUVER, BC, V6E 0C3 CA</v>
-    <v>200.75</v>
+    <v>1021 West Hastings Street Suite 3500, BC, V6E 0C3 CA</v>
+    <v>183.3</v>
     <v>Metals &amp; Mining</v>
     <v>Stock</v>
-    <v>46071.875</v>
+    <v>46157.863032407404</v>
     <v>18</v>
-    <v>196.5</v>
-    <v>90077151360</v>
+    <v>176</v>
+    <v>81465501689</v>
     <v>Wheaton Precious Metals Corp.</v>
     <v>Wheaton Precious Metals Corp.</v>
-    <v>198.22</v>
-    <v>64.691100000000006</v>
-    <v>193.98</v>
-    <v>198.4</v>
-    <v>198.4</v>
-    <v>454017900</v>
+    <v>183.17</v>
+    <v>34.700499999999998</v>
+    <v>191.05</v>
+    <v>179.39</v>
+    <v>180.27</v>
+    <v>454125100</v>
     <v>WPM</v>
     <v>Wheaton Precious Metals Corp. (XTSE:WPM)</v>
-    <v>615955</v>
-    <v>816980</v>
+    <v>699869</v>
+    <v>609360</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -1073,26 +1607,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=aaxdur&amp;q=XTSE%3aCCO&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>aaxdur</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>15</v>
+    <v>11</v>
     <v>CAMECO CORPORATION (XTSE:CCO)</v>
-    <v>16</v>
-    <v>17</v>
+    <v>12</v>
+    <v>13</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>14</v>
     <v>182.72</v>
-    <v>49.75</v>
-    <v>1.0448999999999999</v>
-    <v>5.46</v>
-    <v>0</v>
-    <v>3.5441E-2</v>
-    <v>0</v>
+    <v>70.83</v>
+    <v>1.0066999999999999</v>
+    <v>-6.3</v>
+    <v>2.0069E-2</v>
+    <v>-4.0832E-2</v>
+    <v>2.97</v>
     <v>CAD</v>
     <v>Cameco Corporation is a provider of uranium fuel to generate baseload electricity around the globe. Its segments include uranium, fuel services and Westinghouse. The uranium segment involves the exploration for, mining, milling, purchase and sale of uranium concentrate. The fuel services segment involves the refining, conversion and fabrication of uranium concentrate and the purchase and sale of conversion services. The Westinghouse segment reflects its earnings from this equity-accounted investment. Westinghouse is a nuclear reactor technology original equipment manufacturer and a global provider of products and services to commercial utilities and government agencies. It provides outage and maintenance services, engineering support, instrumentation and controls equipment, plant modification, and components and parts to nuclear reactors. It has two operating mines, Cigar Lake and McArthur River as well as a mill at Key Lake. It also has ownership interests in Global Laser Enrichment.</v>
     <v>2424</v>
@@ -1100,25 +1633,25 @@
     <v>XTSE</v>
     <v>XTSE</v>
     <v>2121 11th St W, SASKATOON, SK, S7M 1J3 CA</v>
-    <v>161.5</v>
+    <v>151.28</v>
     <v>Uranium</v>
     <v>Stock</v>
-    <v>46071.875</v>
+    <v>46157.833333333336</v>
     <v>21</v>
-    <v>155.69999999999999</v>
-    <v>69476224160</v>
+    <v>147.63999999999999</v>
+    <v>64454528670</v>
     <v>CAMECO CORPORATION</v>
     <v>CAMECO CORPORATION</v>
-    <v>156.72</v>
-    <v>117.85039999999999</v>
-    <v>154.06</v>
-    <v>159.52000000000001</v>
-    <v>159.52000000000001</v>
+    <v>151</v>
+    <v>103.3056</v>
+    <v>154.29</v>
+    <v>147.99</v>
+    <v>150.96</v>
     <v>435533000</v>
     <v>CCO</v>
     <v>CAMECO CORPORATION (XTSE:CCO)</v>
-    <v>883405</v>
-    <v>1123750</v>
+    <v>838634</v>
+    <v>970740</v>
     <v>1997</v>
   </rv>
   <rv s="2">
@@ -1128,52 +1661,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a1yv52</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
+    <v>12</v>
     <v>15</v>
-    <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>20</v>
-    <v>212.18989999999999</v>
-    <v>86.62</v>
-    <v>2.3212000000000002</v>
-    <v>3.01</v>
-    <v>-1.064E-4</v>
-    <v>1.6272999999999999E-2</v>
-    <v>-0.02</v>
+    <v>236.54</v>
+    <v>129.16</v>
+    <v>2.2498999999999998</v>
+    <v>-10.42</v>
+    <v>-4.0390000000000001E-3</v>
+    <v>-4.4200999999999997E-2</v>
+    <v>-0.91</v>
     <v>USD</v>
-    <v>NVIDIA Corporation is a full-stack computing infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. The Company’s segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing platforms and artificial intelligence (AI) solutions and software; networking; automotive platforms and autonomous and electric vehicle solutions; Jetson for robotics and other embedded platforms, and DGX Cloud computing services. The Graphics segment includes GeForce GPUs for gaming and PCs, the GeForce NOW game streaming service and related infrastructure, and solutions for gaming platforms; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; virtual GPU software for cloud-based visual and virtual computing; automotive platforms for infotainment systems, and Omniverse Enterprise software for building and operating industrial AI and digital twin applications.</v>
-    <v>36000</v>
+    <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
+    <v>42000</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>190.37</v>
+    <v>231.5</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46072.041641770309</v>
+    <v>46157.999984050781</v>
     <v>24</v>
-    <v>186.76</v>
-    <v>4567914000000</v>
+    <v>224.24</v>
+    <v>5457369819600</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>188.75</v>
-    <v>46.559100000000001</v>
-    <v>184.97</v>
-    <v>187.98</v>
-    <v>187.96</v>
-    <v>24300000000</v>
+    <v>229.76</v>
+    <v>48.093000000000004</v>
+    <v>235.74</v>
+    <v>225.32</v>
+    <v>224.41</v>
+    <v>24220530000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>164749125</v>
-    <v>173287884</v>
+    <v>180977639</v>
+    <v>153023101</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -1183,52 +1715,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1ndww&amp;q=XNAS%3aAMD&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a1ndww</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
+    <v>12</v>
     <v>15</v>
-    <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>20</v>
-    <v>267.07990000000001</v>
-    <v>76.48</v>
-    <v>1.9769000000000001</v>
-    <v>-2.96</v>
-    <v>-5.9960000000000005E-4</v>
-    <v>-1.4576E-2</v>
-    <v>-0.12</v>
+    <v>469.21499999999997</v>
+    <v>107.6671</v>
+    <v>2.4121999999999999</v>
+    <v>-25.6</v>
+    <v>-9.0069999999999994E-3</v>
+    <v>-5.6927000000000005E-2</v>
+    <v>-3.82</v>
     <v>USD</v>
-    <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing, graphics and visualization technologies. Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes artificial intelligence (AI) accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), smart network interface Cards (SmartNICs) and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, GPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, and others.</v>
+    <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
     <v>31000</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2485 Augustine Drive, SANTA CLARA, CA, 95054 US</v>
-    <v>203.2</v>
+    <v>439</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46072.041657383597</v>
+    <v>46157.999999687498</v>
     <v>27</v>
-    <v>195.0001</v>
-    <v>326277849320</v>
+    <v>423.36160000000001</v>
+    <v>691537884100</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
-    <v>198.405</v>
-    <v>76.8386</v>
-    <v>203.08</v>
-    <v>200.12</v>
-    <v>200</v>
-    <v>1630411000</v>
+    <v>433.34</v>
+    <v>149.905</v>
+    <v>449.7</v>
+    <v>424.1</v>
+    <v>420.28</v>
+    <v>1630601000</v>
     <v>AMD</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>35664087</v>
-    <v>42904536</v>
+    <v>29131579</v>
+    <v>44542813</v>
     <v>1969</v>
   </rv>
   <rv s="2">
@@ -1238,52 +1769,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1u3p2&amp;q=XNAS%3aGOOG&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a1u3p2</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>ALPHABET INC. (XNAS:GOOG)</v>
+    <v>12</v>
     <v>15</v>
-    <v>ALPHABET INC. (XNAS:GOOG)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>21</v>
-    <v>350.15</v>
-    <v>142.66</v>
-    <v>1.1095999999999999</v>
-    <v>1.1200000000000001</v>
-    <v>1.1840000000000002E-3</v>
-    <v>3.699E-3</v>
-    <v>0.36</v>
+    <v>399.93</v>
+    <v>163.33000000000001</v>
+    <v>1.2638</v>
+    <v>-3.85</v>
+    <v>-3.356E-3</v>
+    <v>-9.6940000000000012E-3</v>
+    <v>-1.32</v>
     <v>USD</v>
     <v>Alphabet Inc. is a holding company. The Company's segments include Google Services, Google Cloud, and Other Bets. The Google Services segment includes products and services such as ads, Android, Chrome, devices, Google Maps, Google Play, Search, and YouTube. The Google Cloud segment includes infrastructure and platform services, collaboration tools, and other services for enterprise customers. Its Other Bets segment is engaged in the sale of healthcare-related services and Internet services. Its Google Cloud provides enterprise-ready cloud services, including Google Cloud Platform and Google Workspace. Google Cloud Platform provides access to solutions such as artificial intelligence (AI) offerings, including its AI infrastructure, Vertex AI platform, and Gemini for Google Cloud; cybersecurity, and data and analytics. Google Workspace includes cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet.</v>
-    <v>190820</v>
+    <v>194668</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1600 Amphitheatre Parkway, MOUNTAIN VIEW, CA, 94043 US</v>
-    <v>305.91000000000003</v>
+    <v>395.88</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46072.041624501566</v>
+    <v>46157.999899467184</v>
     <v>30</v>
-    <v>301.98</v>
-    <v>3676762180000</v>
+    <v>389.76</v>
+    <v>4765465120000</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
-    <v>302.43200000000002</v>
-    <v>28.1584</v>
-    <v>302.82</v>
-    <v>303.94</v>
-    <v>304.3</v>
-    <v>12097000000</v>
+    <v>393.21499999999997</v>
+    <v>30.3324</v>
+    <v>397.17</v>
+    <v>393.32</v>
+    <v>392</v>
+    <v>12116000000</v>
     <v>GOOG</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>15847701</v>
-    <v>24434945</v>
+    <v>15801942</v>
+    <v>17823401</v>
     <v>2015</v>
   </rv>
   <rv s="2">
@@ -1293,52 +1823,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a269ec&amp;q=XNYS%3aXOM&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a269ec</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>EXXON MOBIL CORPORATION (XNYS:XOM)</v>
+    <v>12</v>
     <v>15</v>
-    <v>EXXON MOBIL CORPORATION (XNYS:XOM)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>20</v>
-    <v>156.93</v>
-    <v>97.8</v>
-    <v>0.35360000000000003</v>
-    <v>4.49</v>
-    <v>1.6259999999999998E-3</v>
-    <v>3.0713000000000001E-2</v>
-    <v>0.245</v>
+    <v>176.41</v>
+    <v>101.185</v>
+    <v>0.18360000000000001</v>
+    <v>6.17</v>
+    <v>-3.388E-4</v>
+    <v>4.0659000000000001E-2</v>
+    <v>-5.3499999999999999E-2</v>
     <v>USD</v>
     <v>Exxon Mobil Corporation is an energy provider and chemical manufacturer. The Company’s principal business involves exploration for, and production of, crude oil and natural gas; the manufacture, trade, transport and sale of crude oil, natural gas, petroleum products, petrochemicals and a wide variety of specialty products; and pursuit of lower-emission and other new business opportunities, including carbon capture and storage, hydrogen, lower-emission fuels, Proxxima systems, carbon materials, and lithium. Its Upstream segment explores for and produces crude oil and natural gas. The Energy Products, Chemical Products, and Specialty Products segments manufacture and sell petroleum products and petrochemicals. Energy Products segment includes fuels, aromatics, and catalysts and licensing. Chemical Products segment consists of olefins, polyolefins, and intermediates. Specialty Products segment includes finished lubricants, basestocks and waxes, synthetics, and elastomers and resins.</v>
-    <v>61000</v>
+    <v>58000</v>
     <v>New York Stock Exchange</v>
     <v>XNYS</v>
     <v>XNYS</v>
     <v>22777 SPRINGWOODS VILLAGE PARKWAY, SPRING, TX, 77389-1425 US</v>
-    <v>150.97999999999999</v>
+    <v>158</v>
     <v>Oil &amp; Gas</v>
     <v>Stock</v>
-    <v>46072.041644120312</v>
+    <v>46157.999833760936</v>
     <v>33</v>
-    <v>147.61000000000001</v>
-    <v>629691720000</v>
+    <v>153</v>
+    <v>654570030240</v>
     <v>EXXON MOBIL CORPORATION</v>
     <v>EXXON MOBIL CORPORATION</v>
-    <v>148.15</v>
-    <v>22.506900000000002</v>
-    <v>146.19</v>
-    <v>150.68</v>
-    <v>150.92500000000001</v>
-    <v>4179000000</v>
+    <v>153.75</v>
+    <v>25.6692</v>
+    <v>151.75</v>
+    <v>157.91999999999999</v>
+    <v>157.8665</v>
+    <v>4144947000</v>
     <v>XOM</v>
     <v>EXXON MOBIL CORPORATION (XNYS:XOM)</v>
-    <v>19849670</v>
-    <v>21641066</v>
+    <v>27882407</v>
+    <v>16888131</v>
     <v>1882</v>
   </rv>
   <rv s="2">
@@ -1348,135 +1877,132 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1qlz2&amp;q=XNYS%3aCVX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a1qlz2</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>CHEVRON CORPORATION (XNYS:CVX)</v>
+    <v>12</v>
     <v>15</v>
-    <v>CHEVRON CORPORATION (XNYS:CVX)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>20</v>
-    <v>186.52</v>
-    <v>132.04</v>
-    <v>0.66679999999999995</v>
-    <v>3.32</v>
-    <v>7.0699999999999995E-4</v>
-    <v>1.8388000000000002E-2</v>
-    <v>0.13</v>
+    <v>214.71</v>
+    <v>133.77000000000001</v>
+    <v>0.4965</v>
+    <v>4.46</v>
+    <v>-1.5179999999999998E-3</v>
+    <v>2.3896000000000001E-2</v>
+    <v>-0.28999999999999998</v>
     <v>USD</v>
     <v>Chevron Corporation is an integrated energy company. The Company produces crude oil and natural gas; manufactures transportation fuels, lubricants, petrochemicals and additives; and develops technologies that enhance its business and industry. The Company’s segments include Upstream and Downstream. Upstream operations consist primarily of exploring for, developing, producing and transporting crude oil and natural gas; liquefaction, transportation and regasification associated with LNG; transporting crude oil by major international oil export pipelines; processing, transporting, storage and marketing of natural gas; carbon capture and storage; and a gas-to-liquids plant. Downstream operations consist primarily of the refining of crude oil into petroleum products; marketing crude oil, refined products, and lubricants; manufacturing and marketing of renewable fuels, and transporting of crude oil and refined products by pipeline, marine vessel, motor equipment and rail car.</v>
-    <v>45298</v>
+    <v>43039</v>
     <v>New York Stock Exchange</v>
     <v>XNYS</v>
     <v>XNYS</v>
     <v>1400 SMITH STREET, HOUSTON, TX, 77002 US</v>
-    <v>183.92</v>
+    <v>191.5</v>
     <v>Oil &amp; Gas</v>
     <v>Stock</v>
-    <v>46072.041327812498</v>
+    <v>46157.999713078127</v>
     <v>36</v>
-    <v>181.98</v>
-    <v>364062600000</v>
+    <v>187.9</v>
+    <v>380594377800</v>
     <v>CHEVRON CORPORATION</v>
     <v>CHEVRON CORPORATION</v>
-    <v>183.23</v>
-    <v>27.658000000000001</v>
-    <v>180.55</v>
-    <v>183.87</v>
-    <v>184</v>
-    <v>1980000000</v>
+    <v>188.6</v>
+    <v>32.400500000000001</v>
+    <v>186.64</v>
+    <v>191.1</v>
+    <v>190.81</v>
+    <v>1991598000</v>
     <v>CVX</v>
     <v>CHEVRON CORPORATION (XNYS:CVX)</v>
-    <v>10313434</v>
-    <v>11635510</v>
+    <v>11210811</v>
+    <v>9983000</v>
     <v>1926</v>
   </rv>
   <rv s="2">
     <v>37</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>en-CA</v>
     <v>cc5pdm</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>8</v>
+    <v>iShares Bitcoin Trust (XNAS:IBIT)</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>12</v>
-    <v>iShares Bitcoin Trust (XNAS:IBIT)</v>
-    <v>13</v>
-    <v>14</v>
+    <v>10</v>
     <v>Finance</v>
-    <v>7</v>
+    <v>4</v>
     <v>71.819999999999993</v>
     <v>35.299999999999997</v>
-    <v>-0.85</v>
-    <v>3.189E-3</v>
-    <v>-2.2141000000000001E-2</v>
-    <v>0.1197</v>
+    <v>-1.35</v>
+    <v>-4.462E-4</v>
+    <v>-2.9239999999999999E-2</v>
+    <v>-0.02</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>2.5000000000000001E-3</v>
-    <v>38.75</v>
+    <v>45.33</v>
     <v>ETF</v>
-    <v>46072.041638726565</v>
-    <v>37.299999999999997</v>
-    <v>64803765803.980003</v>
+    <v>46157.999885277342</v>
+    <v>44.5</v>
+    <v>61891578535.07</v>
     <v>iShares Bitcoin Trust</v>
-    <v>38</v>
-    <v>38.39</v>
-    <v>37.54</v>
-    <v>37.659700000000001</v>
+    <v>45.32</v>
+    <v>46.17</v>
+    <v>44.82</v>
+    <v>44.8</v>
     <v>IBIT</v>
     <v>iShares Bitcoin Trust (XNAS:IBIT)</v>
-    <v>50091290</v>
-    <v>81560942</v>
+    <v>39817920</v>
+    <v>39288740</v>
   </rv>
   <rv s="2">
     <v>39</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>en-CA</v>
     <v>ce8mrw</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>8</v>
+    <v>iShares Ethereum Trust (XNAS:ETHA)</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>12</v>
-    <v>iShares Ethereum Trust (XNAS:ETHA)</v>
-    <v>13</v>
-    <v>14</v>
+    <v>10</v>
     <v>Finance</v>
-    <v>11</v>
+    <v>4</v>
     <v>36.799999999999997</v>
-    <v>10.99</v>
-    <v>-0.42</v>
-    <v>8.8859999999999998E-3</v>
-    <v>-2.7907000000000001E-2</v>
-    <v>0.13</v>
+    <v>13.62</v>
+    <v>-0.6</v>
+    <v>0</v>
+    <v>-3.4562000000000002E-2</v>
+    <v>0</v>
     <v>USD</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
-    <v>1.1999999999999999E-3</v>
-    <v>15.19</v>
+    <v>2.3E-3</v>
+    <v>16.97</v>
     <v>ETF</v>
-    <v>46072.041543622654</v>
-    <v>14.52</v>
-    <v>9144441799.9599991</v>
+    <v>46157.999833668749</v>
+    <v>16.63</v>
+    <v>7115884479.9899998</v>
     <v>iShares Ethereum Trust</v>
-    <v>14.835000000000001</v>
-    <v>15.05</v>
-    <v>14.63</v>
-    <v>14.76</v>
+    <v>16.96</v>
+    <v>17.36</v>
+    <v>16.760000000000002</v>
+    <v>16.760000000000002</v>
     <v>ETHA</v>
     <v>iShares Ethereum Trust (XNAS:ETHA)</v>
-    <v>33189928</v>
-    <v>50289476</v>
+    <v>23810489</v>
+    <v>24604273</v>
   </rv>
   <rv s="2">
     <v>41</v>
@@ -1485,52 +2011,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1sp52&amp;q=XNYS%3aFCX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a1sp52</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>FREEPORT-MCMORAN INC. (XNYS:FCX)</v>
+    <v>12</v>
     <v>15</v>
-    <v>FREEPORT-MCMORAN INC. (XNYS:FCX)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>21</v>
-    <v>69.44</v>
-    <v>27.66</v>
-    <v>1.4279999999999999</v>
-    <v>1.46</v>
-    <v>-2.8779999999999999E-3</v>
-    <v>2.3899E-2</v>
-    <v>-0.18</v>
+    <v>70.965000000000003</v>
+    <v>35.15</v>
+    <v>1.3285</v>
+    <v>-3.13</v>
+    <v>4.7609999999999997E-4</v>
+    <v>-4.7324000000000005E-2</v>
+    <v>0.03</v>
     <v>USD</v>
-    <v>Freeport-McMoRan Inc. is an international metals company focused on copper. The Company operates geographically diverse assets with significant proven and probable mineral reserves of copper, gold and molybdenum. The Company's segments include the Morenci and Cerro Verde copper mines, the Indonesia operations (including the Grasberg minerals district and PT-FI’s downstream processing facilities), the Rod &amp; Refining operations and Atlantic Copper Smelting &amp; Refining. Its operations include North America, South America and Indonesia. In North America, it manages seven copper operations: Morenci, Bagdad, Safford (including Lone Star), Sierrita and Miami in Arizona, and Chino and Tyrone in New Mexico, and two molybdenum mines: Henderson and Climax in Colorado. It also operates a copper smelter in Miami, Arizona. In South America, it manages two copper operations: Cerro Verde in Peru and El Abra in Chile. In addition to copper, the Grasberg minerals district also produces gold and silver.</v>
+    <v>Freeport-McMoRan Inc. is a metals company. The Company operates assets with reserves of copper, gold and molybdenum. Its portfolio of assets includes the Grasberg minerals district in Indonesia, which is a copper and gold deposit; and operations in the United States, including the large-scale Morenci minerals district in North America and the Cerro Verde operation in South America. Its segments include Cerro Verde copper mine, Indonesia operations and United States Rod &amp; Refining operations. It produces copper concentrate, cathode and continuous cast copper rod. Its copper ore from mines is processed by smelting and refining or by solution extraction and electrowinning (SX/EW). It produces copper cathodes at an electrolytic refinery located in El Paso, Texas. The SX/EW cathode is produced from the Morenci, Bagdad, Safford, Sierrita, Miami, Chino and Tyrone mines in the United States, and from the Cerro Verde and El Abra mines in South America.</v>
     <v>29000</v>
     <v>New York Stock Exchange</v>
     <v>XNYS</v>
     <v>XNYS</v>
     <v>333 N Central Ave, PHOENIX, AZ, 85004 US</v>
-    <v>63.18</v>
+    <v>63.805</v>
     <v>Metals &amp; Mining</v>
     <v>Stock</v>
-    <v>46072.041372950778</v>
+    <v>46157.999993564059</v>
     <v>43</v>
-    <v>61.55</v>
-    <v>89896985100</v>
+    <v>61.38</v>
+    <v>90580655600</v>
     <v>FREEPORT-MCMORAN INC.</v>
     <v>FREEPORT-MCMORAN INC.</v>
-    <v>62.76</v>
-    <v>40.957000000000001</v>
-    <v>61.09</v>
-    <v>62.55</v>
-    <v>62.37</v>
-    <v>1437202000</v>
+    <v>62.19</v>
+    <v>35.018799999999999</v>
+    <v>66.14</v>
+    <v>63.01</v>
+    <v>63.04</v>
+    <v>1437560000</v>
     <v>FCX</v>
     <v>FREEPORT-MCMORAN INC. (XNYS:FCX)</v>
-    <v>17244815</v>
-    <v>23186437</v>
+    <v>15462565</v>
+    <v>15824397</v>
     <v>1987</v>
   </rv>
   <rv s="2">
@@ -1540,52 +2065,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1upz2&amp;q=XNYS%3aHL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a1upz2</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>HECLA MINING COMPANY (XNYS:HL)</v>
+    <v>12</v>
     <v>15</v>
-    <v>HECLA MINING COMPANY (XNYS:HL)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>20</v>
     <v>34.17</v>
-    <v>4.46</v>
-    <v>1.254</v>
-    <v>0.78</v>
-    <v>-9.0829999999999991E-4</v>
-    <v>3.6722999999999999E-2</v>
-    <v>-0.02</v>
+    <v>4.8150000000000004</v>
+    <v>1.2696000000000001</v>
+    <v>-1.81</v>
+    <v>-5.6689999999999996E-4</v>
+    <v>-9.3058999999999989E-2</v>
+    <v>-0.01</v>
     <v>USD</v>
-    <v>Hecla Mining Company is a silver producer in the United States and Canada. The Company discovers, acquires and develops mines and other mineral interests and produces and markets concentrates containing silver, gold, lead, zinc and copper; carbon material containing silver and gold, and unrefined dore containing silver and gold. The Company's segments include Greens Creek, Lucky Friday, Keno Hill and Casa Berardi. The Greens Creek operation is located on Admiralty Island, near Juneau, Alaska. The Greens Creek ore body contains silver, zinc, gold and lead. The Lucky Friday mine is a deep underground silver, lead, and zinc mine located in the Coeur d’Alene Mining District in northern Idaho. The Casa Berardi mine is an underground/open-pit gold mine located in western Quebec. It owns 100% of the Keno Hill Silver Project, which is located within the Keno Hill Silver District in Canada’s Yukon Territory. The Company also owns a number of exploration and pre-development projects.</v>
-    <v>1830</v>
+    <v>Hecla Mining Company is a silver producer in the United States and Canada. It discovers, acquires and develops mines and other mineral interests and produces and markets concentrates containing silver, gold, lead, zinc and copper; carbon material containing silver and gold, and unrefined dore containing silver and gold. Its segments include Greens Creek, Lucky Friday, Keno Hill and Casa Berardi. Greens Creek operation is located on Admiralty Island, near Juneau, Alaska. Greens Creek property includes over 440 unpatented lode mining claims, 58 unpatented millsite claims, 21 patented lode claims and one patented millsite. Lucky Friday mine is a deep underground silver, lead, and zinc mine located in the Coeur d’Alene Mining District in northern Idaho. Keno Hill Silver Project is located within the Keno Hill Silver District in Canada’s Yukon Territory, which comprises over 242 square kilometers with numerous mineral deposits. It owns a number of exploration and pre-development projects.</v>
+    <v>1865</v>
     <v>New York Stock Exchange</v>
     <v>XNYS</v>
     <v>XNYS</v>
     <v>NONE, 6500 N MINERAL DRIVE SUITE 200, COEUR D'ALENE, ID, 83815-9408 US</v>
-    <v>23.53</v>
+    <v>18.399999999999999</v>
     <v>Metals &amp; Mining</v>
     <v>Stock</v>
-    <v>46072.041411133592</v>
+    <v>46157.999835312497</v>
     <v>46</v>
-    <v>21.9</v>
-    <v>14761102596</v>
+    <v>17.535</v>
+    <v>11831366736</v>
     <v>HECLA MINING COMPANY</v>
     <v>HECLA MINING COMPANY</v>
-    <v>23.12</v>
-    <v>45.023299999999999</v>
-    <v>21.24</v>
-    <v>22.02</v>
-    <v>22</v>
-    <v>670098700</v>
+    <v>18.3</v>
+    <v>28.6417</v>
+    <v>19.45</v>
+    <v>17.64</v>
+    <v>17.63</v>
+    <v>670712400</v>
     <v>HL</v>
     <v>HECLA MINING COMPANY (XNYS:HL)</v>
-    <v>27865282</v>
-    <v>29492436</v>
+    <v>15505491</v>
+    <v>13247251</v>
     <v>2006</v>
   </rv>
   <rv s="2">
@@ -1595,45 +2119,44 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a233ur&amp;q=ARCX%3aSLV&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="1">
     <v>en-CA</v>
     <v>a233ur</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>5</v>
+    <v>0</v>
     <v>IShares:Silver Trust (ARCX:SLV)</v>
     <v>2</v>
-    <v>6</v>
+    <v>3</v>
     <v>Finance</v>
-    <v>11</v>
+    <v>4</v>
     <v>109.83</v>
-    <v>26.57</v>
-    <v>1.7767999999999999</v>
-    <v>3.72</v>
-    <v>-1.0525E-2</v>
-    <v>5.6048999999999995E-2</v>
-    <v>-0.73770000000000002</v>
+    <v>29.305</v>
+    <v>1.3998999999999999</v>
+    <v>-6.47</v>
+    <v>-4.0560000000000006E-3</v>
+    <v>-8.568400000000001E-2</v>
+    <v>-0.28000000000000003</v>
     <v>USD</v>
     <v>NYSE Arca</v>
     <v>ARCX</v>
     <v>5.0000000000000001E-3</v>
-    <v>70.97</v>
+    <v>70.06</v>
     <v>ETF</v>
-    <v>46072.041667777346</v>
+    <v>46157.999996666404</v>
     <v>49</v>
-    <v>69.069999999999993</v>
-    <v>51481949150.650002</v>
+    <v>68.545000000000002</v>
+    <v>35607910524.279999</v>
     <v>IShares:Silver Trust</v>
-    <v>69.66</v>
-    <v>66.37</v>
-    <v>70.09</v>
-    <v>69.3523</v>
+    <v>69.739999999999995</v>
+    <v>75.510000000000005</v>
+    <v>69.040000000000006</v>
+    <v>68.760000000000005</v>
     <v>SLV</v>
     <v>IShares:Silver Trust (ARCX:SLV)</v>
-    <v>63749363</v>
-    <v>160900950</v>
+    <v>45770126</v>
+    <v>23707068</v>
   </rv>
   <rv s="2">
     <v>50</v>
@@ -1642,52 +2165,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1mou2&amp;q=XNAS%3aAAPL&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a1mou2</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>APPLE INC. (XNAS:AAPL)</v>
+    <v>12</v>
     <v>15</v>
-    <v>APPLE INC. (XNAS:AAPL)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>20</v>
-    <v>288.62</v>
-    <v>169.21010000000001</v>
-    <v>1.1012999999999999</v>
-    <v>0.47</v>
-    <v>-3.9719999999999998E-3</v>
-    <v>1.781E-3</v>
-    <v>-1.05</v>
+    <v>303.2</v>
+    <v>193.46</v>
+    <v>1.0724</v>
+    <v>2.02</v>
+    <v>-1.5319999999999999E-3</v>
+    <v>6.7739999999999996E-3</v>
+    <v>-0.46</v>
     <v>USD</v>
-    <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, and Wearables, Home and Accessories. Its software platforms include iOS, iPadOS, macOS, watchOS, visionOS, and tvOS. Its services include advertising, AppleCare, cloud services, digital content and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
+    <v>Apple Inc. designs, manufactures and markets smartphones, personal computers, tablets, wearables and accessories, and sells a variety of related services. Its product categories include iPhone, Mac, iPad, Wearables, Home and Accessories. Its services include advertising, AppleCare, cloud services, digital content, and payment services. The Company operates various platforms, including the App Store, that allow customers to discover and download applications and digital content, such as books, music, video, games and podcasts. It also offers digital content through subscription-based services, including Apple Arcade, Apple Fitness+, Apple Music, Apple News+, and Apple TV+. Its wearables include smartwatches, wireless headphones, and spatial computers. Its products include iPhone 16 Pro, iPhone 16, iPhone 15, iPhone 14, iPhone SE, MacBook Air, MacBook Pro, iMac, Mac mini, Mac Studio, Mac Pro, iPad Pro, iPad Air, AirPods, AirPods Pro, AirPods Max, Apple TV, Apple Vision Pro and others.</v>
     <v>166000</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Apple Park Way, CUPERTINO, CA, 95014 US</v>
-    <v>266.82</v>
+    <v>303.2</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46072.041537013283</v>
+    <v>46157.999824964842</v>
     <v>52</v>
-    <v>262.45</v>
-    <v>3886658745000</v>
+    <v>296.52</v>
+    <v>4409586092800</v>
     <v>APPLE INC.</v>
     <v>APPLE INC.</v>
-    <v>263.60000000000002</v>
-    <v>33.584899999999998</v>
-    <v>263.88</v>
-    <v>264.35000000000002</v>
-    <v>263.3</v>
-    <v>14702700000</v>
+    <v>297.89999999999998</v>
+    <v>36.217700000000001</v>
+    <v>298.20999999999998</v>
+    <v>300.23</v>
+    <v>299.77</v>
+    <v>14687360000</v>
     <v>AAPL</v>
     <v>APPLE INC. (XNAS:AAPL)</v>
-    <v>34203337</v>
-    <v>56980282</v>
+    <v>54862836</v>
+    <v>47348428</v>
     <v>1977</v>
   </rv>
   <rv s="2">
@@ -1697,52 +2219,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1zfec&amp;q=XNAS%3aPAAS&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a1zfec</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>15</v>
+    <v>11</v>
     <v>Pan American Silver Corp. (XNYS:PAAS)</v>
+    <v>12</v>
+    <v>17</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>22</v>
-    <v>Finance</v>
-    <v>20</v>
     <v>69.989999999999995</v>
-    <v>20.55</v>
-    <v>1.2342</v>
-    <v>1.92</v>
-    <v>1.3617999999999998E-2</v>
-    <v>3.4230999999999998E-2</v>
-    <v>0.79</v>
+    <v>22.69</v>
+    <v>1.4866999999999999</v>
+    <v>-4.6900000000000004</v>
+    <v>1.7480000000000002E-3</v>
+    <v>-7.6772000000000007E-2</v>
+    <v>9.8599999999999993E-2</v>
     <v>USD</v>
     <v>Pan American Silver Corp. is a producer of silver and gold in the Americas, operating mines in Canada, Mexico, Peru, Brazil, Bolivia, Chile and Argentina. It owns a 100% interest in the Escobal mine in Guatemala, and it holds interests in exploration and development projects. Its segments include Silver, Gold and Other. Silver segment includes operations of La Colorada, Huaron, San Vicente, Cerro Moro, La Colorada Skarn, Navidad and Escobal. Gold segment includes operations in Dolores, Shahuindo, Timmins, Jacobina, El Penon and Minera Florida. La Colorada mine produces silver-rich lead and zinc concentrates from a flotation plant treating sulfide ore. Huaron mine produces silver-rich zinc, lead and copper concentrates using floatation technology. It owns 44% joint venture interest in the Juanicipio silver mine in Zacatecas, Mexico, operated by Fresnillo plc, along with 100% ownership of the Larder exploration project and a 100% earn-in interest in the Deer Trail exploration project.</v>
-    <v>9000</v>
+    <v>9348</v>
     <v>New York Stock Exchange</v>
     <v>XNYS</v>
     <v>XNYS</v>
-    <v>2100-733 Seymour Street, VANCOUVER, BC, V6B 0S6 CA</v>
-    <v>58.38</v>
+    <v>2100 - 733 Seymour Street, BC, V6B 0S6 CA</v>
+    <v>58.22</v>
     <v>Metals &amp; Mining</v>
     <v>Stock</v>
-    <v>46072.041549085159</v>
+    <v>46157.999149085153</v>
     <v>55</v>
-    <v>56.5</v>
+    <v>55.825000000000003</v>
     <v>32779090000</v>
     <v>Pan American Silver Corp.</v>
     <v>Pan American Silver Corp.</v>
-    <v>57.33</v>
-    <v>33.548699999999997</v>
-    <v>56.09</v>
-    <v>58.01</v>
-    <v>58.8</v>
-    <v>421976000</v>
+    <v>58.12</v>
+    <v>19.587299999999999</v>
+    <v>61.09</v>
+    <v>56.4</v>
+    <v>56.498600000000003</v>
+    <v>421350000</v>
     <v>PAAS</v>
     <v>Pan American Silver Corp. (XNYS:PAAS)</v>
-    <v>7545664</v>
-    <v>10012884</v>
+    <v>7443910</v>
+    <v>4773525</v>
     <v>1979</v>
   </rv>
   <rv s="2">
@@ -1752,52 +2273,51 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=ab1ic7&amp;q=XTSE%3aTRI&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>ab1ic7</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>15</v>
+    <v>11</v>
     <v>THOMSON REUTERS CORPORATION (XTSE:TRI)</v>
-    <v>16</v>
-    <v>17</v>
+    <v>12</v>
+    <v>13</v>
     <v>Finance</v>
-    <v>18</v>
+    <v>14</v>
     <v>299.24</v>
-    <v>112.145</v>
-    <v>0.21290000000000001</v>
-    <v>3.9</v>
-    <v>0</v>
-    <v>3.4367000000000002E-2</v>
+    <v>107.91</v>
+    <v>0.2069</v>
+    <v>5.45</v>
+    <v>0</v>
+    <v>5.0179999999999995E-2</v>
     <v>0</v>
     <v>CAD</v>
     <v>Thomson Reuters Corporation is a content and technology company. The Legal Professionals segment serves law firms and governments with research and workflow products powered by technologies, including generative artificial intelligence (AI). The Corporates segment serves corporations ranging from small businesses to multinational organizations with a full suite of content-driven products, powered by technologies, including generative AI. The Tax &amp; Accounting Professionals segment serves tax, audit and accounting firms with research and workflow products powered by technologies, including generative AI. The Reuters News segment supplies business, financial and global news and data to media organizations, professionals and news consumers through Reuters News Agency, Reuters.com, Reuters Events, Thomson Reuters products and to financial firms exclusively via LSEG products. The Global Print segment provides legal and tax information and commercial printing services.</v>
-    <v>26400</v>
+    <v>27100</v>
     <v>Toronto Stock Exchange</v>
     <v>XTSE</v>
     <v>XTSE</v>
-    <v>19 Duncan Street, TORONTO, ON, M5H 3H1 CA</v>
-    <v>118.41</v>
+    <v>19 Duncan Street, ON, M5H 3H1 CA</v>
+    <v>114.11</v>
     <v>Professional &amp; Commercial Services</v>
     <v>Stock</v>
-    <v>46071.875</v>
+    <v>46157.833333333336</v>
     <v>58</v>
-    <v>112.7</v>
-    <v>52234100000</v>
+    <v>109</v>
+    <v>49791615528</v>
     <v>THOMSON REUTERS CORPORATION</v>
     <v>THOMSON REUTERS CORPORATION</v>
-    <v>114.04</v>
-    <v>26.0016</v>
-    <v>113.48</v>
-    <v>117.38</v>
-    <v>117.38</v>
-    <v>445000000</v>
+    <v>109.4</v>
+    <v>22.830300000000001</v>
+    <v>108.61</v>
+    <v>114.06</v>
+    <v>114.06</v>
+    <v>436538800</v>
     <v>TRI</v>
     <v>THOMSON REUTERS CORPORATION (XTSE:TRI)</v>
-    <v>507358</v>
-    <v>1530930</v>
+    <v>845291</v>
+    <v>771390</v>
     <v>2010</v>
   </rv>
   <rv s="2">
@@ -1807,26 +2327,25 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a24kar&amp;q=XNAS%3aTSLA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="6">
     <v>en-CA</v>
     <v>a24kar</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
+    <v>11</v>
+    <v>TESLA, INC. (XNAS:TSLA)</v>
+    <v>12</v>
     <v>15</v>
-    <v>TESLA, INC. (XNAS:TSLA)</v>
+    <v>Finance</v>
     <v>16</v>
-    <v>19</v>
-    <v>Finance</v>
-    <v>20</v>
     <v>498.83</v>
-    <v>214.25</v>
-    <v>1.8932</v>
-    <v>0.69</v>
-    <v>-2.5409999999999999E-3</v>
-    <v>1.6800000000000001E-3</v>
-    <v>-1.0449999999999999</v>
+    <v>273.20999999999998</v>
+    <v>1.7948</v>
+    <v>-21.06</v>
+    <v>-8.6920000000000001E-3</v>
+    <v>-4.7507000000000001E-2</v>
+    <v>-3.67</v>
     <v>USD</v>
     <v>Tesla, Inc. designs, develops, manufactures, sells and leases high-performance fully electric vehicles and energy generation and storage systems, and offers services related to its products. Its segments include automotive, and energy generation and storage. The automotive segment includes the design, development, manufacturing, sales and leasing of high-performance fully electric vehicles, and sales of automotive regulatory credits. It also includes sales of used vehicles, non-warranty maintenance services and collisions, part sales, paid supercharging, insurance services revenue and retail merchandise sales. The energy generation and storage segment include the design, manufacture, installation, sales and leasing of solar energy generation and energy storage products and related services and sales of solar energy systems incentives. Its consumer vehicles include the Model 3, Y, S, X and Cybertruck. Its lithium-ion battery energy storage products include Powerwall and Megapack.</v>
     <v>134785</v>
@@ -1834,351 +2353,344 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1 Tesla Road, AUSTIN, TX, 78725 US</v>
-    <v>416.9</v>
+    <v>434.66</v>
     <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
-    <v>46072.041665578123</v>
+    <v>46157.999991585159</v>
     <v>61</v>
-    <v>409.58</v>
-    <v>1543450330240</v>
+    <v>422</v>
+    <v>1585816901760</v>
     <v>TESLA, INC.</v>
     <v>TESLA, INC.</v>
-    <v>411.11</v>
-    <v>382.48090000000002</v>
-    <v>410.63</v>
-    <v>411.32</v>
-    <v>410.27499999999998</v>
-    <v>3752432000</v>
+    <v>433.98</v>
+    <v>405.18799999999999</v>
+    <v>443.3</v>
+    <v>422.24</v>
+    <v>418.57</v>
+    <v>3755724000</v>
     <v>TSLA</v>
     <v>TESLA, INC. (XNAS:TSLA)</v>
-    <v>45921402</v>
-    <v>60932674</v>
+    <v>52688742</v>
+    <v>63172495</v>
     <v>2024</v>
   </rv>
   <rv s="2">
     <v>62</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>avylur</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>USD/CAD</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>23</v>
-    <v>USD/CAD</v>
-    <v>13</v>
-    <v>24</v>
+    <v>19</v>
     <v>Finance</v>
-    <v>25</v>
-    <v>1.4542999999999999</v>
+    <v>20</v>
+    <v>1.4139999999999999</v>
     <v>1.3479000000000001</v>
-    <v>-1.2999999999999999E-3</v>
-    <v>-9.4930000000000004E-4</v>
+    <v>1E-4</v>
+    <v>7.2730000000000003E-5</v>
     <v>CAD</v>
     <v>USD</v>
-    <v>1.3704000000000001</v>
+    <v>1.3763000000000001</v>
     <v>Currency Pair</v>
-    <v>46072.34003472222</v>
-    <v>1.3677999999999999</v>
+    <v>46160.19903935185</v>
+    <v>1.3744000000000001</v>
     <v>US Dollar/Canadian Dollar FX Spot Rate</v>
-    <v>1.3694</v>
-    <v>1.3694999999999999</v>
-    <v>1.3682000000000001</v>
+    <v>1.3745000000000001</v>
+    <v>1.3749</v>
+    <v>1.375</v>
     <v>USDCAD</v>
     <v>USD/CAD</v>
   </rv>
   <rv s="2">
     <v>64</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>bo8l6h</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>BTC/USD</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>23</v>
-    <v>BTC/USD</v>
-    <v>13</v>
-    <v>26</v>
+    <v>21</v>
     <v>Finance</v>
-    <v>25</v>
+    <v>20</v>
     <v>126223.18</v>
     <v>60008.52</v>
-    <v>772.49</v>
-    <v>1.1647000000000001E-2</v>
+    <v>-1282.5899999999999</v>
+    <v>-1.6389000000000001E-2</v>
     <v>USD</v>
     <v>BTC</v>
-    <v>67300.070000000007</v>
+    <v>78426.87</v>
     <v>Currency Pair</v>
-    <v>46072.340069444443</v>
-    <v>66213.289999999994</v>
+    <v>46160.198946759258</v>
+    <v>76673.289999999994</v>
     <v>Bitcoin/US Dollar FX Spot Rate</v>
-    <v>66323.77</v>
-    <v>66324.240000000005</v>
-    <v>67096.73</v>
+    <v>78231.570000000007</v>
+    <v>78258.48</v>
+    <v>76975.89</v>
     <v>BTCUSD</v>
     <v>BTC/USD</v>
   </rv>
   <rv s="2">
     <v>66</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>brjcfr</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>ETH/USD</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>23</v>
-    <v>ETH/USD</v>
-    <v>13</v>
-    <v>26</v>
+    <v>21</v>
     <v>Finance</v>
-    <v>25</v>
+    <v>20</v>
     <v>4955.1400000000003</v>
-    <v>1387.02</v>
-    <v>36.82</v>
-    <v>1.8963000000000001E-2</v>
+    <v>1751.94</v>
+    <v>-65.650000000000006</v>
+    <v>-2.9996999999999999E-2</v>
     <v>USD</v>
     <v>ETH</v>
-    <v>1986.91</v>
+    <v>2193.46</v>
     <v>Currency Pair</v>
-    <v>46072.340104166666</v>
-    <v>1939.05</v>
+    <v>46160.198981481481</v>
+    <v>2104.3200000000002</v>
     <v>Ether/US Dollar FX Spot Rate</v>
-    <v>1941.71</v>
-    <v>1941.71</v>
-    <v>1978.53</v>
+    <v>2187.77</v>
+    <v>2188.54</v>
+    <v>2122.89</v>
     <v>ETHUSD</v>
     <v>ETH/USD</v>
   </rv>
   <rv s="2">
     <v>68</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>avyn9c</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>USD/EUR</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>23</v>
-    <v>USD/EUR</v>
-    <v>13</v>
-    <v>27</v>
+    <v>22</v>
     <v>Finance</v>
-    <v>25</v>
-    <v>0.96519999999999995</v>
+    <v>20</v>
+    <v>0.90210000000000001</v>
     <v>0.82779999999999998</v>
-    <v>-1.1999999999999999E-3</v>
-    <v>-1.4139999999999999E-3</v>
+    <v>2.0000000000000001E-4</v>
+    <v>2.3249999999999999E-4</v>
     <v>EUR</v>
     <v>USD</v>
-    <v>0.84850000000000003</v>
+    <v>0.86140000000000005</v>
     <v>Currency Pair</v>
-    <v>46072.340069444443</v>
-    <v>0.84719999999999995</v>
+    <v>46160.199074074073</v>
+    <v>0.86009999999999998</v>
     <v>US Dollar/Euro FX Cross Rate</v>
-    <v>0.84850000000000003</v>
-    <v>0.84850000000000003</v>
-    <v>0.84730000000000005</v>
+    <v>0.85960000000000003</v>
+    <v>0.86009999999999998</v>
+    <v>0.86029999999999995</v>
     <v>USDEUR</v>
     <v>USD/EUR</v>
   </rv>
   <rv s="2">
     <v>70</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>avyomw</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>USD/JPY</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
     <v>23</v>
-    <v>USD/JPY</v>
-    <v>13</v>
-    <v>28</v>
     <v>Finance</v>
-    <v>25</v>
-    <v>159.44999999999999</v>
-    <v>139.86000000000001</v>
-    <v>0.11</v>
-    <v>7.1049999999999998E-4</v>
+    <v>20</v>
+    <v>160.72</v>
+    <v>142.1</v>
+    <v>0.19</v>
+    <v>1.1969999999999999E-3</v>
     <v>JPY</v>
     <v>USD</v>
-    <v>155.34</v>
+    <v>159.07</v>
     <v>Currency Pair</v>
-    <v>46072.340104166666</v>
-    <v>154.63</v>
+    <v>46160.19902777778</v>
+    <v>158.57</v>
     <v>US Dollar/Japanese Yen FX Spot Rate</v>
-    <v>154.78</v>
-    <v>154.82</v>
-    <v>154.93</v>
+    <v>158.51</v>
+    <v>158.76</v>
+    <v>158.94999999999999</v>
     <v>USDJPY</v>
     <v>USD/JPY</v>
   </rv>
   <rv s="2">
     <v>72</v>
   </rv>
-  <rv s="9">
+  <rv s="7">
     <v>en-CA</v>
     <v>avym77</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>USD/CNY</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>29</v>
-    <v>USD/CNY</v>
-    <v>13</v>
-    <v>30</v>
+    <v>24</v>
     <v>Finance</v>
-    <v>25</v>
-    <v>7.3509000000000002</v>
-    <v>6.8998999999999997</v>
-    <v>0</v>
-    <v>0</v>
+    <v>20</v>
+    <v>7.2251000000000003</v>
+    <v>6.7847</v>
+    <v>4.4000000000000003E-3</v>
+    <v>6.4619999999999999E-4</v>
     <v>CNY</v>
     <v>USD</v>
+    <v>6.8190999999999997</v>
     <v>Currency Pair</v>
-    <v>46066.396585648145</v>
+    <v>46160.198958333334</v>
+    <v>6.8141999999999996</v>
     <v>US Dollar/Chinese Renminbi FX Spot Rate</v>
-    <v>6.9080000000000004</v>
-    <v>6.9080000000000004</v>
+    <v>6.8140000000000001</v>
+    <v>6.8091999999999997</v>
+    <v>6.8136000000000001</v>
     <v>USDCNY</v>
     <v>USD/CNY</v>
   </rv>
   <rv s="2">
     <v>74</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>avytp2</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>USD/TRY</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>23</v>
-    <v>USD/TRY</v>
-    <v>13</v>
-    <v>31</v>
+    <v>25</v>
     <v>Finance</v>
-    <v>25</v>
-    <v>43.774299999999997</v>
-    <v>35.819600000000001</v>
-    <v>2.81E-2</v>
-    <v>6.4250000000000006E-4</v>
+    <v>20</v>
+    <v>45.579799999999999</v>
+    <v>38.473999999999997</v>
+    <v>8.3000000000000004E-2</v>
+    <v>1.825E-3</v>
     <v>TRY</v>
     <v>USD</v>
-    <v>43.774299999999997</v>
+    <v>45.579799999999999</v>
     <v>Currency Pair</v>
-    <v>46072.340069444443</v>
-    <v>43.706000000000003</v>
+    <v>46160.198865740742</v>
+    <v>45.527500000000003</v>
     <v>US Dollar/Turkish Lira FX Spot Rate</v>
-    <v>43.743600000000001</v>
-    <v>43.738799999999998</v>
-    <v>43.7669</v>
+    <v>45.373699999999999</v>
+    <v>45.490099999999998</v>
+    <v>45.573099999999997</v>
     <v>USDTRY</v>
     <v>USD/TRY</v>
   </rv>
   <rv s="2">
     <v>76</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>avyo8m</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>USD/INR</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>23</v>
-    <v>USD/INR</v>
-    <v>13</v>
-    <v>32</v>
+    <v>26</v>
     <v>Finance</v>
-    <v>25</v>
-    <v>92.212999999999994</v>
-    <v>83.76</v>
-    <v>0.27</v>
-    <v>2.9740000000000001E-3</v>
+    <v>20</v>
+    <v>96.24</v>
+    <v>84.625</v>
+    <v>0.25</v>
+    <v>2.6050000000000001E-3</v>
     <v>INR</v>
     <v>USD</v>
-    <v>91.203999999999994</v>
+    <v>96.24</v>
     <v>Currency Pair</v>
-    <v>46072.339942129627</v>
-    <v>90.71</v>
+    <v>46160.19902777778</v>
+    <v>96.125</v>
     <v>US Dollar/Indian Rupee FX Spot Rate</v>
-    <v>90.763000000000005</v>
-    <v>90.775000000000006</v>
-    <v>91.045000000000002</v>
+    <v>96.165000000000006</v>
+    <v>95.96</v>
+    <v>96.21</v>
     <v>USDINR</v>
     <v>USD/INR</v>
   </rv>
   <rv s="2">
     <v>78</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>avyspr</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>USD/SGD</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>23</v>
-    <v>USD/SGD</v>
-    <v>13</v>
-    <v>33</v>
+    <v>27</v>
     <v>Finance</v>
-    <v>25</v>
-    <v>1.355</v>
+    <v>20</v>
+    <v>1.3096000000000001</v>
     <v>1.2582</v>
-    <v>1E-4</v>
-    <v>7.8949999999999995E-5</v>
+    <v>4.0000000000000002E-4</v>
+    <v>3.1250000000000001E-4</v>
     <v>SGD</v>
     <v>USD</v>
-    <v>1.2682</v>
+    <v>1.282</v>
     <v>Currency Pair</v>
-    <v>46072.340046296296</v>
-    <v>1.2665</v>
+    <v>46160.198981481481</v>
+    <v>1.2803</v>
     <v>US Dollar/Singapore Dollar FX Spot Rate</v>
-    <v>1.2665999999999999</v>
-    <v>1.2666999999999999</v>
-    <v>1.2667999999999999</v>
+    <v>1.2787999999999999</v>
+    <v>1.2801</v>
+    <v>1.2805</v>
     <v>USDSGD</v>
     <v>USD/SGD</v>
   </rv>
   <rv s="2">
     <v>80</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-CA</v>
     <v>avytar</v>
     <v>268435456</v>
     <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>18</v>
+    <v>USD/TWD</v>
     <v>9</v>
-    <v>Powered by Refinitiv</v>
-    <v>23</v>
-    <v>USD/TWD</v>
-    <v>13</v>
-    <v>34</v>
+    <v>28</v>
     <v>Finance</v>
-    <v>25</v>
-    <v>33.295000000000002</v>
+    <v>20</v>
+    <v>32.185000000000002</v>
     <v>28.734000000000002</v>
-    <v>8.0000000000000002E-3</v>
-    <v>2.5369999999999999E-4</v>
+    <v>6.0999999999999999E-2</v>
+    <v>1.933E-3</v>
     <v>TWD</v>
     <v>USD</v>
-    <v>31.564</v>
+    <v>31.667000000000002</v>
     <v>Currency Pair</v>
-    <v>46072.339953703704</v>
-    <v>31.5</v>
+    <v>46160.199050925927</v>
+    <v>31.559000000000001</v>
     <v>US Dollar/Taiwan Dollar FX Spot Rate</v>
-    <v>31.529</v>
-    <v>31.529</v>
-    <v>31.536999999999999</v>
+    <v>31.568000000000001</v>
+    <v>31.561</v>
+    <v>31.622</v>
     <v>USDTWD</v>
     <v>USD/TWD</v>
   </rv>
@@ -2189,30 +2701,29 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=auvwoc&amp;q=Gold&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="8">
     <v>en-CA</v>
     <v>auvwoc</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>35</v>
+    <v>29</v>
     <v>Gold</v>
     <v>2</v>
-    <v>36</v>
+    <v>30</v>
     <v>Finance</v>
     <v>Metal</v>
-    <v>19.3</v>
-    <v>3.8529999999999997E-3</v>
+    <v>-17.399999999999999</v>
+    <v>-3.8140000000000001E-3</v>
     <v>US</v>
     <v>USD</v>
     <v>43830</v>
     <v>Future</v>
-    <v>46072.333126654688</v>
+    <v>46160.192092870311</v>
     <v>84</v>
     <v>12</v>
     <v>Gold</v>
-    <v>5028.8</v>
+    <v>4544.5</v>
     <v>@GC0Y</v>
     <v>OZS</v>
     <v>Gold</v>
@@ -2221,113 +2732,2579 @@
   <rv s="2">
     <v>85</v>
   </rv>
+  <rv s="9">
+    <fb t="e">#N/A</fb>
+    <v>6</v>
+    <v>4</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=auvwr7&amp;q=Silver&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="8">
     <v>en-CA</v>
     <v>auvwr7</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>35</v>
+    <v>29</v>
     <v>Silver</v>
     <v>2</v>
-    <v>36</v>
+    <v>30</v>
     <v>Finance</v>
     <v>Metal</v>
-    <v>1.1919999999999999</v>
-    <v>1.5361E-2</v>
+    <v>-1.7170000000000001</v>
+    <v>-2.2141000000000001E-2</v>
     <v>US</v>
     <v>USD</v>
     <v>43830</v>
     <v>Future</v>
-    <v>46072.332874895314</v>
-    <v>87</v>
+    <v>46160.191801782028</v>
+    <v>88</v>
     <v>12</v>
     <v>Silver</v>
-    <v>78.790000000000006</v>
+    <v>75.83</v>
     <v>@SI0Y</v>
     <v>OZS</v>
     <v>Silver</v>
     <v>2019</v>
   </rv>
   <rv s="2">
-    <v>88</v>
+    <v>89</v>
   </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=auvwu2&amp;q=Platinum&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="8">
     <v>en-CA</v>
     <v>auvwu2</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>35</v>
+    <v>29</v>
     <v>Platinum</v>
     <v>2</v>
-    <v>36</v>
+    <v>30</v>
     <v>Finance</v>
     <v>Metal</v>
-    <v>-6.4</v>
-    <v>-3.029E-3</v>
+    <v>-17.7</v>
+    <v>-8.8859999999999998E-3</v>
     <v>US</v>
     <v>USD</v>
     <v>43861</v>
     <v>Future</v>
-    <v>46072.333164941403</v>
-    <v>90</v>
+    <v>46160.191763135939</v>
+    <v>91</v>
     <v>1</v>
     <v>Platinum</v>
-    <v>2106.5</v>
+    <v>1974.1</v>
     <v>@PL0Y</v>
     <v>OZS</v>
     <v>Platinum</v>
     <v>2020</v>
   </rv>
   <rv s="2">
-    <v>91</v>
+    <v>92</v>
   </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=auvx6h&amp;q=Natural+Gas&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="10">
+  <rv s="8">
     <v>en-CA</v>
     <v>auvx6h</v>
     <v>268435456</v>
     <v>1</v>
-    <v>9</v>
     <v>Powered by Refinitiv</v>
-    <v>35</v>
+    <v>29</v>
     <v>Natural Gas</v>
     <v>2</v>
-    <v>36</v>
+    <v>30</v>
     <v>Finance</v>
     <v>Energy</v>
-    <v>2E-3</v>
-    <v>6.642000000000001E-4</v>
+    <v>7.0999999999999994E-2</v>
+    <v>2.3986E-2</v>
     <v>US</v>
     <v>USD</v>
     <v>43799</v>
     <v>Future</v>
-    <v>46072.332689178125</v>
-    <v>93</v>
+    <v>46160.192094003905</v>
+    <v>94</v>
     <v>11</v>
     <v>Natural Gas</v>
-    <v>3.0129999999999999</v>
+    <v>3.0310000000000001</v>
     <v>@NG0Y</v>
     <v>MMBTU</v>
     <v>Natural Gas</v>
     <v>2019</v>
   </rv>
   <rv s="2">
+    <v>95</v>
+  </rv>
+  <rv s="10">
+    <v>31</v>
+    <v>avytar</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764002658969,0</v>
+    <v>0</v>
+    <v>avytar</v>
+    <v>USDTWD</v>
+    <v>1</v>
+  </rv>
+  <rv s="10">
+    <v>31</v>
+    <v>avytar</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764003736444,0</v>
+    <v>0</v>
+    <v>avytar</v>
+    <v>USDTWD</v>
+    <v>2</v>
+  </rv>
+  <rv s="10">
+    <v>31</v>
+    <v>avytar</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764006522357,0</v>
+    <v>0</v>
+    <v>avytar</v>
+    <v>USDTWD</v>
+    <v>3</v>
+  </rv>
+  <rv s="10">
+    <v>31</v>
+    <v>avytar</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764007786431,0</v>
+    <v>0</v>
+    <v>avytar</v>
+    <v>USDTWD</v>
+    <v>4</v>
+  </rv>
+  <rv s="10">
+    <v>31</v>
+    <v>avytar</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764002977560,0</v>
+    <v>0</v>
+    <v>avytar</v>
+    <v>USDTWD</v>
+    <v>5</v>
+  </rv>
+  <rv s="10">
+    <v>31</v>
+    <v>avytar</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764007169520,0</v>
+    <v>0</v>
+    <v>avytar</v>
+    <v>USDTWD</v>
+    <v>6</v>
+  </rv>
+  <rv s="10">
+    <v>31</v>
+    <v>avytar</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764008115369,0</v>
+    <v>0</v>
+    <v>avytar</v>
+    <v>USDTWD</v>
+    <v>7</v>
+  </rv>
+  <rv s="10">
+    <v>31</v>
+    <v>avytar</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764006870832,0</v>
+    <v>0</v>
+    <v>avytar</v>
+    <v>USDTWD</v>
+    <v>8</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a24b5r</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004885258,0</v>
+    <v>0</v>
+    <v>a24b5r</v>
+    <v>XNAS:TLT</v>
+    <v>9</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a24b5r</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764002827301,0</v>
+    <v>0</v>
+    <v>a24b5r</v>
+    <v>XNAS:TLT</v>
+    <v>10</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a24b5r</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004121618,0</v>
+    <v>0</v>
+    <v>a24b5r</v>
+    <v>XNAS:TLT</v>
+    <v>11</v>
+  </rv>
+  <rv s="10">
+    <v>33</v>
+    <v>avyspr</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764003413817,0</v>
+    <v>0</v>
+    <v>avyspr</v>
+    <v>USDSGD</v>
+    <v>12</v>
+  </rv>
+  <rv s="10">
+    <v>33</v>
+    <v>avyspr</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764006431569,0</v>
+    <v>0</v>
+    <v>avyspr</v>
+    <v>USDSGD</v>
+    <v>13</v>
+  </rv>
+  <rv s="10">
+    <v>33</v>
+    <v>avyspr</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764007107581,0</v>
+    <v>0</v>
+    <v>avyspr</v>
+    <v>USDSGD</v>
+    <v>14</v>
+  </rv>
+  <rv s="10">
+    <v>33</v>
+    <v>avyspr</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764005932746,0</v>
+    <v>0</v>
+    <v>avyspr</v>
+    <v>USDSGD</v>
+    <v>15</v>
+  </rv>
+  <rv s="10">
+    <v>33</v>
+    <v>avyspr</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003510917,0</v>
+    <v>0</v>
+    <v>avyspr</v>
+    <v>USDSGD</v>
+    <v>16</v>
+  </rv>
+  <rv s="10">
+    <v>33</v>
+    <v>avyspr</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764007814478,0</v>
+    <v>0</v>
+    <v>avyspr</v>
+    <v>USDSGD</v>
+    <v>17</v>
+  </rv>
+  <rv s="10">
+    <v>33</v>
+    <v>avyspr</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764008202758,0</v>
+    <v>0</v>
+    <v>avyspr</v>
+    <v>USDSGD</v>
+    <v>18</v>
+  </rv>
+  <rv s="10">
+    <v>33</v>
+    <v>avyspr</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764006029864,0</v>
+    <v>0</v>
+    <v>avyspr</v>
+    <v>USDSGD</v>
+    <v>19</v>
+  </rv>
+  <rv s="10">
+    <v>34</v>
+    <v>avyn9c</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764003158760,0</v>
+    <v>0</v>
+    <v>avyn9c</v>
+    <v>USDEUR</v>
+    <v>20</v>
+  </rv>
+  <rv s="10">
+    <v>34</v>
+    <v>avyn9c</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004263915,0</v>
+    <v>0</v>
+    <v>avyn9c</v>
+    <v>USDEUR</v>
+    <v>21</v>
+  </rv>
+  <rv s="10">
+    <v>34</v>
+    <v>avyn9c</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004234042,0</v>
+    <v>0</v>
+    <v>avyn9c</v>
+    <v>USDEUR</v>
+    <v>22</v>
+  </rv>
+  <rv s="10">
+    <v>34</v>
+    <v>avyn9c</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764008116986,0</v>
+    <v>0</v>
+    <v>avyn9c</v>
+    <v>USDEUR</v>
+    <v>23</v>
+  </rv>
+  <rv s="10">
+    <v>34</v>
+    <v>avyn9c</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764006693238,0</v>
+    <v>0</v>
+    <v>avyn9c</v>
+    <v>USDEUR</v>
+    <v>24</v>
+  </rv>
+  <rv s="10">
+    <v>34</v>
+    <v>avyn9c</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764008296197,0</v>
+    <v>0</v>
+    <v>avyn9c</v>
+    <v>USDEUR</v>
+    <v>25</v>
+  </rv>
+  <rv s="10">
+    <v>34</v>
+    <v>avyn9c</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764006394550,0</v>
+    <v>0</v>
+    <v>avyn9c</v>
+    <v>USDEUR</v>
+    <v>26</v>
+  </rv>
+  <rv s="10">
+    <v>34</v>
+    <v>avyn9c</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764004706165,0</v>
+    <v>0</v>
+    <v>avyn9c</v>
+    <v>USDEUR</v>
+    <v>27</v>
+  </rv>
+  <rv s="10">
+    <v>35</v>
+    <v>avym77</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764002907876,0</v>
+    <v>0</v>
+    <v>avym77</v>
+    <v>USDCNY</v>
+    <v>28</v>
+  </rv>
+  <rv s="10">
+    <v>35</v>
+    <v>avym77</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764004212493,0</v>
+    <v>0</v>
+    <v>avym77</v>
+    <v>USDCNY</v>
+    <v>29</v>
+  </rv>
+  <rv s="10">
+    <v>35</v>
+    <v>avym77</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764004032929,0</v>
+    <v>0</v>
+    <v>avym77</v>
+    <v>USDCNY</v>
+    <v>30</v>
+  </rv>
+  <rv s="10">
+    <v>35</v>
+    <v>avym77</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764007727075,0</v>
+    <v>0</v>
+    <v>avym77</v>
+    <v>USDCNY</v>
+    <v>31</v>
+  </rv>
+  <rv s="10">
+    <v>35</v>
+    <v>avym77</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764007290834,0</v>
+    <v>0</v>
+    <v>avym77</v>
+    <v>USDCNY</v>
+    <v>32</v>
+  </rv>
+  <rv s="10">
+    <v>35</v>
+    <v>avym77</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764003694765,0</v>
+    <v>0</v>
+    <v>avym77</v>
+    <v>USDCNY</v>
+    <v>33</v>
+  </rv>
+  <rv s="10">
+    <v>35</v>
+    <v>avym77</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764007639303,0</v>
+    <v>0</v>
+    <v>avym77</v>
+    <v>USDCNY</v>
+    <v>34</v>
+  </rv>
+  <rv s="10">
+    <v>35</v>
+    <v>avym77</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764006583939,0</v>
+    <v>0</v>
+    <v>avym77</v>
+    <v>USDCNY</v>
+    <v>35</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1zfec</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004742760,0</v>
+    <v>0</v>
+    <v>a1zfec</v>
+    <v>XNYS:PAAS</v>
+    <v>36</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1zfec</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764006769256,0</v>
+    <v>0</v>
+    <v>a1zfec</v>
+    <v>XNYS:PAAS</v>
+    <v>37</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1zfec</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764007486104,0</v>
+    <v>0</v>
+    <v>a1zfec</v>
+    <v>XNYS:PAAS</v>
+    <v>38</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1ic7</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004144652,0</v>
+    <v>0</v>
+    <v>ab1ic7</v>
+    <v>XTSE:TRI</v>
+    <v>39</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1ic7</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764003547277,0</v>
+    <v>0</v>
+    <v>ab1ic7</v>
+    <v>XTSE:TRI</v>
+    <v>40</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1ic7</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764008304164,0</v>
+    <v>0</v>
+    <v>ab1ic7</v>
+    <v>XTSE:TRI</v>
+    <v>41</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a233ur</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003894106,0</v>
+    <v>0</v>
+    <v>a233ur</v>
+    <v>ARCX:SLV</v>
+    <v>42</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a233ur</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004384328,0</v>
+    <v>0</v>
+    <v>a233ur</v>
+    <v>ARCX:SLV</v>
+    <v>43</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a233ur</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764003229402,0</v>
+    <v>0</v>
+    <v>a233ur</v>
+    <v>ARCX:SLV</v>
+    <v>44</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1qlz2</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004381963,0</v>
+    <v>0</v>
+    <v>a1qlz2</v>
+    <v>XNYS:CVX</v>
+    <v>45</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1qlz2</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003406244,0</v>
+    <v>0</v>
+    <v>a1qlz2</v>
+    <v>XNYS:CVX</v>
+    <v>46</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1qlz2</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004023534,0</v>
+    <v>0</v>
+    <v>a1qlz2</v>
+    <v>XNYS:CVX</v>
+    <v>47</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1u3p2</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004647590,0</v>
+    <v>0</v>
+    <v>a1u3p2</v>
+    <v>XNAS:GOOG</v>
+    <v>48</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1u3p2</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004623547,0</v>
+    <v>0</v>
+    <v>a1u3p2</v>
+    <v>XNAS:GOOG</v>
+    <v>49</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1u3p2</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003916652,0</v>
+    <v>0</v>
+    <v>a1u3p2</v>
+    <v>XNAS:GOOG</v>
+    <v>50</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1sp52</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004459957,0</v>
+    <v>0</v>
+    <v>a1sp52</v>
+    <v>XNYS:FCX</v>
+    <v>51</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1sp52</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764007874973,0</v>
+    <v>0</v>
+    <v>a1sp52</v>
+    <v>XNYS:FCX</v>
+    <v>52</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1sp52</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764006588827,0</v>
+    <v>0</v>
+    <v>a1sp52</v>
+    <v>XNYS:FCX</v>
+    <v>53</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>cfzfpr</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764002729218,0</v>
+    <v>0</v>
+    <v>cfzfpr</v>
+    <v>XNAS:GBUG</v>
+    <v>54</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>cfzfpr</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003652921,0</v>
+    <v>0</v>
+    <v>cfzfpr</v>
+    <v>XNAS:GBUG</v>
+    <v>55</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>cfzfpr</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004252531,0</v>
+    <v>0</v>
+    <v>cfzfpr</v>
+    <v>XNAS:GBUG</v>
+    <v>56</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1yv52</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764002974585,0</v>
+    <v>0</v>
+    <v>a1yv52</v>
+    <v>XNAS:NVDA</v>
+    <v>57</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1yv52</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764002824298,0</v>
+    <v>0</v>
+    <v>a1yv52</v>
+    <v>XNAS:NVDA</v>
+    <v>58</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1yv52</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003890555,0</v>
+    <v>0</v>
+    <v>a1yv52</v>
+    <v>XNAS:NVDA</v>
+    <v>59</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1y3m</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004743029,0</v>
+    <v>0</v>
+    <v>ab1y3m</v>
+    <v>XTSE:XIU</v>
+    <v>60</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1y3m</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003677477,0</v>
+    <v>0</v>
+    <v>ab1y3m</v>
+    <v>XTSE:XIU</v>
+    <v>61</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1y3m</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004368828,0</v>
+    <v>0</v>
+    <v>ab1y3m</v>
+    <v>XTSE:XIU</v>
+    <v>62</v>
+  </rv>
+  <rv s="10">
+    <v>37</v>
+    <v>avyo8m</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764007007259,0</v>
+    <v>0</v>
+    <v>avyo8m</v>
+    <v>USDINR</v>
+    <v>63</v>
+  </rv>
+  <rv s="10">
+    <v>37</v>
+    <v>avyo8m</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764008257612,0</v>
+    <v>0</v>
+    <v>avyo8m</v>
+    <v>USDINR</v>
+    <v>64</v>
+  </rv>
+  <rv s="10">
+    <v>37</v>
+    <v>avyo8m</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764006455521,0</v>
+    <v>0</v>
+    <v>avyo8m</v>
+    <v>USDINR</v>
+    <v>65</v>
+  </rv>
+  <rv s="10">
+    <v>37</v>
+    <v>avyo8m</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764008735321,0</v>
+    <v>0</v>
+    <v>avyo8m</v>
+    <v>USDINR</v>
+    <v>66</v>
+  </rv>
+  <rv s="10">
+    <v>37</v>
+    <v>avyo8m</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764007958920,0</v>
+    <v>0</v>
+    <v>avyo8m</v>
+    <v>USDINR</v>
+    <v>67</v>
+  </rv>
+  <rv s="10">
+    <v>37</v>
+    <v>avyo8m</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764002711932,0</v>
+    <v>0</v>
+    <v>avyo8m</v>
+    <v>USDINR</v>
+    <v>68</v>
+  </rv>
+  <rv s="10">
+    <v>37</v>
+    <v>avyo8m</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764008197672,0</v>
+    <v>0</v>
+    <v>avyo8m</v>
+    <v>USDINR</v>
+    <v>69</v>
+  </rv>
+  <rv s="10">
+    <v>37</v>
+    <v>avyo8m</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764007724092,0</v>
+    <v>0</v>
+    <v>avyo8m</v>
+    <v>USDINR</v>
+    <v>70</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1ndww</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004437341,0</v>
+    <v>0</v>
+    <v>a1ndww</v>
+    <v>XNAS:AMD</v>
+    <v>71</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1ndww</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764004154388,0</v>
+    <v>0</v>
+    <v>a1ndww</v>
+    <v>XNAS:AMD</v>
+    <v>72</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1ndww</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764003786010,0</v>
+    <v>0</v>
+    <v>a1ndww</v>
+    <v>XNAS:AMD</v>
+    <v>73</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a23hqh</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764003503826,0</v>
+    <v>0</v>
+    <v>a23hqh</v>
+    <v>ARCX:SPY</v>
+    <v>74</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a23hqh</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003065741,0</v>
+    <v>0</v>
+    <v>a23hqh</v>
+    <v>ARCX:SPY</v>
+    <v>75</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a23hqh</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004856434,0</v>
+    <v>0</v>
+    <v>a23hqh</v>
+    <v>ARCX:SPY</v>
+    <v>76</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>bo8l6h</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764007879271,0</v>
+    <v>0</v>
+    <v>bo8l6h</v>
+    <v>BTCUSD</v>
+    <v>77</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>bo8l6h</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764006290383,0</v>
+    <v>0</v>
+    <v>bo8l6h</v>
+    <v>BTCUSD</v>
+    <v>78</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>bo8l6h</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764002731843,0</v>
+    <v>0</v>
+    <v>bo8l6h</v>
+    <v>BTCUSD</v>
+    <v>79</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>bo8l6h</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764007256156,0</v>
+    <v>0</v>
+    <v>bo8l6h</v>
+    <v>BTCUSD</v>
+    <v>80</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>bo8l6h</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764003478348,0</v>
+    <v>0</v>
+    <v>bo8l6h</v>
+    <v>BTCUSD</v>
+    <v>81</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>bo8l6h</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764008108064,0</v>
+    <v>0</v>
+    <v>bo8l6h</v>
+    <v>BTCUSD</v>
+    <v>82</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>bo8l6h</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764003209747,0</v>
+    <v>0</v>
+    <v>bo8l6h</v>
+    <v>BTCUSD</v>
+    <v>83</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>bo8l6h</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764007580377,0</v>
+    <v>0</v>
+    <v>bo8l6h</v>
+    <v>BTCUSD</v>
+    <v>84</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwr7</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764007075771,0</v>
+    <v>0</v>
+    <v>auvwr7</v>
+    <v>Silver</v>
+    <v>85</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwr7</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003976959,0</v>
+    <v>0</v>
+    <v>auvwr7</v>
+    <v>Silver</v>
+    <v>86</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwr7</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764007023563,0</v>
+    <v>0</v>
+    <v>auvwr7</v>
+    <v>Silver</v>
+    <v>87</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwr7</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764003319837,0</v>
+    <v>0</v>
+    <v>auvwr7</v>
+    <v>Silver</v>
+    <v>88</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwr7</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764003807678,0</v>
+    <v>0</v>
+    <v>auvwr7</v>
+    <v>Silver</v>
+    <v>89</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwr7</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764005221477,0</v>
+    <v>0</v>
+    <v>auvwr7</v>
+    <v>Silver</v>
+    <v>90</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwr7</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764004454851,0</v>
+    <v>0</v>
+    <v>auvwr7</v>
+    <v>Silver</v>
+    <v>91</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwr7</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764002961410,0</v>
+    <v>0</v>
+    <v>auvwr7</v>
+    <v>Silver</v>
+    <v>92</v>
+  </rv>
+  <rv s="10">
+    <v>38</v>
+    <v>avytp2</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764003209747,0</v>
+    <v>0</v>
+    <v>avytp2</v>
+    <v>USDTRY</v>
+    <v>93</v>
+  </rv>
+  <rv s="10">
+    <v>38</v>
+    <v>avytp2</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764004217979,0</v>
+    <v>0</v>
+    <v>avytp2</v>
+    <v>USDTRY</v>
     <v>94</v>
+  </rv>
+  <rv s="10">
+    <v>38</v>
+    <v>avytp2</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764008190505,0</v>
+    <v>0</v>
+    <v>avytp2</v>
+    <v>USDTRY</v>
+    <v>95</v>
+  </rv>
+  <rv s="10">
+    <v>38</v>
+    <v>avytp2</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764003759999,0</v>
+    <v>0</v>
+    <v>avytp2</v>
+    <v>USDTRY</v>
+    <v>96</v>
+  </rv>
+  <rv s="10">
+    <v>38</v>
+    <v>avytp2</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764006538224,0</v>
+    <v>0</v>
+    <v>avytp2</v>
+    <v>USDTRY</v>
+    <v>97</v>
+  </rv>
+  <rv s="10">
+    <v>38</v>
+    <v>avytp2</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764007483615,0</v>
+    <v>0</v>
+    <v>avytp2</v>
+    <v>USDTRY</v>
+    <v>98</v>
+  </rv>
+  <rv s="10">
+    <v>38</v>
+    <v>avytp2</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764003020555,0</v>
+    <v>0</v>
+    <v>avytp2</v>
+    <v>USDTRY</v>
+    <v>99</v>
+  </rv>
+  <rv s="10">
+    <v>38</v>
+    <v>avytp2</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764006933408,0</v>
+    <v>0</v>
+    <v>avytp2</v>
+    <v>USDTRY</v>
+    <v>100</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwu2</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764007406460,0</v>
+    <v>0</v>
+    <v>auvwu2</v>
+    <v>Platinum</v>
+    <v>101</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwu2</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004718239,0</v>
+    <v>0</v>
+    <v>auvwu2</v>
+    <v>Platinum</v>
+    <v>102</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwu2</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764005942888,0</v>
+    <v>0</v>
+    <v>auvwu2</v>
+    <v>Platinum</v>
+    <v>103</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwu2</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764007388768,0</v>
+    <v>0</v>
+    <v>auvwu2</v>
+    <v>Platinum</v>
+    <v>104</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwu2</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003704936,0</v>
+    <v>0</v>
+    <v>auvwu2</v>
+    <v>Platinum</v>
+    <v>105</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwu2</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764008304746,0</v>
+    <v>0</v>
+    <v>auvwu2</v>
+    <v>Platinum</v>
+    <v>106</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwu2</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764004971750,0</v>
+    <v>0</v>
+    <v>auvwu2</v>
+    <v>Platinum</v>
+    <v>107</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwu2</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764007050251,0</v>
+    <v>0</v>
+    <v>auvwu2</v>
+    <v>Platinum</v>
+    <v>88</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1mou2</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764003264626,0</v>
+    <v>0</v>
+    <v>a1mou2</v>
+    <v>XNAS:AAPL</v>
+    <v>108</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1mou2</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764006432964,0</v>
+    <v>0</v>
+    <v>a1mou2</v>
+    <v>XNAS:AAPL</v>
+    <v>109</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1mou2</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764006196357,0</v>
+    <v>0</v>
+    <v>a1mou2</v>
+    <v>XNAS:AAPL</v>
+    <v>110</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a24kar</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764007577357,0</v>
+    <v>0</v>
+    <v>a24kar</v>
+    <v>XNAS:TSLA</v>
+    <v>111</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a24kar</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004979130,0</v>
+    <v>0</v>
+    <v>a24kar</v>
+    <v>XNAS:TSLA</v>
+    <v>112</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a24kar</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003445857,0</v>
+    <v>0</v>
+    <v>a24kar</v>
+    <v>XNAS:TSLA</v>
+    <v>113</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1upz2</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004005042,0</v>
+    <v>0</v>
+    <v>a1upz2</v>
+    <v>XNYS:HL</v>
+    <v>114</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1upz2</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764007571157,0</v>
+    <v>0</v>
+    <v>a1upz2</v>
+    <v>XNYS:HL</v>
+    <v>115</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a1upz2</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764008067194,0</v>
+    <v>0</v>
+    <v>a1upz2</v>
+    <v>XNYS:HL</v>
+    <v>116</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a269ec</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764003939825,0</v>
+    <v>0</v>
+    <v>a269ec</v>
+    <v>XNYS:XOM</v>
+    <v>117</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a269ec</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003302392,0</v>
+    <v>0</v>
+    <v>a269ec</v>
+    <v>XNYS:XOM</v>
+    <v>118</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a269ec</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764003083337,0</v>
+    <v>0</v>
+    <v>a269ec</v>
+    <v>XNYS:XOM</v>
+    <v>119</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>aay9k2</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004180594,0</v>
+    <v>0</v>
+    <v>aay9k2</v>
+    <v>XTSE:FNV</v>
+    <v>120</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>aay9k2</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004869821,0</v>
+    <v>0</v>
+    <v>aay9k2</v>
+    <v>XTSE:FNV</v>
+    <v>121</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>aay9k2</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764004977114,0</v>
+    <v>0</v>
+    <v>aay9k2</v>
+    <v>XTSE:FNV</v>
+    <v>122</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>aaxdur</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004987812,0</v>
+    <v>0</v>
+    <v>aaxdur</v>
+    <v>XTSE:CCO</v>
+    <v>123</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>aaxdur</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764004745883,0</v>
+    <v>0</v>
+    <v>aaxdur</v>
+    <v>XTSE:CCO</v>
+    <v>124</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>aaxdur</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764004609472,0</v>
+    <v>0</v>
+    <v>aaxdur</v>
+    <v>XTSE:CCO</v>
+    <v>125</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvx6h</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764004496966,0</v>
+    <v>0</v>
+    <v>auvx6h</v>
+    <v>Natural Gas</v>
+    <v>126</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvx6h</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764007825480,0</v>
+    <v>0</v>
+    <v>auvx6h</v>
+    <v>Natural Gas</v>
+    <v>127</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvx6h</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764008051391,0</v>
+    <v>0</v>
+    <v>auvx6h</v>
+    <v>Natural Gas</v>
+    <v>128</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvx6h</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764005980462,0</v>
+    <v>0</v>
+    <v>auvx6h</v>
+    <v>Natural Gas</v>
+    <v>88</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvx6h</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764006560912,0</v>
+    <v>0</v>
+    <v>auvx6h</v>
+    <v>Natural Gas</v>
+    <v>129</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvx6h</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764006816794,0</v>
+    <v>0</v>
+    <v>auvx6h</v>
+    <v>Natural Gas</v>
+    <v>130</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>brjcfr</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764005458660,0</v>
+    <v>0</v>
+    <v>brjcfr</v>
+    <v>ETHUSD</v>
+    <v>131</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>brjcfr</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764006856731,0</v>
+    <v>0</v>
+    <v>brjcfr</v>
+    <v>ETHUSD</v>
+    <v>132</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>brjcfr</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764004965024,0</v>
+    <v>0</v>
+    <v>brjcfr</v>
+    <v>ETHUSD</v>
+    <v>133</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>brjcfr</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764005209750,0</v>
+    <v>0</v>
+    <v>brjcfr</v>
+    <v>ETHUSD</v>
+    <v>134</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>brjcfr</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764008495324,0</v>
+    <v>0</v>
+    <v>brjcfr</v>
+    <v>ETHUSD</v>
+    <v>135</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>brjcfr</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764007320485,0</v>
+    <v>0</v>
+    <v>brjcfr</v>
+    <v>ETHUSD</v>
+    <v>136</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>brjcfr</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764006784615,0</v>
+    <v>0</v>
+    <v>brjcfr</v>
+    <v>ETHUSD</v>
+    <v>137</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>brjcfr</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764008437337,0</v>
+    <v>0</v>
+    <v>brjcfr</v>
+    <v>ETHUSD</v>
+    <v>138</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>cc5pdm</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764003266857,0</v>
+    <v>0</v>
+    <v>cc5pdm</v>
+    <v>XNAS:IBIT</v>
+    <v>139</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>cc5pdm</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764006032485,0</v>
+    <v>0</v>
+    <v>cc5pdm</v>
+    <v>XNAS:IBIT</v>
+    <v>140</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>cc5pdm</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764002766809,0</v>
+    <v>0</v>
+    <v>cc5pdm</v>
+    <v>XNAS:IBIT</v>
+    <v>141</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>avylur</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764003457448,0</v>
+    <v>0</v>
+    <v>avylur</v>
+    <v>USDCAD</v>
+    <v>142</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>avylur</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764006757167,0</v>
+    <v>0</v>
+    <v>avylur</v>
+    <v>USDCAD</v>
+    <v>143</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>avylur</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764008027377,0</v>
+    <v>0</v>
+    <v>avylur</v>
+    <v>USDCAD</v>
+    <v>144</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>avylur</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004721885,0</v>
+    <v>0</v>
+    <v>avylur</v>
+    <v>USDCAD</v>
+    <v>145</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>avylur</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764006912276,0</v>
+    <v>0</v>
+    <v>avylur</v>
+    <v>USDCAD</v>
+    <v>146</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>avylur</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764006217107,0</v>
+    <v>0</v>
+    <v>avylur</v>
+    <v>USDCAD</v>
+    <v>147</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>avylur</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764006175511,0</v>
+    <v>0</v>
+    <v>avylur</v>
+    <v>USDCAD</v>
+    <v>148</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>avylur</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764006991925,0</v>
+    <v>0</v>
+    <v>avylur</v>
+    <v>USDCAD</v>
+    <v>149</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1tfr</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764007484764,0</v>
+    <v>0</v>
+    <v>ab1tfr</v>
+    <v>XTSE:WPM</v>
+    <v>150</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1tfr</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764002974585,0</v>
+    <v>0</v>
+    <v>ab1tfr</v>
+    <v>XTSE:WPM</v>
+    <v>151</v>
+  </rv>
+  <rv s="10">
+    <v>36</v>
+    <v>ab1tfr</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764006929305,0</v>
+    <v>0</v>
+    <v>ab1tfr</v>
+    <v>XTSE:WPM</v>
+    <v>152</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwoc</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764003960675,0</v>
+    <v>0</v>
+    <v>auvwoc</v>
+    <v>Gold</v>
+    <v>153</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwoc</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764007335845,0</v>
+    <v>0</v>
+    <v>auvwoc</v>
+    <v>Gold</v>
+    <v>88</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwoc</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764007545564,0</v>
+    <v>0</v>
+    <v>auvwoc</v>
+    <v>Gold</v>
+    <v>154</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwoc</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764006340236,0</v>
+    <v>0</v>
+    <v>auvwoc</v>
+    <v>Gold</v>
+    <v>155</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwoc</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764007973680,0</v>
+    <v>0</v>
+    <v>auvwoc</v>
+    <v>Gold</v>
+    <v>156</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwoc</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764007959727,0</v>
+    <v>0</v>
+    <v>auvwoc</v>
+    <v>Gold</v>
+    <v>157</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwoc</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764006635537,0</v>
+    <v>0</v>
+    <v>auvwoc</v>
+    <v>Gold</v>
+    <v>158</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>auvwoc</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764006509479,0</v>
+    <v>0</v>
+    <v>auvwoc</v>
+    <v>Gold</v>
+    <v>159</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>ce8mrw</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004510833,0</v>
+    <v>0</v>
+    <v>ce8mrw</v>
+    <v>XNAS:ETHA</v>
+    <v>160</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>ce8mrw</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764007637522,0</v>
+    <v>0</v>
+    <v>ce8mrw</v>
+    <v>XNAS:ETHA</v>
+    <v>161</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>ce8mrw</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764007637522,0</v>
+    <v>0</v>
+    <v>ce8mrw</v>
+    <v>XNAS:ETHA</v>
+    <v>162</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a21mim</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764004777720,0</v>
+    <v>0</v>
+    <v>a21mim</v>
+    <v>XNAS:QQQ</v>
+    <v>163</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a21mim</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764007246239,0</v>
+    <v>0</v>
+    <v>a21mim</v>
+    <v>XNAS:QQQ</v>
+    <v>164</v>
+  </rv>
+  <rv s="10">
+    <v>32</v>
+    <v>a21mim</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764006161639,0</v>
+    <v>0</v>
+    <v>a21mim</v>
+    <v>XNAS:QQQ</v>
+    <v>165</v>
+  </rv>
+  <rv s="10">
+    <v>39</v>
+    <v>avyomw</v>
+    <v>Daily</v>
+    <v>45793</v>
+    <v>45793</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638829504000000000,639146764006275066,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>166</v>
+  </rv>
+  <rv s="10">
+    <v>39</v>
+    <v>avyomw</v>
+    <v>Daily</v>
+    <v>45611</v>
+    <v>45611</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638672256000000000,639146764005020584,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>167</v>
+  </rv>
+  <rv s="10">
+    <v>39</v>
+    <v>avyomw</v>
+    <v>Daily</v>
+    <v>46128</v>
+    <v>46128</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639118944000000000,639146764008058999,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>168</v>
+  </rv>
+  <rv s="10">
+    <v>39</v>
+    <v>avyomw</v>
+    <v>Daily</v>
+    <v>46069</v>
+    <v>46069</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639067968000000000,639146764006275066,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>169</v>
+  </rv>
+  <rv s="10">
+    <v>39</v>
+    <v>avyomw</v>
+    <v>Daily</v>
+    <v>46153</v>
+    <v>46153</v>
+    <v>0</v>
+    <v>1</v>
+    <v>639140544000000000,639146764007340384,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>170</v>
+  </rv>
+  <rv s="10">
+    <v>39</v>
+    <v>avyomw</v>
+    <v>Daily</v>
+    <v>45062</v>
+    <v>45062</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638197920000000000,639146764006822669,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>171</v>
+  </rv>
+  <rv s="10">
+    <v>39</v>
+    <v>avyomw</v>
+    <v>Daily</v>
+    <v>45428</v>
+    <v>45428</v>
+    <v>0</v>
+    <v>1</v>
+    <v>638514144000000000,639146764007141257,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>172</v>
+  </rv>
+  <rv s="10">
+    <v>39</v>
+    <v>avyomw</v>
+    <v>Daily</v>
+    <v>44697</v>
+    <v>44697</v>
+    <v>0</v>
+    <v>1</v>
+    <v>637882560000000000,639146764007111401,0</v>
+    <v>0</v>
+    <v>avyomw</v>
+    <v>USDJPY</v>
+    <v>173</v>
   </rv>
 </rvData>
 </file>
@@ -2343,51 +5320,6 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
-    <k n="%OutdatedReason" t="i"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change (%)"/>
-    <k n="Currency" t="s"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="Expense ratio"/>
-    <k n="High"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Open"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-  </s>
-  <s t="_linkedentity">
-    <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -2422,12 +5354,19 @@
     <k n="Volume"/>
     <k n="Volume average"/>
   </s>
+  <s t="_linkedentity">
+    <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="ptg" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
-    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -2463,7 +5402,6 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
-    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -2501,7 +5439,6 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
-    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -2549,7 +5486,6 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
-    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -2579,34 +5515,6 @@
     <k n="%EntityId" t="s"/>
     <k n="%EntityServiceId"/>
     <k n="%IsRefreshable" t="b"/>
-    <k n="%OutdatedReason" t="i"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Change"/>
-    <k n="Change (%)"/>
-    <k n="Currency" t="s"/>
-    <k n="From currency" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="Name" t="s"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%OutdatedReason" t="i"/>
     <k n="%ProviderInfo" t="s"/>
     <k n="_Display" t="spb"/>
     <k n="_DisplayString" t="s"/>
@@ -2630,50 +5538,31 @@
     <k n="UniqueName" t="s"/>
     <k n="Year"/>
   </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+  <s t="_stockhistorycache">
+    <k n="_Format" t="spb"/>
+    <k n="Symbol" t="s"/>
+    <k n="Interval" t="s"/>
+    <k n="StartDate" t="i"/>
+    <k n="EndDate" t="i"/>
+    <k n="f1904" t="b"/>
+    <k n="fdcompat" t="b"/>
+    <k n="etag" t="s"/>
+    <k n="Date" t="a"/>
+    <k n="EntityId" t="s"/>
+    <k n="Instrument" t="s"/>
+    <k n="Close" t="a"/>
+  </s>
 </rvStructures>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="8">
-    <a count="35">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Exchange</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Expense ratio</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">Instrument type</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">%ProviderInfo</v>
-      <v t="s">%OutdatedReason</v>
-    </a>
-    <a count="38">
+  <spbArrays count="6">
+    <a count="37">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -2711,9 +5600,8 @@
       <v t="s">_DisplayString</v>
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
-      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="34">
+    <a count="33">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -2747,9 +5635,8 @@
       <v t="s">_DisplayString</v>
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
-      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="36">
+    <a count="35">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -2785,9 +5672,8 @@
       <v t="s">UniqueName</v>
       <v t="s">_DisplayString</v>
       <v t="s">%ProviderInfo</v>
-      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="46">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -2833,9 +5719,8 @@
       <v t="s">LearnMoreOnLink</v>
       <v t="s">ExchangeID</v>
       <v t="s">%ProviderInfo</v>
-      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="28">
+    <a count="27">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -2863,36 +5748,8 @@
       <v t="s">UniqueName</v>
       <v t="s">_DisplayString</v>
       <v t="s">%ProviderInfo</v>
-      <v t="s">%OutdatedReason</v>
     </a>
-    <a count="25">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">Price</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Change</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Currency</v>
-      <v t="s">From currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Instrument type</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">%ProviderInfo</v>
-      <v t="s">%OutdatedReason</v>
-    </a>
-    <a count="27">
+    <a count="26">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -2919,10 +5776,9 @@
       <v t="s">_DisplayString</v>
       <v t="s">LearnMoreOnLink</v>
       <v t="s">%ProviderInfo</v>
-      <v t="s">%OutdatedReason</v>
     </a>
   </spbArrays>
-  <spbData count="37">
+  <spbData count="40">
     <spb s="0">
       <v>0</v>
       <v>Name</v>
@@ -2956,13 +5812,19 @@
       <v>4</v>
       <v>7</v>
       <v>8</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>from previous close</v>
       <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -2970,43 +5832,6 @@
       <v>LearnMoreOnLink</v>
     </spb>
     <spb s="5">
-      <v>1</v>
-      <v>2</v>
-      <v>1</v>
-      <v>3</v>
-      <v>1</v>
-      <v>1</v>
-      <v>1</v>
-      <v>4</v>
-      <v>5</v>
-      <v>6</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
-      <v>1</v>
-      <v>4</v>
-      <v>7</v>
-      <v>8</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
-    </spb>
-    <spb s="6">
-      <v>at close</v>
-      <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
-      <v>from previous close</v>
-      <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
-    </spb>
-    <spb s="0">
-      <v>2</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="7">
       <v>9</v>
       <v>2</v>
       <v>9</v>
@@ -3024,31 +5849,21 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="8">
+    <spb s="6">
       <v>Delayed 20 minutes</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>GMT</v>
     </spb>
-    <spb s="6">
-      <v>at close</v>
-      <v>from previous close</v>
-      <v>Source: Nasdaq</v>
-      <v>from previous close</v>
-      <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
-    </spb>
-    <spb s="9">
-      <v>3</v>
+    <spb s="7">
+      <v>2</v>
       <v>Name</v>
     </spb>
-    <spb s="10">
+    <spb s="8">
       <v>1</v>
       <v>1</v>
     </spb>
-    <spb s="11">
+    <spb s="9">
       <v>1</v>
       <v>1</v>
       <v>3</v>
@@ -3070,17 +5885,17 @@
       <v>5</v>
     </spb>
     <spb s="0">
-      <v>4</v>
+      <v>3</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="12">
+    <spb s="10">
       <v>1</v>
       <v>1</v>
       <v>1</v>
       <v>1</v>
     </spb>
-    <spb s="13">
+    <spb s="11">
       <v>9</v>
       <v>2</v>
       <v>2</v>
@@ -3105,7 +5920,7 @@
       <v>9</v>
       <v>5</v>
     </spb>
-    <spb s="14">
+    <spb s="12">
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -3114,7 +5929,7 @@
       <v>from close</v>
       <v>from close</v>
     </spb>
-    <spb s="13">
+    <spb s="11">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -3139,7 +5954,7 @@
       <v>1</v>
       <v>5</v>
     </spb>
-    <spb s="15">
+    <spb s="13">
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -3149,17 +5964,7 @@
       <v>from close</v>
       <v>from close</v>
     </spb>
-    <spb s="15">
-      <v>at close</v>
-      <v>from previous close</v>
-      <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
-      <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
-    </spb>
-    <spb s="13">
+    <spb s="11">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -3184,11 +5989,11 @@
       <v>1</v>
       <v>5</v>
     </spb>
-    <spb s="9">
-      <v>5</v>
+    <spb s="7">
+      <v>4</v>
       <v>Name</v>
     </spb>
-    <spb s="16">
+    <spb s="14">
       <v>9</v>
       <v>9</v>
       <v>3</v>
@@ -3202,10 +6007,10 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="17">
+    <spb s="15">
       <v>GMT</v>
     </spb>
-    <spb s="16">
+    <spb s="14">
       <v>1</v>
       <v>1</v>
       <v>3</v>
@@ -3219,7 +6024,7 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="16">
+    <spb s="14">
       <v>12</v>
       <v>12</v>
       <v>3</v>
@@ -3233,7 +6038,7 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="16">
+    <spb s="14">
       <v>13</v>
       <v>13</v>
       <v>3</v>
@@ -3247,12 +6052,11 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="9">
-      <v>6</v>
-      <v>Name</v>
-    </spb>
-    <spb s="18">
+    <spb s="14">
+      <v>14</v>
+      <v>14</v>
       <v>3</v>
+      <v>14</v>
       <v>14</v>
       <v>14</v>
       <v>5</v>
@@ -3262,7 +6066,7 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="16">
+    <spb s="14">
       <v>15</v>
       <v>15</v>
       <v>3</v>
@@ -3276,7 +6080,7 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="16">
+    <spb s="14">
       <v>16</v>
       <v>16</v>
       <v>3</v>
@@ -3290,7 +6094,7 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="16">
+    <spb s="14">
       <v>17</v>
       <v>17</v>
       <v>3</v>
@@ -3304,7 +6108,7 @@
       <v>7</v>
       <v>8</v>
     </spb>
-    <spb s="16">
+    <spb s="14">
       <v>18</v>
       <v>18</v>
       <v>3</v>
@@ -3319,11 +6123,11 @@
       <v>8</v>
     </spb>
     <spb s="0">
-      <v>7</v>
+      <v>5</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="19">
+    <spb s="16">
       <v>3</v>
       <v>11</v>
       <v>11</v>
@@ -3334,12 +6138,48 @@
       <v>7</v>
       <v>8</v>
     </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>18</v>
+    </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>1</v>
+    </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>17</v>
+    </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>12</v>
+    </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>14</v>
+    </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>9</v>
+    </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>16</v>
+    </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>15</v>
+    </spb>
+    <spb s="17">
+      <v>19</v>
+      <v>13</v>
+    </spb>
   </spbData>
 </supportingPropertyBags>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="20">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="18">
   <s>
     <k n="^Order" t="spba"/>
     <k n="TitleProperty" t="s"/>
@@ -3354,32 +6194,6 @@
     <k n="UniqueName" t="spb"/>
     <k n="`%ProviderInfo" t="spb"/>
     <k n="LearnMoreOnLink" t="spb"/>
-  </s>
-  <s>
-    <k n="Low" t="i"/>
-    <k n="Beta" t="i"/>
-    <k n="High" t="i"/>
-    <k n="Name" t="i"/>
-    <k n="Open" t="i"/>
-    <k n="Price" t="i"/>
-    <k n="Change" t="i"/>
-    <k n="Volume" t="i"/>
-    <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
-    <k n="52 week low" t="i"/>
-    <k n="52 week high" t="i"/>
-    <k n="Expense ratio" t="i"/>
-    <k n="Previous close" t="i"/>
-    <k n="Volume average" t="i"/>
-    <k n="Last trade time" t="i"/>
-    <k n="`%EntityServiceId" t="i"/>
-  </s>
-  <s>
-    <k n="Price" t="s"/>
-    <k n="Change" t="s"/>
-    <k n="Exchange" t="s"/>
-    <k n="Change (%)" t="s"/>
-    <k n="Last trade time" t="s"/>
   </s>
   <s>
     <k n="Low" t="i"/>
@@ -3535,17 +6349,6 @@
   </s>
   <s>
     <k n="Name" t="i"/>
-    <k n="Price" t="i"/>
-    <k n="Change" t="i"/>
-    <k n="Change (%)" t="i"/>
-    <k n="52 week low" t="i"/>
-    <k n="52 week high" t="i"/>
-    <k n="Previous close" t="i"/>
-    <k n="Last trade time" t="i"/>
-    <k n="`%EntityServiceId" t="i"/>
-  </s>
-  <s>
-    <k n="Name" t="i"/>
     <k n="Year" t="i"/>
     <k n="Month" t="i"/>
     <k n="Price" t="i"/>
@@ -3554,6 +6357,10 @@
     <k n="Expiration Date" t="i"/>
     <k n="Last trade time" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
+  </s>
+  <s>
+    <k n="Date" t="i"/>
+    <k n="Close" t="i"/>
   </s>
 </spbStructures>
 </file>
@@ -3647,9 +6454,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3687,7 +6494,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3793,7 +6600,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3935,7 +6742,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3987,19 +6794,19 @@
       </c>
       <c r="I1" s="8">
         <f ca="1">WORKDAY(TODAY(),-5)</f>
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="J1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-1),-1)</f>
-        <v>46107</v>
+        <v>46128</v>
       </c>
       <c r="K1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-3),-1)</f>
-        <v>46048</v>
+        <v>46069</v>
       </c>
       <c r="L1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-12),-1)</f>
-        <v>45772</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -4018,7 +6825,7 @@
       </c>
       <c r="E2" s="3" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">_FV(A2,"Price")</f>
-        <v>686.24</v>
+        <v>739.17</v>
       </c>
       <c r="F2" t="str" cm="1">
         <f t="array" aca="1" ref="F2" ca="1">_FV(A2,"Currency")</f>
@@ -4026,27 +6833,27 @@
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2" ca="1" si="0">D2*E2</f>
-        <v>68624</v>
+        <v>73917</v>
       </c>
       <c r="H2" s="4">
         <f ca="1">IF(F2="CAD",G2,(G2*Currency!$B$2))</f>
-        <v>93891.356800000009</v>
-      </c>
-      <c r="I2" s="2" t="e" cm="1" vm="2">
+        <v>101635.875</v>
+      </c>
+      <c r="I2" s="2" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">($E2 - _xlfn.STOCKHISTORY($A2, I$1,I$1,0,0,1))/$E2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J2" s="2" t="e" cm="1" vm="2">
+        <v>-1.7587293856622356E-4</v>
+      </c>
+      <c r="J2" s="2" cm="1">
         <f t="array" aca="1" ref="J2" ca="1">($E2 - _xlfn.STOCKHISTORY($A2, J$1,J$1,0,0,1))/$E2</f>
-        <v>#VALUE!</v>
+        <v>5.0746107120148265E-2</v>
       </c>
       <c r="K2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K2" ca="1">($E2 - _xlfn.STOCKHISTORY($A2, K$1,K$1,0,0,1))/$E2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L2" s="2" t="e" cm="1" vm="2">
+      <c r="L2" s="2" cm="1">
         <f t="array" aca="1" ref="L2" ca="1">($E2 - _xlfn.STOCKHISTORY($A2, L$1,L$1,0,0,1))/$E2</f>
-        <v>#VALUE!</v>
+        <v>0.19612538387651005</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -4065,7 +6872,7 @@
       </c>
       <c r="E3" s="3" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">_FV(A3,"Price")</f>
-        <v>605.79</v>
+        <v>708.93</v>
       </c>
       <c r="F3" t="str" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">_FV(A3,"Currency")</f>
@@ -4073,27 +6880,27 @@
       </c>
       <c r="G3" s="4">
         <f t="shared" ref="G3:G8" ca="1" si="1">D3*E3</f>
-        <v>60579</v>
+        <v>70893</v>
       </c>
       <c r="H3" s="4">
         <f ca="1">IF(F3="CAD",G3,(G3*Currency!$B$2))</f>
-        <v>82884.1878</v>
-      </c>
-      <c r="I3" s="2" t="e" cm="1" vm="2">
+        <v>97477.875</v>
+      </c>
+      <c r="I3" s="2" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">($E3 - _xlfn.STOCKHISTORY($A3, I$1,I$1,0,0,1))/$E3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J3" s="2" t="e" cm="1" vm="2">
+        <v>-6.1501135514084801E-3</v>
+      </c>
+      <c r="J3" s="2" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">($E3 - _xlfn.STOCKHISTORY($A3, J$1,J$1,0,0,1))/$E3</f>
-        <v>#VALUE!</v>
+        <v>9.6568067369133662E-2</v>
       </c>
       <c r="K3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K3" ca="1">($E3 - _xlfn.STOCKHISTORY($A3, K$1,K$1,0,0,1))/$E3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L3" s="2" t="e" cm="1" vm="2">
+      <c r="L3" s="2" cm="1">
         <f t="array" aca="1" ref="L3" ca="1">($E3 - _xlfn.STOCKHISTORY($A3, L$1,L$1,0,0,1))/$E3</f>
-        <v>#VALUE!</v>
+        <v>0.26437024812040677</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -4112,7 +6919,7 @@
       </c>
       <c r="E4" s="3" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">_FV(A4,"Price")</f>
-        <v>49.08</v>
+        <v>49.82</v>
       </c>
       <c r="F4" t="str" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">_FV(A4,"Currency")</f>
@@ -4120,27 +6927,27 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>98160</v>
+        <v>99640</v>
       </c>
       <c r="H4" s="4">
         <f ca="1">IF(F4="CAD",G4,(G4*Currency!$B$2))</f>
-        <v>98160</v>
-      </c>
-      <c r="I4" s="2" t="e" cm="1" vm="2">
+        <v>99640</v>
+      </c>
+      <c r="I4" s="2" cm="1">
         <f t="array" aca="1" ref="I4" ca="1">($E4 - _xlfn.STOCKHISTORY($A4, I$1,I$1,0,0,1))/$E4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J4" s="2" t="e" cm="1" vm="2">
+        <v>-4.8173424327579688E-3</v>
+      </c>
+      <c r="J4" s="2" cm="1">
         <f t="array" aca="1" ref="J4" ca="1">($E4 - _xlfn.STOCKHISTORY($A4, J$1,J$1,0,0,1))/$E4</f>
-        <v>#VALUE!</v>
+        <v>-5.0180650341228421E-3</v>
       </c>
       <c r="K4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K4" ca="1">($E4 - _xlfn.STOCKHISTORY($A4, K$1,K$1,0,0,1))/$E4</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L4" s="2" t="e" cm="1" vm="2">
+      <c r="L4" s="2" cm="1">
         <f t="array" aca="1" ref="L4" ca="1">($E4 - _xlfn.STOCKHISTORY($A4, L$1,L$1,0,0,1))/$E4</f>
-        <v>#VALUE!</v>
+        <v>0.2050381372942594</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -4159,7 +6966,7 @@
       </c>
       <c r="E5" s="3" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">_FV(A5,"Price")</f>
-        <v>89.53</v>
+        <v>83.66</v>
       </c>
       <c r="F5" t="str" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">_FV(A5,"Currency")</f>
@@ -4167,27 +6974,27 @@
       </c>
       <c r="G5" s="4">
         <f t="shared" ref="G5:G7" ca="1" si="2">D5*E5</f>
-        <v>71624</v>
+        <v>66928</v>
       </c>
       <c r="H5" s="4">
         <f ca="1">IF(F5="CAD",G5,(G5*Currency!$B$2))</f>
-        <v>97995.9568</v>
-      </c>
-      <c r="I5" s="2" t="e" cm="1" vm="2">
+        <v>92026</v>
+      </c>
+      <c r="I5" s="2" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">($E5 - _xlfn.STOCKHISTORY($A5, I$1,I$1,0,0,1))/$E5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J5" s="2" t="e" cm="1" vm="2">
+        <v>-2.2710972985895358E-2</v>
+      </c>
+      <c r="J5" s="2" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">($E5 - _xlfn.STOCKHISTORY($A5, J$1,J$1,0,0,1))/$E5</f>
-        <v>#VALUE!</v>
+        <v>-3.1317236433181982E-2</v>
       </c>
       <c r="K5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K5" ca="1">($E5 - _xlfn.STOCKHISTORY($A5, K$1,K$1,0,0,1))/$E5</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L5" s="2" t="e" cm="1" vm="2">
+      <c r="L5" s="2" cm="1">
         <f t="array" aca="1" ref="L5" ca="1">($E5 - _xlfn.STOCKHISTORY($A5, L$1,L$1,0,0,1))/$E5</f>
-        <v>#VALUE!</v>
+        <v>-3.1556299306717675E-2</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -4206,7 +7013,7 @@
       </c>
       <c r="E6" s="3" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">_FV(A6,"Price")</f>
-        <v>50.626100000000001</v>
+        <v>44.39</v>
       </c>
       <c r="F6" t="str" cm="1">
         <f t="array" aca="1" ref="F6" ca="1">_FV(A6,"Currency")</f>
@@ -4214,27 +7021,27 @@
       </c>
       <c r="G6" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>50626.1</v>
+        <v>44390</v>
       </c>
       <c r="H6" s="4">
         <f ca="1">IF(F6="CAD",G6,(G6*Currency!$B$2))</f>
-        <v>69266.630019999997</v>
-      </c>
-      <c r="I6" s="2" t="e" cm="1" vm="2">
+        <v>61036.25</v>
+      </c>
+      <c r="I6" s="2" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">($E6 - _xlfn.STOCKHISTORY($A6, I$1,I$1,0,0,1))/$E6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J6" s="2" t="e" cm="1" vm="2">
+        <v>-8.9981977922955675E-2</v>
+      </c>
+      <c r="J6" s="2" cm="1">
         <f t="array" aca="1" ref="J6" ca="1">($E6 - _xlfn.STOCKHISTORY($A6, J$1,J$1,0,0,1))/$E6</f>
-        <v>#VALUE!</v>
+        <v>-0.10430277089434563</v>
       </c>
       <c r="K6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K6" ca="1">($E6 - _xlfn.STOCKHISTORY($A6, K$1,K$1,0,0,1))/$E6</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L6" s="2" t="e" cm="1" vm="2">
+      <c r="L6" s="2" cm="1">
         <f t="array" aca="1" ref="L6" ca="1">($E6 - _xlfn.STOCKHISTORY($A6, L$1,L$1,0,0,1))/$E6</f>
-        <v>#VALUE!</v>
+        <v>0.48727190808740706</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -4253,7 +7060,7 @@
       </c>
       <c r="E7" s="3" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">_FV(A7,"Price")</f>
-        <v>348.1</v>
+        <v>310.02999999999997</v>
       </c>
       <c r="F7" t="str" cm="1">
         <f t="array" aca="1" ref="F7" ca="1">_FV(A7,"Currency")</f>
@@ -4261,27 +7068,27 @@
       </c>
       <c r="G7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>69620</v>
+        <v>62005.999999999993</v>
       </c>
       <c r="H7" s="4">
         <f ca="1">IF(F7="CAD",G7,(G7*Currency!$B$2))</f>
-        <v>69620</v>
-      </c>
-      <c r="I7" s="2" t="e" cm="1" vm="2">
+        <v>62005.999999999993</v>
+      </c>
+      <c r="I7" s="2" cm="1">
         <f t="array" aca="1" ref="I7" ca="1">($E7 - _xlfn.STOCKHISTORY($A7, I$1,I$1,0,0,1))/$E7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J7" s="2" t="e" cm="1" vm="2">
+        <v>-4.8221139889688243E-2</v>
+      </c>
+      <c r="J7" s="2" cm="1">
         <f t="array" aca="1" ref="J7" ca="1">($E7 - _xlfn.STOCKHISTORY($A7, J$1,J$1,0,0,1))/$E7</f>
-        <v>#VALUE!</v>
+        <v>-0.14072831661452134</v>
       </c>
       <c r="K7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K7" ca="1">($E7 - _xlfn.STOCKHISTORY($A7, K$1,K$1,0,0,1))/$E7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L7" s="2" t="e" cm="1" vm="2">
+      <c r="L7" s="2" cm="1">
         <f t="array" aca="1" ref="L7" ca="1">($E7 - _xlfn.STOCKHISTORY($A7, L$1,L$1,0,0,1))/$E7</f>
-        <v>#VALUE!</v>
+        <v>0.28174692771667248</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -4300,7 +7107,7 @@
       </c>
       <c r="E8" s="3" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">_FV(A8,"Price")</f>
-        <v>198.4</v>
+        <v>179.39</v>
       </c>
       <c r="F8" t="str" cm="1">
         <f t="array" aca="1" ref="F8" ca="1">_FV(A8,"Currency")</f>
@@ -4308,27 +7115,27 @@
       </c>
       <c r="G8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>79360</v>
+        <v>71756</v>
       </c>
       <c r="H8" s="4">
         <f ca="1">IF(F8="CAD",G8,(G8*Currency!$B$2))</f>
-        <v>79360</v>
-      </c>
-      <c r="I8" s="2" t="e" cm="1" vm="2">
+        <v>71756</v>
+      </c>
+      <c r="I8" s="2" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">($E8 - _xlfn.STOCKHISTORY($A8, I$1,I$1,0,0,1))/$E8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J8" s="2" t="e" cm="1" vm="2">
+        <v>-9.6772395339762618E-2</v>
+      </c>
+      <c r="J8" s="2" cm="1">
         <f t="array" aca="1" ref="J8" ca="1">($E8 - _xlfn.STOCKHISTORY($A8, J$1,J$1,0,0,1))/$E8</f>
-        <v>#VALUE!</v>
+        <v>-0.10641618819332184</v>
       </c>
       <c r="K8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K8" ca="1">($E8 - _xlfn.STOCKHISTORY($A8, K$1,K$1,0,0,1))/$E8</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L8" s="2" t="e" cm="1" vm="2">
+      <c r="L8" s="2" cm="1">
         <f t="array" aca="1" ref="L8" ca="1">($E8 - _xlfn.STOCKHISTORY($A8, L$1,L$1,0,0,1))/$E8</f>
-        <v>#VALUE!</v>
+        <v>0.38809298177155915</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -4347,7 +7154,7 @@
       </c>
       <c r="E9" s="3" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">_FV(A9,"Price")</f>
-        <v>159.52000000000001</v>
+        <v>147.99</v>
       </c>
       <c r="F9" t="str" cm="1">
         <f t="array" aca="1" ref="F9" ca="1">_FV(A9,"Currency")</f>
@@ -4355,27 +7162,27 @@
       </c>
       <c r="G9" s="4">
         <f t="shared" ref="G9:G10" ca="1" si="3">D9*E9</f>
-        <v>79760</v>
+        <v>73995</v>
       </c>
       <c r="H9" s="4">
         <f ca="1">IF(F9="CAD",G9,(G9*Currency!$B$2))</f>
-        <v>79760</v>
-      </c>
-      <c r="I9" s="2" t="e" cm="1" vm="2">
+        <v>73995</v>
+      </c>
+      <c r="I9" s="2" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">($E9 - _xlfn.STOCKHISTORY($A9, I$1,I$1,0,0,1))/$E9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J9" s="2" t="e" cm="1" vm="2">
+        <v>-0.11183188053246829</v>
+      </c>
+      <c r="J9" s="2" cm="1">
         <f t="array" aca="1" ref="J9" ca="1">($E9 - _xlfn.STOCKHISTORY($A9, J$1,J$1,0,0,1))/$E9</f>
-        <v>#VALUE!</v>
+        <v>-0.11466991012906276</v>
       </c>
       <c r="K9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K9" ca="1">($E9 - _xlfn.STOCKHISTORY($A9, K$1,K$1,0,0,1))/$E9</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L9" s="2" t="e" cm="1" vm="2">
+      <c r="L9" s="2" cm="1">
         <f t="array" aca="1" ref="L9" ca="1">($E9 - _xlfn.STOCKHISTORY($A9, L$1,L$1,0,0,1))/$E9</f>
-        <v>#VALUE!</v>
+        <v>0.51537266031488616</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -4394,7 +7201,7 @@
       </c>
       <c r="E10" s="3" cm="1">
         <f t="array" aca="1" ref="E10" ca="1">_FV(A10,"Price")</f>
-        <v>187.98</v>
+        <v>225.32</v>
       </c>
       <c r="F10" t="str" cm="1">
         <f t="array" aca="1" ref="F10" ca="1">_FV(A10,"Currency")</f>
@@ -4402,27 +7209,27 @@
       </c>
       <c r="G10" s="4">
         <f t="shared" ca="1" si="3"/>
-        <v>37596</v>
+        <v>45064</v>
       </c>
       <c r="H10" s="4">
         <f ca="1">IF(F10="CAD",G10,(G10*Currency!$B$2))</f>
-        <v>51438.847200000004</v>
-      </c>
-      <c r="I10" s="2" t="e" cm="1" vm="2">
+        <v>61963</v>
+      </c>
+      <c r="I10" s="2" cm="1">
         <f t="array" aca="1" ref="I10" ca="1">($E10 - _xlfn.STOCKHISTORY($A10, I$1,I$1,0,0,1))/$E10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="2" t="e" cm="1" vm="2">
+        <v>2.6096218711166321E-2</v>
+      </c>
+      <c r="J10" s="2" cm="1">
         <f t="array" aca="1" ref="J10" ca="1">($E10 - _xlfn.STOCKHISTORY($A10, J$1,J$1,0,0,1))/$E10</f>
-        <v>#VALUE!</v>
+        <v>0.11969643174152317</v>
       </c>
       <c r="K10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K10" ca="1">($E10 - _xlfn.STOCKHISTORY($A10, K$1,K$1,0,0,1))/$E10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L10" s="2" t="e" cm="1" vm="2">
+      <c r="L10" s="2" cm="1">
         <f t="array" aca="1" ref="L10" ca="1">($E10 - _xlfn.STOCKHISTORY($A10, L$1,L$1,0,0,1))/$E10</f>
-        <v>#VALUE!</v>
+        <v>0.39907686845375462</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -4441,7 +7248,7 @@
       </c>
       <c r="E11" s="3" cm="1">
         <f t="array" aca="1" ref="E11" ca="1">_FV(A11,"Price")</f>
-        <v>200.12</v>
+        <v>424.1</v>
       </c>
       <c r="F11" t="str" cm="1">
         <f t="array" aca="1" ref="F11" ca="1">_FV(A11,"Currency")</f>
@@ -4449,27 +7256,27 @@
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G14" ca="1" si="4">D11*E11</f>
-        <v>40024</v>
+        <v>84820</v>
       </c>
       <c r="H11" s="4">
         <f ca="1">IF(F11="CAD",G11,(G11*Currency!$B$2))</f>
-        <v>54760.836800000005</v>
-      </c>
-      <c r="I11" s="2" t="e" cm="1" vm="2">
+        <v>116627.5</v>
+      </c>
+      <c r="I11" s="2" cm="1">
         <f t="array" aca="1" ref="I11" ca="1">($E11 - _xlfn.STOCKHISTORY($A11, I$1,I$1,0,0,1))/$E11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J11" s="2" t="e" cm="1" vm="2">
+        <v>-8.1796746050459793E-2</v>
+      </c>
+      <c r="J11" s="2" cm="1">
         <f t="array" aca="1" ref="J11" ca="1">($E11 - _xlfn.STOCKHISTORY($A11, J$1,J$1,0,0,1))/$E11</f>
-        <v>#VALUE!</v>
+        <v>0.34388116010374919</v>
       </c>
       <c r="K11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K11" ca="1">($E11 - _xlfn.STOCKHISTORY($A11, K$1,K$1,0,0,1))/$E11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L11" s="2" t="e" cm="1" vm="2">
+      <c r="L11" s="2" cm="1">
         <f t="array" aca="1" ref="L11" ca="1">($E11 - _xlfn.STOCKHISTORY($A11, L$1,L$1,0,0,1))/$E11</f>
-        <v>#VALUE!</v>
+        <v>0.72372082056118836</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -4488,7 +7295,7 @@
       </c>
       <c r="E12" s="3" cm="1">
         <f t="array" aca="1" ref="E12" ca="1">_FV(A12,"Price")</f>
-        <v>303.94</v>
+        <v>393.32</v>
       </c>
       <c r="F12" t="str" cm="1">
         <f t="array" aca="1" ref="F12" ca="1">_FV(A12,"Currency")</f>
@@ -4496,27 +7303,27 @@
       </c>
       <c r="G12" s="4">
         <f t="shared" ref="G12:G13" ca="1" si="5">D12*E12</f>
-        <v>45591</v>
+        <v>58998</v>
       </c>
       <c r="H12" s="4">
         <f ca="1">IF(F12="CAD",G12,(G12*Currency!$B$2))</f>
-        <v>62377.606200000002</v>
-      </c>
-      <c r="I12" s="2" t="e" cm="1" vm="2">
+        <v>81122.25</v>
+      </c>
+      <c r="I12" s="2" cm="1">
         <f t="array" aca="1" ref="I12" ca="1">($E12 - _xlfn.STOCKHISTORY($A12, I$1,I$1,0,0,1))/$E12</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J12" s="2" t="e" cm="1" vm="2">
+        <v>1.6653106884979181E-2</v>
+      </c>
+      <c r="J12" s="2" cm="1">
         <f t="array" aca="1" ref="J12" ca="1">($E12 - _xlfn.STOCKHISTORY($A12, J$1,J$1,0,0,1))/$E12</f>
-        <v>#VALUE!</v>
+        <v>0.15394589647106685</v>
       </c>
       <c r="K12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K12" ca="1">($E12 - _xlfn.STOCKHISTORY($A12, K$1,K$1,0,0,1))/$E12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L12" s="2" t="e" cm="1" vm="2">
+      <c r="L12" s="2" cm="1">
         <f t="array" aca="1" ref="L12" ca="1">($E12 - _xlfn.STOCKHISTORY($A12, L$1,L$1,0,0,1))/$E12</f>
-        <v>#VALUE!</v>
+        <v>0.57431607851113597</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -4535,7 +7342,7 @@
       </c>
       <c r="E13" s="3" cm="1">
         <f t="array" aca="1" ref="E13" ca="1">_FV(A13,"Price")</f>
-        <v>150.68</v>
+        <v>157.91999999999999</v>
       </c>
       <c r="F13" t="str" cm="1">
         <f t="array" aca="1" ref="F13" ca="1">_FV(A13,"Currency")</f>
@@ -4543,27 +7350,27 @@
       </c>
       <c r="G13" s="4">
         <f t="shared" ca="1" si="5"/>
-        <v>30136</v>
+        <v>31583.999999999996</v>
       </c>
       <c r="H13" s="4">
         <f ca="1">IF(F13="CAD",G13,(G13*Currency!$B$2))</f>
-        <v>41232.075199999999</v>
-      </c>
-      <c r="I13" s="2" t="e" cm="1" vm="2">
+        <v>43427.999999999993</v>
+      </c>
+      <c r="I13" s="2" cm="1">
         <f t="array" aca="1" ref="I13" ca="1">($E13 - _xlfn.STOCKHISTORY($A13, I$1,I$1,0,0,1))/$E13</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J13" s="2" t="e" cm="1" vm="2">
+        <v>5.2178318135764824E-2</v>
+      </c>
+      <c r="J13" s="2" cm="1">
         <f t="array" aca="1" ref="J13" ca="1">($E13 - _xlfn.STOCKHISTORY($A13, J$1,J$1,0,0,1))/$E13</f>
-        <v>#VALUE!</v>
+        <v>3.7613981762917921E-2</v>
       </c>
       <c r="K13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K13" ca="1">($E13 - _xlfn.STOCKHISTORY($A13, K$1,K$1,0,0,1))/$E13</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L13" s="2" t="e" cm="1" vm="2">
+      <c r="L13" s="2" cm="1">
         <f t="array" aca="1" ref="L13" ca="1">($E13 - _xlfn.STOCKHISTORY($A13, L$1,L$1,0,0,1))/$E13</f>
-        <v>#VALUE!</v>
+        <v>0.31490628166160078</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -4582,7 +7389,7 @@
       </c>
       <c r="E14" s="3" cm="1">
         <f t="array" aca="1" ref="E14" ca="1">_FV(A14,"Price")</f>
-        <v>183.87</v>
+        <v>191.1</v>
       </c>
       <c r="F14" t="str" cm="1">
         <f t="array" aca="1" ref="F14" ca="1">_FV(A14,"Currency")</f>
@@ -4590,27 +7397,27 @@
       </c>
       <c r="G14" s="4">
         <f t="shared" ca="1" si="4"/>
-        <v>36774</v>
+        <v>38220</v>
       </c>
       <c r="H14" s="4">
         <f ca="1">IF(F14="CAD",G14,(G14*Currency!$B$2))</f>
-        <v>50314.186800000003</v>
-      </c>
-      <c r="I14" s="2" t="e" cm="1" vm="2">
+        <v>52552.5</v>
+      </c>
+      <c r="I14" s="2" cm="1">
         <f t="array" aca="1" ref="I14" ca="1">($E14 - _xlfn.STOCKHISTORY($A14, I$1,I$1,0,0,1))/$E14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J14" s="2" t="e" cm="1" vm="2">
+        <v>3.3281004709576061E-2</v>
+      </c>
+      <c r="J14" s="2" cm="1">
         <f t="array" aca="1" ref="J14" ca="1">($E14 - _xlfn.STOCKHISTORY($A14, J$1,J$1,0,0,1))/$E14</f>
-        <v>#VALUE!</v>
+        <v>1.5436944008372521E-2</v>
       </c>
       <c r="K14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K14" ca="1">($E14 - _xlfn.STOCKHISTORY($A14, K$1,K$1,0,0,1))/$E14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L14" s="2" t="e" cm="1" vm="2">
+      <c r="L14" s="2" cm="1">
         <f t="array" aca="1" ref="L14" ca="1">($E14 - _xlfn.STOCKHISTORY($A14, L$1,L$1,0,0,1))/$E14</f>
-        <v>#VALUE!</v>
+        <v>0.25641025641025644</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -4629,7 +7436,7 @@
       </c>
       <c r="E15" s="3" cm="1">
         <f t="array" aca="1" ref="E15" ca="1">_FV(A15,"Price")</f>
-        <v>37.54</v>
+        <v>44.82</v>
       </c>
       <c r="F15" t="str" cm="1">
         <f t="array" aca="1" ref="F15" ca="1">_FV(A15,"Currency")</f>
@@ -4637,27 +7444,27 @@
       </c>
       <c r="G15" s="4">
         <f t="shared" ref="G15:G16" ca="1" si="6">D15*E15</f>
-        <v>37540</v>
+        <v>44820</v>
       </c>
       <c r="H15" s="4">
         <f ca="1">IF(F15="CAD",G15,(G15*Currency!$B$2))</f>
-        <v>51362.228000000003</v>
-      </c>
-      <c r="I15" s="2" t="e" cm="1" vm="2">
+        <v>61627.5</v>
+      </c>
+      <c r="I15" s="2" cm="1">
         <f t="array" aca="1" ref="I15" ca="1">($E15 - _xlfn.STOCKHISTORY($A15, I$1,I$1,0,0,1))/$E15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J15" s="2" t="e" cm="1" vm="2">
+        <v>-3.6813922356090996E-2</v>
+      </c>
+      <c r="J15" s="2" cm="1">
         <f t="array" aca="1" ref="J15" ca="1">($E15 - _xlfn.STOCKHISTORY($A15, J$1,J$1,0,0,1))/$E15</f>
-        <v>#VALUE!</v>
+        <v>4.6630968317715384E-2</v>
       </c>
       <c r="K15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K15" ca="1">($E15 - _xlfn.STOCKHISTORY($A15, K$1,K$1,0,0,1))/$E15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L15" s="2" t="e" cm="1" vm="2">
+      <c r="L15" s="2" cm="1">
         <f t="array" aca="1" ref="L15" ca="1">($E15 - _xlfn.STOCKHISTORY($A15, L$1,L$1,0,0,1))/$E15</f>
-        <v>#VALUE!</v>
+        <v>-0.32083891120035701</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -4676,7 +7483,7 @@
       </c>
       <c r="E16" s="3" cm="1">
         <f t="array" aca="1" ref="E16" ca="1">_FV(A16,"Price")</f>
-        <v>14.63</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="F16" t="str" cm="1">
         <f t="array" aca="1" ref="F16" ca="1">_FV(A16,"Currency")</f>
@@ -4684,27 +7491,27 @@
       </c>
       <c r="G16" s="4">
         <f t="shared" ca="1" si="6"/>
-        <v>7315</v>
+        <v>8380</v>
       </c>
       <c r="H16" s="4">
         <f ca="1">IF(F16="CAD",G16,(G16*Currency!$B$2))</f>
-        <v>10008.383</v>
-      </c>
-      <c r="I16" s="2" t="e" cm="1" vm="2">
+        <v>11522.5</v>
+      </c>
+      <c r="I16" s="2" cm="1">
         <f t="array" aca="1" ref="I16" ca="1">($E16 - _xlfn.STOCKHISTORY($A16, I$1,I$1,0,0,1))/$E16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J16" s="2" t="e" cm="1" vm="2">
+        <v>-5.4295942720763726E-2</v>
+      </c>
+      <c r="J16" s="2" cm="1">
         <f t="array" aca="1" ref="J16" ca="1">($E16 - _xlfn.STOCKHISTORY($A16, J$1,J$1,0,0,1))/$E16</f>
-        <v>#VALUE!</v>
+        <v>-6.3245823389021391E-2</v>
       </c>
       <c r="K16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="K16" ca="1">($E16 - _xlfn.STOCKHISTORY($A16, K$1,K$1,0,0,1))/$E16</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L16" s="2" t="e" cm="1" vm="2">
+      <c r="L16" s="2" cm="1">
         <f t="array" aca="1" ref="L16" ca="1">($E16 - _xlfn.STOCKHISTORY($A16, L$1,L$1,0,0,1))/$E16</f>
-        <v>#VALUE!</v>
+        <v>-0.17243436754176591</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
@@ -4754,7 +7561,7 @@
       </c>
       <c r="H18" s="4">
         <f ca="1">IF(F18="CAD",G18,(G18*Currency!$B$2))</f>
-        <v>4104.6000000000004</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4810,7 +7617,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="H21" s="4">
         <f ca="1">SUM(H2:H20)</f>
-        <v>999036.89462000004</v>
+        <v>1095041.25</v>
       </c>
     </row>
   </sheetData>
@@ -4936,19 +7743,19 @@
       </c>
       <c r="O1" s="8">
         <f ca="1">WORKDAY(TODAY(),-5)</f>
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="P1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-1),-1)</f>
-        <v>46107</v>
+        <v>46128</v>
       </c>
       <c r="Q1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-3),-1)</f>
-        <v>46048</v>
+        <v>46069</v>
       </c>
       <c r="R1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-12),-1)</f>
-        <v>45772</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
@@ -4976,7 +7783,7 @@
       </c>
       <c r="H2" s="3" cm="1">
         <f t="array" aca="1" ref="H2" ca="1">_FV(A2,"Price")</f>
-        <v>62.55</v>
+        <v>63.01</v>
       </c>
       <c r="I2" t="str" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">_FV(A2,"Currency")</f>
@@ -4999,23 +7806,23 @@
       </c>
       <c r="N2" s="9">
         <f ca="1">IF(I2="CAD",M2,(M2*Currency!$B$2))</f>
-        <v>246276.00000000003</v>
-      </c>
-      <c r="O2" s="2" t="e" cm="1" vm="2">
+        <v>247500</v>
+      </c>
+      <c r="O2" s="2" cm="1">
         <f t="array" aca="1" ref="O2" ca="1">($H2 - _xlfn.STOCKHISTORY($A2, O$1,O$1,0,0,1))/$H2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P2" s="2" t="e" cm="1" vm="2">
+        <v>-2.1583875575305611E-2</v>
+      </c>
+      <c r="P2" s="2" cm="1">
         <f t="array" aca="1" ref="P2" ca="1">(H2 - _xlfn.STOCKHISTORY($A2, P$1,P$1,0,0,1))/$H2</f>
-        <v>#VALUE!</v>
+        <v>-8.3637517854308896E-2</v>
       </c>
       <c r="Q2" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q2" ca="1">($H2 - _xlfn.STOCKHISTORY($A2, Q$1,Q$1,0,0,1))/$H2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R2" s="2" t="e" cm="1" vm="2">
+      <c r="R2" s="2" cm="1">
         <f t="array" aca="1" ref="R2" ca="1">($H2 - _xlfn.STOCKHISTORY($A2, R$1,R$1,0,0,1))/$H2</f>
-        <v>#VALUE!</v>
+        <v>0.39660371369623865</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
@@ -5043,7 +7850,7 @@
       </c>
       <c r="H3" s="3" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">_FV(A3,"Price")</f>
-        <v>62.55</v>
+        <v>63.01</v>
       </c>
       <c r="I3" t="str" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">_FV(A3,"Currency")</f>
@@ -5069,21 +7876,21 @@
         <f ca="1">IF(I3="CAD",M3,(M3*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O3" s="2" t="e" cm="1" vm="2">
+      <c r="O3" s="2" cm="1">
         <f t="array" aca="1" ref="O3" ca="1">($H3 - _xlfn.STOCKHISTORY($A3, O$1,O$1,0,0,1))/$H3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P3" s="2" t="e" cm="1" vm="2">
+        <v>-2.1583875575305611E-2</v>
+      </c>
+      <c r="P3" s="2" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">(H3 - _xlfn.STOCKHISTORY($A3, P$1,P$1,0,0,1))/$H3</f>
-        <v>#VALUE!</v>
+        <v>-8.3637517854308896E-2</v>
       </c>
       <c r="Q3" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q3" ca="1">($H3 - _xlfn.STOCKHISTORY($A3, Q$1,Q$1,0,0,1))/$H3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="2" t="e" cm="1" vm="2">
+      <c r="R3" s="2" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">($H3 - _xlfn.STOCKHISTORY($A3, R$1,R$1,0,0,1))/$H3</f>
-        <v>#VALUE!</v>
+        <v>0.39660371369623865</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -5111,7 +7918,7 @@
       </c>
       <c r="H4" s="3" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">_FV(A4,"Price")</f>
-        <v>22.02</v>
+        <v>17.64</v>
       </c>
       <c r="I4" t="str" cm="1">
         <f t="array" aca="1" ref="I4" ca="1">_FV(A4,"Currency")</f>
@@ -5119,11 +7926,11 @@
       </c>
       <c r="J4" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-21799.999999999996</v>
       </c>
       <c r="K4" s="9">
         <f ca="1">IF(I4="CAD",J4,(J4*Currency!$B$2))</f>
-        <v>0</v>
+        <v>-29974.999999999996</v>
       </c>
       <c r="L4" s="5">
         <v>18</v>
@@ -5134,23 +7941,23 @@
       </c>
       <c r="N4" s="9">
         <f ca="1">IF(I4="CAD",M4,(M4*Currency!$B$2))</f>
-        <v>123138.00000000001</v>
-      </c>
-      <c r="O4" s="2" t="e" cm="1" vm="2">
+        <v>123750</v>
+      </c>
+      <c r="O4" s="2" cm="1">
         <f t="array" aca="1" ref="O4" ca="1">($H4 - _xlfn.STOCKHISTORY($A4, O$1,O$1,0,0,1))/$H4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P4" s="2" t="e" cm="1" vm="2">
+        <v>-0.17176870748299325</v>
+      </c>
+      <c r="P4" s="2" cm="1">
         <f t="array" aca="1" ref="P4" ca="1">(H4 - _xlfn.STOCKHISTORY($A4, P$1,P$1,0,0,1))/$H4</f>
-        <v>#VALUE!</v>
+        <v>-8.3333333333333259E-2</v>
       </c>
       <c r="Q4" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q4" ca="1">($H4 - _xlfn.STOCKHISTORY($A4, Q$1,Q$1,0,0,1))/$H4</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R4" s="2" t="e" cm="1" vm="2">
+      <c r="R4" s="2" cm="1">
         <f t="array" aca="1" ref="R4" ca="1">($H4 - _xlfn.STOCKHISTORY($A4, R$1,R$1,0,0,1))/$H4</f>
-        <v>#VALUE!</v>
+        <v>0.723922902494331</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
@@ -5178,7 +7985,7 @@
       </c>
       <c r="H5" s="3" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">_FV(A5,"Price")</f>
-        <v>22.02</v>
+        <v>17.64</v>
       </c>
       <c r="I5" t="str" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">_FV(A5,"Currency")</f>
@@ -5186,11 +7993,11 @@
       </c>
       <c r="J5" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>14950.000000000002</v>
+        <v>25900</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">IF(I5="CAD",J5,(J5*Currency!$B$2))</f>
-        <v>20454.590000000004</v>
+        <v>35612.5</v>
       </c>
       <c r="L5" s="5">
         <f>IF(E5="PUT",IF(G5&lt;0,-F5*G5,0),0)</f>
@@ -5204,21 +8011,21 @@
         <f ca="1">IF(I5="CAD",M5,(M5*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O5" s="2" t="e" cm="1" vm="2">
+      <c r="O5" s="2" cm="1">
         <f t="array" aca="1" ref="O5" ca="1">($H5 - _xlfn.STOCKHISTORY($A5, O$1,O$1,0,0,1))/$H5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P5" s="2" t="e" cm="1" vm="2">
+        <v>-0.17176870748299325</v>
+      </c>
+      <c r="P5" s="2" cm="1">
         <f t="array" aca="1" ref="P5" ca="1">(H5 - _xlfn.STOCKHISTORY($A5, P$1,P$1,0,0,1))/$H5</f>
-        <v>#VALUE!</v>
+        <v>-8.3333333333333259E-2</v>
       </c>
       <c r="Q5" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q5" ca="1">($H5 - _xlfn.STOCKHISTORY($A5, Q$1,Q$1,0,0,1))/$H5</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R5" s="2" t="e" cm="1" vm="2">
+      <c r="R5" s="2" cm="1">
         <f t="array" aca="1" ref="R5" ca="1">($H5 - _xlfn.STOCKHISTORY($A5, R$1,R$1,0,0,1))/$H5</f>
-        <v>#VALUE!</v>
+        <v>0.723922902494331</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -5246,7 +8053,7 @@
       </c>
       <c r="H6" s="3" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">_FV(A6,"Price")</f>
-        <v>70.09</v>
+        <v>69.040000000000006</v>
       </c>
       <c r="I6" t="str" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">_FV(A6,"Currency")</f>
@@ -5269,23 +8076,23 @@
       </c>
       <c r="N6" s="9">
         <f ca="1">IF(I6="CAD",M6,(M6*Currency!$B$2))</f>
-        <v>379675.5</v>
-      </c>
-      <c r="O6" s="2" t="e" cm="1" vm="2">
+        <v>381562.5</v>
+      </c>
+      <c r="O6" s="2" cm="1">
         <f t="array" aca="1" ref="O6" ca="1">($H6 - _xlfn.STOCKHISTORY($A6, O$1,O$1,0,0,1))/$H6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P6" s="2" t="e" cm="1" vm="2">
+        <v>-0.12977983777520269</v>
+      </c>
+      <c r="P6" s="2" cm="1">
         <f t="array" aca="1" ref="P6" ca="1">(H6 - _xlfn.STOCKHISTORY($A6, P$1,P$1,0,0,1))/$H6</f>
-        <v>#VALUE!</v>
+        <v>-3.1865585168018372E-2</v>
       </c>
       <c r="Q6" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q6" ca="1">($H6 - _xlfn.STOCKHISTORY($A6, Q$1,Q$1,0,0,1))/$H6</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R6" s="2" t="e" cm="1" vm="2">
+      <c r="R6" s="2" cm="1">
         <f t="array" aca="1" ref="R6" ca="1">($H6 - _xlfn.STOCKHISTORY($A6, R$1,R$1,0,0,1))/$H6</f>
-        <v>#VALUE!</v>
+        <v>0.57560834298957131</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -5313,7 +8120,7 @@
       </c>
       <c r="H7" s="3" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">_FV(A7,"Price")</f>
-        <v>70.09</v>
+        <v>69.040000000000006</v>
       </c>
       <c r="I7" t="str" cm="1">
         <f t="array" aca="1" ref="I7" ca="1">_FV(A7,"Currency")</f>
@@ -5321,11 +8128,11 @@
       </c>
       <c r="J7" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>2399.9999999999845</v>
       </c>
       <c r="K7" s="9">
         <f ca="1">IF(I7="CAD",J7,(J7*Currency!$B$2))</f>
-        <v>0</v>
+        <v>3299.9999999999786</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -5338,21 +8145,21 @@
         <f ca="1">IF(I7="CAD",M7,(M7*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="2" t="e" cm="1" vm="2">
+      <c r="O7" s="2" cm="1">
         <f t="array" aca="1" ref="O7" ca="1">($H7 - _xlfn.STOCKHISTORY($A7, O$1,O$1,0,0,1))/$H7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P7" s="2" t="e" cm="1" vm="2">
+        <v>-0.12977983777520269</v>
+      </c>
+      <c r="P7" s="2" cm="1">
         <f t="array" aca="1" ref="P7" ca="1">(H7 - _xlfn.STOCKHISTORY($A7, P$1,P$1,0,0,1))/$H7</f>
-        <v>#VALUE!</v>
+        <v>-3.1865585168018372E-2</v>
       </c>
       <c r="Q7" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q7" ca="1">($H7 - _xlfn.STOCKHISTORY($A7, Q$1,Q$1,0,0,1))/$H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R7" s="2" t="e" cm="1" vm="2">
+      <c r="R7" s="2" cm="1">
         <f t="array" aca="1" ref="R7" ca="1">($H7 - _xlfn.STOCKHISTORY($A7, R$1,R$1,0,0,1))/$H7</f>
-        <v>#VALUE!</v>
+        <v>0.57560834298957131</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
@@ -5380,7 +8187,7 @@
       </c>
       <c r="H8" s="3" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">_FV(A8,"Price")</f>
-        <v>264.35000000000002</v>
+        <v>300.23</v>
       </c>
       <c r="I8" t="str" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">_FV(A8,"Currency")</f>
@@ -5405,21 +8212,21 @@
         <f ca="1">IF(I8="CAD",M8,(M8*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="2" t="e" cm="1" vm="2">
+      <c r="O8" s="2" cm="1">
         <f t="array" aca="1" ref="O8" ca="1">($H8 - _xlfn.STOCKHISTORY($A8, O$1,O$1,0,0,1))/$H8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P8" s="2" t="e" cm="1" vm="2">
+        <v>2.5147387003297508E-2</v>
+      </c>
+      <c r="P8" s="2" cm="1">
         <f t="array" aca="1" ref="P8" ca="1">(H8 - _xlfn.STOCKHISTORY($A8, P$1,P$1,0,0,1))/$H8</f>
-        <v>#VALUE!</v>
+        <v>0.12267261765979429</v>
       </c>
       <c r="Q8" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q8" ca="1">($H8 - _xlfn.STOCKHISTORY($A8, Q$1,Q$1,0,0,1))/$H8</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R8" s="2" t="e" cm="1" vm="2">
+      <c r="R8" s="2" cm="1">
         <f t="array" aca="1" ref="R8" ca="1">($H8 - _xlfn.STOCKHISTORY($A8, R$1,R$1,0,0,1))/$H8</f>
-        <v>#VALUE!</v>
+        <v>0.2963394730706459</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
@@ -5447,7 +8254,7 @@
       </c>
       <c r="H9" s="3" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">_FV(A9,"Price")</f>
-        <v>264.35000000000002</v>
+        <v>300.23</v>
       </c>
       <c r="I9" t="str" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">_FV(A9,"Currency")</f>
@@ -5470,23 +8277,23 @@
       </c>
       <c r="N9" s="9">
         <f ca="1">IF(I9="CAD",M9,(M9*Currency!$B$2))</f>
-        <v>246276.00000000003</v>
-      </c>
-      <c r="O9" s="2" t="e" cm="1" vm="2">
+        <v>247500</v>
+      </c>
+      <c r="O9" s="2" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">($H9 - _xlfn.STOCKHISTORY($A9, O$1,O$1,0,0,1))/$H9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P9" s="2" t="e" cm="1" vm="2">
+        <v>2.5147387003297508E-2</v>
+      </c>
+      <c r="P9" s="2" cm="1">
         <f t="array" aca="1" ref="P9" ca="1">(H9 - _xlfn.STOCKHISTORY($A9, P$1,P$1,0,0,1))/$H9</f>
-        <v>#VALUE!</v>
+        <v>0.12267261765979429</v>
       </c>
       <c r="Q9" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q9" ca="1">($H9 - _xlfn.STOCKHISTORY($A9, Q$1,Q$1,0,0,1))/$H9</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R9" s="2" t="e" cm="1" vm="2">
+      <c r="R9" s="2" cm="1">
         <f t="array" aca="1" ref="R9" ca="1">($H9 - _xlfn.STOCKHISTORY($A9, R$1,R$1,0,0,1))/$H9</f>
-        <v>#VALUE!</v>
+        <v>0.2963394730706459</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
@@ -5514,7 +8321,7 @@
       </c>
       <c r="H10" s="3" cm="1">
         <f t="array" aca="1" ref="H10" ca="1">_FV(A10,"Price")</f>
-        <v>264.35000000000002</v>
+        <v>300.23</v>
       </c>
       <c r="I10" t="str" cm="1">
         <f t="array" aca="1" ref="I10" ca="1">_FV(A10,"Currency")</f>
@@ -5539,21 +8346,21 @@
         <f ca="1">IF(I10="CAD",M10,(M10*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O10" s="2" t="e" cm="1" vm="2">
+      <c r="O10" s="2" cm="1">
         <f t="array" aca="1" ref="O10" ca="1">($H10 - _xlfn.STOCKHISTORY($A10, O$1,O$1,0,0,1))/$H10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P10" s="2" t="e" cm="1" vm="2">
+        <v>2.5147387003297508E-2</v>
+      </c>
+      <c r="P10" s="2" cm="1">
         <f t="array" aca="1" ref="P10" ca="1">(H10 - _xlfn.STOCKHISTORY($A10, P$1,P$1,0,0,1))/$H10</f>
-        <v>#VALUE!</v>
+        <v>0.12267261765979429</v>
       </c>
       <c r="Q10" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q10" ca="1">($H10 - _xlfn.STOCKHISTORY($A10, Q$1,Q$1,0,0,1))/$H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R10" s="2" t="e" cm="1" vm="2">
+      <c r="R10" s="2" cm="1">
         <f t="array" aca="1" ref="R10" ca="1">($H10 - _xlfn.STOCKHISTORY($A10, R$1,R$1,0,0,1))/$H10</f>
-        <v>#VALUE!</v>
+        <v>0.2963394730706459</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -5581,7 +8388,7 @@
       </c>
       <c r="H11" s="3" cm="1">
         <f t="array" aca="1" ref="H11" ca="1">_FV(A11,"Price")</f>
-        <v>58.01</v>
+        <v>56.4</v>
       </c>
       <c r="I11" t="str" cm="1">
         <f t="array" aca="1" ref="I11" ca="1">_FV(A11,"Currency")</f>
@@ -5606,21 +8413,21 @@
         <f ca="1">IF(I11="CAD",M11,(M11*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O11" s="2" t="e" cm="1" vm="2">
+      <c r="O11" s="2" cm="1">
         <f t="array" aca="1" ref="O11" ca="1">($H11 - _xlfn.STOCKHISTORY($A11, O$1,O$1,0,0,1))/$H11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P11" s="2" t="e" cm="1" vm="2">
+        <v>-0.10443262411347519</v>
+      </c>
+      <c r="P11" s="2" cm="1">
         <f t="array" aca="1" ref="P11" ca="1">(H11 - _xlfn.STOCKHISTORY($A11, P$1,P$1,0,0,1))/$H11</f>
-        <v>#VALUE!</v>
+        <v>-1.950354609929068E-3</v>
       </c>
       <c r="Q11" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q11" ca="1">($H11 - _xlfn.STOCKHISTORY($A11, Q$1,Q$1,0,0,1))/$H11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R11" s="2" t="e" cm="1" vm="2">
+      <c r="R11" s="2" cm="1">
         <f t="array" aca="1" ref="R11" ca="1">($H11 - _xlfn.STOCKHISTORY($A11, R$1,R$1,0,0,1))/$H11</f>
-        <v>#VALUE!</v>
+        <v>0.59680851063829787</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
@@ -5648,7 +8455,7 @@
       </c>
       <c r="H12" s="3" cm="1">
         <f t="array" aca="1" ref="H12" ca="1">_FV(A12,"Price")</f>
-        <v>58.01</v>
+        <v>56.4</v>
       </c>
       <c r="I12" t="str" cm="1">
         <f t="array" aca="1" ref="I12" ca="1">_FV(A12,"Currency")</f>
@@ -5671,23 +8478,23 @@
       </c>
       <c r="N12" s="9">
         <f ca="1">IF(I12="CAD",M12,(M12*Currency!$B$2))</f>
-        <v>547280</v>
-      </c>
-      <c r="O12" s="2" t="e" cm="1" vm="2">
+        <v>550000</v>
+      </c>
+      <c r="O12" s="2" cm="1">
         <f t="array" aca="1" ref="O12" ca="1">($H12 - _xlfn.STOCKHISTORY($A12, O$1,O$1,0,0,1))/$H12</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P12" s="2" t="e" cm="1" vm="2">
+        <v>-0.10443262411347519</v>
+      </c>
+      <c r="P12" s="2" cm="1">
         <f t="array" aca="1" ref="P12" ca="1">(H12 - _xlfn.STOCKHISTORY($A12, P$1,P$1,0,0,1))/$H12</f>
-        <v>#VALUE!</v>
+        <v>-1.950354609929068E-3</v>
       </c>
       <c r="Q12" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q12" ca="1">($H12 - _xlfn.STOCKHISTORY($A12, Q$1,Q$1,0,0,1))/$H12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R12" s="2" t="e" cm="1" vm="2">
+      <c r="R12" s="2" cm="1">
         <f t="array" aca="1" ref="R12" ca="1">($H12 - _xlfn.STOCKHISTORY($A12, R$1,R$1,0,0,1))/$H12</f>
-        <v>#VALUE!</v>
+        <v>0.59680851063829787</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -5715,7 +8522,7 @@
       </c>
       <c r="H13" s="3" cm="1">
         <f t="array" aca="1" ref="H13" ca="1">_FV(A13,"Price")</f>
-        <v>686.24</v>
+        <v>739.17</v>
       </c>
       <c r="I13" t="str" cm="1">
         <f t="array" aca="1" ref="I13" ca="1">_FV(A13,"Currency")</f>
@@ -5740,21 +8547,21 @@
         <f ca="1">IF(I13="CAD",M13,(M13*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O13" s="2" t="e" cm="1" vm="2">
+      <c r="O13" s="2" cm="1">
         <f t="array" aca="1" ref="O13" ca="1">($H13 - _xlfn.STOCKHISTORY($A13, O$1,O$1,0,0,1))/$H13</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P13" s="2" t="e" cm="1" vm="2">
+        <v>-1.7587293856622356E-4</v>
+      </c>
+      <c r="P13" s="2" cm="1">
         <f t="array" aca="1" ref="P13" ca="1">(H13 - _xlfn.STOCKHISTORY($A13, P$1,P$1,0,0,1))/$H13</f>
-        <v>#VALUE!</v>
+        <v>5.0746107120148265E-2</v>
       </c>
       <c r="Q13" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q13" ca="1">($H13 - _xlfn.STOCKHISTORY($A13, Q$1,Q$1,0,0,1))/$H13</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R13" s="2" t="e" cm="1" vm="2">
+      <c r="R13" s="2" cm="1">
         <f t="array" aca="1" ref="R13" ca="1">($H13 - _xlfn.STOCKHISTORY($A13, R$1,R$1,0,0,1))/$H13</f>
-        <v>#VALUE!</v>
+        <v>0.19612538387651005</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -5782,7 +8589,7 @@
       </c>
       <c r="H14" s="3" cm="1">
         <f t="array" aca="1" ref="H14" ca="1">_FV(A14,"Price")</f>
-        <v>686.24</v>
+        <v>739.17</v>
       </c>
       <c r="I14" t="str" cm="1">
         <f t="array" aca="1" ref="I14" ca="1">_FV(A14,"Currency")</f>
@@ -5807,21 +8614,21 @@
         <f ca="1">IF(I14="CAD",M14,(M14*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O14" s="2" t="e" cm="1" vm="2">
+      <c r="O14" s="2" cm="1">
         <f t="array" aca="1" ref="O14" ca="1">($H14 - _xlfn.STOCKHISTORY($A14, O$1,O$1,0,0,1))/$H14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P14" s="2" t="e" cm="1" vm="2">
+        <v>-1.7587293856622356E-4</v>
+      </c>
+      <c r="P14" s="2" cm="1">
         <f t="array" aca="1" ref="P14" ca="1">(H14 - _xlfn.STOCKHISTORY($A14, P$1,P$1,0,0,1))/$H14</f>
-        <v>#VALUE!</v>
+        <v>5.0746107120148265E-2</v>
       </c>
       <c r="Q14" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q14" ca="1">($H14 - _xlfn.STOCKHISTORY($A14, Q$1,Q$1,0,0,1))/$H14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R14" s="2" t="e" cm="1" vm="2">
+      <c r="R14" s="2" cm="1">
         <f t="array" aca="1" ref="R14" ca="1">($H14 - _xlfn.STOCKHISTORY($A14, R$1,R$1,0,0,1))/$H14</f>
-        <v>#VALUE!</v>
+        <v>0.19612538387651005</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="26" x14ac:dyDescent="0.35">
@@ -5849,7 +8656,7 @@
       </c>
       <c r="H15" s="3" cm="1">
         <f t="array" aca="1" ref="H15" ca="1">_FV(A15,"Price")</f>
-        <v>117.38</v>
+        <v>114.06</v>
       </c>
       <c r="I15" t="str" cm="1">
         <f t="array" aca="1" ref="I15" ca="1">_FV(A15,"Currency")</f>
@@ -5857,11 +8664,11 @@
       </c>
       <c r="J15" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>-262.00000000000045</v>
+        <v>-593.99999999999977</v>
       </c>
       <c r="K15" s="9">
         <f ca="1">IF(I15="CAD",J15,(J15*Currency!$B$2))</f>
-        <v>-262.00000000000045</v>
+        <v>-593.99999999999977</v>
       </c>
       <c r="L15" s="5">
         <v>120</v>
@@ -5874,21 +8681,21 @@
         <f ca="1">IF(I15="CAD",M15,(M15*Currency!$B$2))</f>
         <v>12000</v>
       </c>
-      <c r="O15" s="2" t="e" cm="1" vm="2">
+      <c r="O15" s="2" cm="1">
         <f t="array" aca="1" ref="O15" ca="1">($H15 - _xlfn.STOCKHISTORY($A15, O$1,O$1,0,0,1))/$H15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P15" s="2" t="e" cm="1" vm="2">
+        <v>-6.9787830966158107E-2</v>
+      </c>
+      <c r="P15" s="2" cm="1">
         <f t="array" aca="1" ref="P15" ca="1">(H15 - _xlfn.STOCKHISTORY($A15, P$1,P$1,0,0,1))/$H15</f>
-        <v>#VALUE!</v>
+        <v>-0.11827108539365241</v>
       </c>
       <c r="Q15" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q15" ca="1">($H15 - _xlfn.STOCKHISTORY($A15, Q$1,Q$1,0,0,1))/$H15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R15" s="2" t="e" cm="1" vm="2">
+      <c r="R15" s="2" cm="1">
         <f t="array" aca="1" ref="R15" ca="1">($H15 - _xlfn.STOCKHISTORY($A15, R$1,R$1,0,0,1))/$H15</f>
-        <v>#VALUE!</v>
+        <v>-1.3456952481150273</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -5916,7 +8723,7 @@
       </c>
       <c r="H16" s="3" cm="1">
         <f t="array" aca="1" ref="H16" ca="1">_FV(A16,"Price")</f>
-        <v>411.32</v>
+        <v>422.24</v>
       </c>
       <c r="I16" t="str" cm="1">
         <f t="array" aca="1" ref="I16" ca="1">_FV(A16,"Currency")</f>
@@ -5941,21 +8748,21 @@
         <f ca="1">IF(I16="CAD",M16,(M16*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O16" s="2" t="e" cm="1" vm="2">
+      <c r="O16" s="2" cm="1">
         <f t="array" aca="1" ref="O16" ca="1">($H16 - _xlfn.STOCKHISTORY($A16, O$1,O$1,0,0,1))/$H16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P16" s="2" t="e" cm="1" vm="2">
+        <v>-5.3902993558165947E-2</v>
+      </c>
+      <c r="P16" s="2" cm="1">
         <f t="array" aca="1" ref="P16" ca="1">(H16 - _xlfn.STOCKHISTORY($A16, P$1,P$1,0,0,1))/$H16</f>
-        <v>#VALUE!</v>
+        <v>7.8959833270178165E-2</v>
       </c>
       <c r="Q16" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q16" ca="1">($H16 - _xlfn.STOCKHISTORY($A16, Q$1,Q$1,0,0,1))/$H16</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R16" s="2" t="e" cm="1" vm="2">
+      <c r="R16" s="2" cm="1">
         <f t="array" aca="1" ref="R16" ca="1">($H16 - _xlfn.STOCKHISTORY($A16, R$1,R$1,0,0,1))/$H16</f>
-        <v>#VALUE!</v>
+        <v>0.17113489958317543</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
@@ -5983,7 +8790,7 @@
       </c>
       <c r="H17" s="3" cm="1">
         <f t="array" aca="1" ref="H17" ca="1">_FV(A17,"Price")</f>
-        <v>411.32</v>
+        <v>422.24</v>
       </c>
       <c r="I17" t="str" cm="1">
         <f t="array" aca="1" ref="I17" ca="1">_FV(A17,"Currency")</f>
@@ -6008,21 +8815,21 @@
         <f ca="1">IF(I17="CAD",M17,(M17*Currency!$B$2))</f>
         <v>0</v>
       </c>
-      <c r="O17" s="2" t="e" cm="1" vm="2">
+      <c r="O17" s="2" cm="1">
         <f t="array" aca="1" ref="O17" ca="1">($H17 - _xlfn.STOCKHISTORY($A17, O$1,O$1,0,0,1))/$H17</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P17" s="2" t="e" cm="1" vm="2">
+        <v>-5.3902993558165947E-2</v>
+      </c>
+      <c r="P17" s="2" cm="1">
         <f t="array" aca="1" ref="P17" ca="1">(H17 - _xlfn.STOCKHISTORY($A17, P$1,P$1,0,0,1))/$H17</f>
-        <v>#VALUE!</v>
+        <v>7.8959833270178165E-2</v>
       </c>
       <c r="Q17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="Q17" ca="1">($H17 - _xlfn.STOCKHISTORY($A17, Q$1,Q$1,0,0,1))/$H17</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R17" s="2" t="e" cm="1" vm="2">
+      <c r="R17" s="2" cm="1">
         <f t="array" aca="1" ref="R17" ca="1">($H17 - _xlfn.STOCKHISTORY($A17, R$1,R$1,0,0,1))/$H17</f>
-        <v>#VALUE!</v>
+        <v>0.17113489958317543</v>
       </c>
     </row>
   </sheetData>
@@ -6123,35 +8930,35 @@
       </c>
       <c r="D1" s="8">
         <f ca="1">WORKDAY(TODAY(),-5)</f>
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="E1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-1),-1)</f>
-        <v>46107</v>
+        <v>46128</v>
       </c>
       <c r="F1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-3),-1)</f>
-        <v>46048</v>
+        <v>46069</v>
       </c>
       <c r="G1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-12),-1)</f>
-        <v>45772</v>
+        <v>45793</v>
       </c>
       <c r="H1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-18),-1)</f>
-        <v>45590</v>
+        <v>45611</v>
       </c>
       <c r="I1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-24),-1)</f>
-        <v>45408</v>
+        <v>45428</v>
       </c>
       <c r="J1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-36),-1)</f>
-        <v>45042</v>
+        <v>45062</v>
       </c>
       <c r="K1" s="8">
         <f ca="1">WORKDAY(EDATE(TODAY(),-48),-1)</f>
-        <v>44677</v>
+        <v>44697</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6160,43 +8967,43 @@
       </c>
       <c r="B2" s="1" cm="1">
         <f t="array" aca="1" ref="B2" ca="1">_FV(A2,"Price")</f>
-        <v>1.3682000000000001</v>
+        <v>1.375</v>
       </c>
       <c r="C2" s="2" cm="1">
         <f t="array" aca="1" ref="C2" ca="1">_FV(A2,"Change (%)",TRUE)</f>
-        <v>-9.4930000000000004E-4</v>
-      </c>
-      <c r="D2" s="2" t="e" cm="1" vm="2">
+        <v>7.2730000000000003E-5</v>
+      </c>
+      <c r="D2" s="2" cm="1">
         <f t="array" aca="1" ref="D2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, D$1,D$1,0,0,1))/$B2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E2" s="2" t="e" cm="1" vm="2">
+        <v>5.3090909090909707E-3</v>
+      </c>
+      <c r="E2" s="2" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, E$1,E$1,0,0,1))/$B2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F2" s="2" t="e" cm="1" vm="2">
+        <v>3.4181818181817647E-3</v>
+      </c>
+      <c r="F2" s="2" cm="1">
         <f t="array" aca="1" ref="F2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, F$1,F$1,0,0,1))/$B2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G2" s="2" t="e" cm="1" vm="2">
+        <v>8.4363636363636758E-3</v>
+      </c>
+      <c r="G2" s="2" cm="1">
         <f t="array" aca="1" ref="G2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, G$1,G$1,0,0,1))/$B2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H2" s="2" t="e" cm="1" vm="2">
+        <v>-1.5636363636363691E-2</v>
+      </c>
+      <c r="H2" s="2" cm="1">
         <f t="array" aca="1" ref="H2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, H$1,H$1,0,0,1))/$B2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I2" s="2" t="e" cm="1" vm="2">
+        <v>-2.4581818181818219E-2</v>
+      </c>
+      <c r="I2" s="2" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, I$1,I$1,0,0,1))/$B2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J2" s="2" t="e" cm="1" vm="2">
+        <v>9.6000000000000738E-3</v>
+      </c>
+      <c r="J2" s="2" cm="1">
         <f t="array" aca="1" ref="J2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, J$1,J$1,0,0,1))/$B2</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K2" s="2" t="e" cm="1" vm="2">
+        <v>1.9490909090909045E-2</v>
+      </c>
+      <c r="K2" s="2" cm="1">
         <f t="array" aca="1" ref="K2" ca="1">($B2 - _xlfn.STOCKHISTORY($A2, K$1,K$1,0,0,1))/$B2</f>
-        <v>#VALUE!</v>
+        <v>6.5963636363636363E-2</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -6205,43 +9012,43 @@
       </c>
       <c r="B3" s="1" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">_FV(A3,"Price")</f>
-        <v>67096.73</v>
+        <v>76975.89</v>
       </c>
       <c r="C3" s="2" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">_FV(A3,"Change (%)",TRUE)</f>
-        <v>1.1647000000000001E-2</v>
-      </c>
-      <c r="D3" s="2" t="e" cm="1" vm="2">
+        <v>-1.6389000000000001E-2</v>
+      </c>
+      <c r="D3" s="2" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, D$1,D$1,0,0,1))/$B3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E3" s="2" t="e" cm="1" vm="2">
+        <v>-6.2711584107699156E-2</v>
+      </c>
+      <c r="E3" s="2" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, E$1,E$1,0,0,1))/$B3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F3" s="2" t="e" cm="1" vm="2">
+        <v>2.2597595169084776E-2</v>
+      </c>
+      <c r="F3" s="2" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, F$1,F$1,0,0,1))/$B3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G3" s="2" t="e" cm="1" vm="2">
+        <v>0.10562099379429071</v>
+      </c>
+      <c r="G3" s="2" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, G$1,G$1,0,0,1))/$B3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H3" s="2" t="e" cm="1" vm="2">
+        <v>-0.34770315744319413</v>
+      </c>
+      <c r="H3" s="2" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, H$1,H$1,0,0,1))/$B3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I3" s="2" t="e" cm="1" vm="2">
+        <v>-0.19193165548329486</v>
+      </c>
+      <c r="I3" s="2" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, I$1,I$1,0,0,1))/$B3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J3" s="2" t="e" cm="1" vm="2">
+        <v>0.1519162688472975</v>
+      </c>
+      <c r="J3" s="2" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, J$1,J$1,0,0,1))/$B3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K3" s="2" t="e" cm="1" vm="2">
+        <v>0.64979943720040134</v>
+      </c>
+      <c r="K3" s="2" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">($B3 - _xlfn.STOCKHISTORY($A3, K$1,K$1,0,0,1))/$B3</f>
-        <v>#VALUE!</v>
+        <v>0.61153745672833404</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -6250,43 +9057,43 @@
       </c>
       <c r="B4" s="1" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">_FV(A4,"Price")</f>
-        <v>1978.53</v>
+        <v>2122.89</v>
       </c>
       <c r="C4" s="2" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">_FV(A4,"Change (%)",TRUE)</f>
-        <v>1.8963000000000001E-2</v>
-      </c>
-      <c r="D4" s="2" t="e" cm="1" vm="2">
+        <v>-2.9996999999999999E-2</v>
+      </c>
+      <c r="D4" s="2" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, D$1,D$1,0,0,1))/$B4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E4" s="2" t="e" cm="1" vm="2">
+        <v>-0.10114513705373349</v>
+      </c>
+      <c r="E4" s="2" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, E$1,E$1,0,0,1))/$B4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F4" s="2" t="e" cm="1" vm="2">
+        <v>-0.10732539132974396</v>
+      </c>
+      <c r="F4" s="2" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, F$1,F$1,0,0,1))/$B4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G4" s="2" t="e" cm="1" vm="2">
+        <v>5.8415650363419572E-2</v>
+      </c>
+      <c r="G4" s="2" cm="1">
         <f t="array" aca="1" ref="G4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, G$1,G$1,0,0,1))/$B4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H4" s="2" t="e" cm="1" vm="2">
+        <v>-0.21155594496182098</v>
+      </c>
+      <c r="H4" s="2" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, H$1,H$1,0,0,1))/$B4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I4" s="2" t="e" cm="1" vm="2">
+        <v>-0.45626951938159782</v>
+      </c>
+      <c r="I4" s="2" cm="1">
         <f t="array" aca="1" ref="I4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, I$1,I$1,0,0,1))/$B4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J4" s="2" t="e" cm="1" vm="2">
+        <v>-0.3840142447324168</v>
+      </c>
+      <c r="J4" s="2" cm="1">
         <f t="array" aca="1" ref="J4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, J$1,J$1,0,0,1))/$B4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K4" s="2" t="e" cm="1" vm="2">
+        <v>0.14211287443061102</v>
+      </c>
+      <c r="K4" s="2" cm="1">
         <f t="array" aca="1" ref="K4" ca="1">($B4 - _xlfn.STOCKHISTORY($A4, K$1,K$1,0,0,1))/$B4</f>
-        <v>#VALUE!</v>
+        <v>4.2625854377758524E-2</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -6295,43 +9102,43 @@
       </c>
       <c r="B5" s="1" cm="1">
         <f t="array" aca="1" ref="B5" ca="1">_FV(A5,"Price")</f>
-        <v>0.84730000000000005</v>
+        <v>0.86029999999999995</v>
       </c>
       <c r="C5" s="2" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(A5,"Change (%)",TRUE)</f>
-        <v>-1.4139999999999999E-3</v>
-      </c>
-      <c r="D5" s="2" t="e" cm="1" vm="2">
+        <v>2.3249999999999999E-4</v>
+      </c>
+      <c r="D5" s="2" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, D$1,D$1,0,0,1))/$B5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E5" s="2" t="e" cm="1" vm="2">
+        <v>1.3599907009182765E-2</v>
+      </c>
+      <c r="E5" s="2" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, E$1,E$1,0,0,1))/$B5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F5" s="2" t="e" cm="1" vm="2">
+        <v>1.3367429966290777E-2</v>
+      </c>
+      <c r="F5" s="2" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, F$1,F$1,0,0,1))/$B5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G5" s="2" t="e" cm="1" vm="2">
+        <v>1.9295594560037137E-2</v>
+      </c>
+      <c r="G5" s="2" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, G$1,G$1,0,0,1))/$B5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H5" s="2" t="e" cm="1" vm="2">
+        <v>-4.1148436591886668E-2</v>
+      </c>
+      <c r="H5" s="2" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, H$1,H$1,0,0,1))/$B5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I5" s="2" t="e" cm="1" vm="2">
+        <v>-0.10263861443682443</v>
+      </c>
+      <c r="I5" s="2" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, I$1,I$1,0,0,1))/$B5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J5" s="2" t="e" cm="1" vm="2">
+        <v>-6.9394397303266409E-2</v>
+      </c>
+      <c r="J5" s="2" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, J$1,J$1,0,0,1))/$B5</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K5" s="2" t="e" cm="1" vm="2">
+        <v>-6.9859351389050389E-2</v>
+      </c>
+      <c r="K5" s="2" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">($B5 - _xlfn.STOCKHISTORY($A5, K$1,K$1,0,0,1))/$B5</f>
-        <v>#VALUE!</v>
+        <v>-0.11391375101708717</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -6340,43 +9147,43 @@
       </c>
       <c r="B6" s="1" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">_FV(A6,"Price")</f>
-        <v>154.93</v>
+        <v>158.94999999999999</v>
       </c>
       <c r="C6" s="2" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(A6,"Change (%)",TRUE)</f>
-        <v>7.1049999999999998E-4</v>
-      </c>
-      <c r="D6" s="2" t="e" cm="1" vm="2">
+        <v>1.1969999999999999E-3</v>
+      </c>
+      <c r="D6" s="2" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, D$1,D$1,0,0,1))/$B6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E6" s="2" t="e" cm="1" vm="2">
+        <v>1.1261402956904637E-2</v>
+      </c>
+      <c r="E6" s="2" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, E$1,E$1,0,0,1))/$B6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F6" s="2" t="e" cm="1" vm="2">
+        <v>-1.4469959106638453E-3</v>
+      </c>
+      <c r="F6" s="2" cm="1">
         <f t="array" aca="1" ref="F6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, F$1,F$1,0,0,1))/$B6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G6" s="2" t="e" cm="1" vm="2">
+        <v>3.422459893048127E-2</v>
+      </c>
+      <c r="G6" s="2" cm="1">
         <f t="array" aca="1" ref="G6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, G$1,G$1,0,0,1))/$B6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H6" s="2" t="e" cm="1" vm="2">
+        <v>8.386284995281526E-2</v>
+      </c>
+      <c r="H6" s="2" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, H$1,H$1,0,0,1))/$B6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I6" s="2" t="e" cm="1" vm="2">
+        <v>2.9002831078955557E-2</v>
+      </c>
+      <c r="I6" s="2" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, I$1,I$1,0,0,1))/$B6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J6" s="2" t="e" cm="1" vm="2">
+        <v>2.2459893048128302E-2</v>
+      </c>
+      <c r="J6" s="2" cm="1">
         <f t="array" aca="1" ref="J6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, J$1,J$1,0,0,1))/$B6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K6" s="2" t="e" cm="1" vm="2">
+        <v>0.14205725070776964</v>
+      </c>
+      <c r="K6" s="2" cm="1">
         <f t="array" aca="1" ref="K6" ca="1">($B6 - _xlfn.STOCKHISTORY($A6, K$1,K$1,0,0,1))/$B6</f>
-        <v>#VALUE!</v>
+        <v>0.18741742686379362</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -6385,43 +9192,43 @@
       </c>
       <c r="B7" s="1" cm="1">
         <f t="array" aca="1" ref="B7" ca="1">_FV(A7,"Price")</f>
-        <v>6.9080000000000004</v>
+        <v>6.8136000000000001</v>
       </c>
       <c r="C7" s="2" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(A7,"Change (%)",TRUE)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="e" cm="1" vm="2">
+        <v>6.4619999999999999E-4</v>
+      </c>
+      <c r="D7" s="2" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, D$1,D$1,0,0,1))/$B7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E7" s="2" t="e" cm="1" vm="2">
+        <v>2.7591875073382215E-3</v>
+      </c>
+      <c r="E7" s="2" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, E$1,E$1,0,0,1))/$B7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F7" s="2" t="e" cm="1" vm="2">
+        <v>-1.0567101091933919E-3</v>
+      </c>
+      <c r="F7" s="2" cm="1">
         <f t="array" aca="1" ref="F7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, F$1,F$1,0,0,1))/$B7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G7" s="2" t="e" cm="1" vm="2">
+        <v>-1.3854643653868771E-2</v>
+      </c>
+      <c r="G7" s="2" cm="1">
         <f t="array" aca="1" ref="G7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, G$1,G$1,0,0,1))/$B7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H7" s="2" t="e" cm="1" vm="2">
+        <v>-5.8030996829869605E-2</v>
+      </c>
+      <c r="H7" s="2" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, H$1,H$1,0,0,1))/$B7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I7" s="2" t="e" cm="1" vm="2">
+        <v>-6.1245156745332867E-2</v>
+      </c>
+      <c r="I7" s="2" cm="1">
         <f t="array" aca="1" ref="I7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, I$1,I$1,0,0,1))/$B7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J7" s="2" t="e" cm="1" vm="2">
+        <v>-5.9366560995655696E-2</v>
+      </c>
+      <c r="J7" s="2" cm="1">
         <f t="array" aca="1" ref="J7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, J$1,J$1,0,0,1))/$B7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K7" s="2" t="e" cm="1" vm="2">
+        <v>-2.4216273335681583E-2</v>
+      </c>
+      <c r="K7" s="2" cm="1">
         <f t="array" aca="1" ref="K7" ca="1">($B7 - _xlfn.STOCKHISTORY($A7, K$1,K$1,0,0,1))/$B7</f>
-        <v>#VALUE!</v>
+        <v>4.6084301984267552E-3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -6430,43 +9237,43 @@
       </c>
       <c r="B8" s="1" cm="1">
         <f t="array" aca="1" ref="B8" ca="1">_FV(A8,"Price")</f>
-        <v>43.7669</v>
+        <v>45.573099999999997</v>
       </c>
       <c r="C8" s="2" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(A8,"Change (%)",TRUE)</f>
-        <v>6.4250000000000006E-4</v>
-      </c>
-      <c r="D8" s="2" t="e" cm="1" vm="2">
+        <v>1.825E-3</v>
+      </c>
+      <c r="D8" s="2" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, D$1,D$1,0,0,1))/$B8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E8" s="2" t="e" cm="1" vm="2">
+        <v>5.1697163458267721E-3</v>
+      </c>
+      <c r="E8" s="2" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, E$1,E$1,0,0,1))/$B8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F8" s="2" t="e" cm="1" vm="2">
+        <v>1.6876183538095821E-2</v>
+      </c>
+      <c r="F8" s="2" cm="1">
         <f t="array" aca="1" ref="F8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, F$1,F$1,0,0,1))/$B8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G8" s="2" t="e" cm="1" vm="2">
+        <v>4.1011035018464835E-2</v>
+      </c>
+      <c r="G8" s="2" cm="1">
         <f t="array" aca="1" ref="G8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, G$1,G$1,0,0,1))/$B8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H8" s="2" t="e" cm="1" vm="2">
+        <v>0.14746418391551153</v>
+      </c>
+      <c r="H8" s="2" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, H$1,H$1,0,0,1))/$B8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I8" s="2" t="e" cm="1" vm="2">
+        <v>0.24476280963989713</v>
+      </c>
+      <c r="I8" s="2" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, I$1,I$1,0,0,1))/$B8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J8" s="2" t="e" cm="1" vm="2">
+        <v>0.29187174012739969</v>
+      </c>
+      <c r="J8" s="2" cm="1">
         <f t="array" aca="1" ref="J8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, J$1,J$1,0,0,1))/$B8</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K8" s="2" t="e" cm="1" vm="2">
+        <v>0.56722496384928822</v>
+      </c>
+      <c r="K8" s="2" cm="1">
         <f t="array" aca="1" ref="K8" ca="1">($B8 - _xlfn.STOCKHISTORY($A8, K$1,K$1,0,0,1))/$B8</f>
-        <v>#VALUE!</v>
+        <v>0.65902473169479359</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -6475,43 +9282,43 @@
       </c>
       <c r="B9" s="1" cm="1">
         <f t="array" aca="1" ref="B9" ca="1">_FV(A9,"Price")</f>
-        <v>91.045000000000002</v>
+        <v>96.21</v>
       </c>
       <c r="C9" s="2" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(A9,"Change (%)",TRUE)</f>
-        <v>2.9740000000000001E-3</v>
-      </c>
-      <c r="D9" s="2" t="e" cm="1" vm="2">
+        <v>2.6050000000000001E-3</v>
+      </c>
+      <c r="D9" s="2" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, D$1,D$1,0,0,1))/$B9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E9" s="2" t="e" cm="1" vm="2">
+        <v>9.3545369504208654E-3</v>
+      </c>
+      <c r="E9" s="2" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, E$1,E$1,0,0,1))/$B9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F9" s="2" t="e" cm="1" vm="2">
+        <v>3.3104666874545143E-2</v>
+      </c>
+      <c r="F9" s="2" cm="1">
         <f t="array" aca="1" ref="F9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, F$1,F$1,0,0,1))/$B9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G9" s="2" t="e" cm="1" vm="2">
+        <v>5.6657312129716184E-2</v>
+      </c>
+      <c r="G9" s="2" cm="1">
         <f t="array" aca="1" ref="G9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, G$1,G$1,0,0,1))/$B9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H9" s="2" t="e" cm="1" vm="2">
+        <v>0.11142292900945847</v>
+      </c>
+      <c r="H9" s="2" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, H$1,H$1,0,0,1))/$B9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I9" s="2" t="e" cm="1" vm="2">
+        <v>0.12250285833073472</v>
+      </c>
+      <c r="I9" s="2" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, I$1,I$1,0,0,1))/$B9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J9" s="2" t="e" cm="1" vm="2">
+        <v>0.13262654609707922</v>
+      </c>
+      <c r="J9" s="2" cm="1">
         <f t="array" aca="1" ref="J9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, J$1,J$1,0,0,1))/$B9</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K9" s="2" t="e" cm="1" vm="2">
+        <v>0.14495374701174513</v>
+      </c>
+      <c r="K9" s="2" cm="1">
         <f t="array" aca="1" ref="K9" ca="1">($B9 - _xlfn.STOCKHISTORY($A9, K$1,K$1,0,0,1))/$B9</f>
-        <v>#VALUE!</v>
+        <v>0.19124311402141139</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -6520,43 +9327,43 @@
       </c>
       <c r="B10" s="1" cm="1">
         <f t="array" aca="1" ref="B10" ca="1">_FV(A10,"Price")</f>
-        <v>1.2667999999999999</v>
+        <v>1.2805</v>
       </c>
       <c r="C10" s="2" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(A10,"Change (%)",TRUE)</f>
-        <v>7.8949999999999995E-5</v>
-      </c>
-      <c r="D10" s="2" t="e" cm="1" vm="2">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="D10" s="2" cm="1">
         <f t="array" aca="1" ref="D10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, D$1,D$1,0,0,1))/$B10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E10" s="2" t="e" cm="1" vm="2">
+        <v>9.6056228035923293E-3</v>
+      </c>
+      <c r="E10" s="2" cm="1">
         <f t="array" aca="1" ref="E10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, E$1,E$1,0,0,1))/$B10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F10" s="2" t="e" cm="1" vm="2">
+        <v>6.4037485357282195E-3</v>
+      </c>
+      <c r="F10" s="2" cm="1">
         <f t="array" aca="1" ref="F10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, F$1,F$1,0,0,1))/$B10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G10" s="2" t="e" cm="1" vm="2">
+        <v>1.4447481452557564E-2</v>
+      </c>
+      <c r="G10" s="2" cm="1">
         <f t="array" aca="1" ref="G10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, G$1,G$1,0,0,1))/$B10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H10" s="2" t="e" cm="1" vm="2">
+        <v>-1.47598594299103E-2</v>
+      </c>
+      <c r="H10" s="2" cm="1">
         <f t="array" aca="1" ref="H10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, H$1,H$1,0,0,1))/$B10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I10" s="2" t="e" cm="1" vm="2">
+        <v>-4.8496680983990667E-2</v>
+      </c>
+      <c r="I10" s="2" cm="1">
         <f t="array" aca="1" ref="I10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, I$1,I$1,0,0,1))/$B10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J10" s="2" t="e" cm="1" vm="2">
+        <v>-5.0995704802811508E-2</v>
+      </c>
+      <c r="J10" s="2" cm="1">
         <f t="array" aca="1" ref="J10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, J$1,J$1,0,0,1))/$B10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K10" s="2" t="e" cm="1" vm="2">
+        <v>-4.6622413119875118E-2</v>
+      </c>
+      <c r="K10" s="2" cm="1">
         <f t="array" aca="1" ref="K10" ca="1">($B10 - _xlfn.STOCKHISTORY($A10, K$1,K$1,0,0,1))/$B10</f>
-        <v>#VALUE!</v>
+        <v>-8.6528699726669281E-2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -6565,43 +9372,43 @@
       </c>
       <c r="B11" s="1" cm="1">
         <f t="array" aca="1" ref="B11" ca="1">_FV(A11,"Price")</f>
-        <v>31.536999999999999</v>
+        <v>31.622</v>
       </c>
       <c r="C11" s="2" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(A11,"Change (%)",TRUE)</f>
-        <v>2.5369999999999999E-4</v>
-      </c>
-      <c r="D11" s="2" t="e" cm="1" vm="2">
+        <v>1.933E-3</v>
+      </c>
+      <c r="D11" s="2" cm="1">
         <f t="array" aca="1" ref="D11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, D$1,D$1,0,0,1))/$B11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E11" s="2" t="e" cm="1" vm="2">
+        <v>8.601606476503652E-3</v>
+      </c>
+      <c r="E11" s="2" cm="1">
         <f t="array" aca="1" ref="E11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, E$1,E$1,0,0,1))/$B11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F11" s="2" t="e" cm="1" vm="2">
+        <v>1.992283853013688E-3</v>
+      </c>
+      <c r="F11" s="2" cm="1">
         <f t="array" aca="1" ref="F11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, F$1,F$1,0,0,1))/$B11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G11" s="2" t="e" cm="1" vm="2">
+        <v>8.5067358168363274E-3</v>
+      </c>
+      <c r="G11" s="2" cm="1">
         <f t="array" aca="1" ref="G11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, G$1,G$1,0,0,1))/$B11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H11" s="2" t="e" cm="1" vm="2">
+        <v>4.4873822022642479E-2</v>
+      </c>
+      <c r="H11" s="2" cm="1">
         <f t="array" aca="1" ref="H11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, H$1,H$1,0,0,1))/$B11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I11" s="2" t="e" cm="1" vm="2">
+        <v>-2.7322749984188134E-2</v>
+      </c>
+      <c r="I11" s="2" cm="1">
         <f t="array" aca="1" ref="I11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, I$1,I$1,0,0,1))/$B11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J11" s="2" t="e" cm="1" vm="2">
+        <v>-1.698184808045029E-2</v>
+      </c>
+      <c r="J11" s="2" cm="1">
         <f t="array" aca="1" ref="J11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, J$1,J$1,0,0,1))/$B11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K11" s="2" t="e" cm="1" vm="2">
+        <v>2.4856112832837941E-2</v>
+      </c>
+      <c r="K11" s="2" cm="1">
         <f t="array" aca="1" ref="K11" ca="1">($B11 - _xlfn.STOCKHISTORY($A11, K$1,K$1,0,0,1))/$B11</f>
-        <v>#VALUE!</v>
+        <v>5.8883056100183365E-2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -6623,146 +9430,146 @@
       </c>
       <c r="B14" s="1" cm="1">
         <f t="array" aca="1" ref="B14" ca="1">_FV(A14,"Price")</f>
-        <v>5028.8</v>
+        <v>4544.5</v>
       </c>
       <c r="C14" s="2" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(A14,"Change (%)",TRUE)</f>
-        <v>3.8529999999999997E-3</v>
-      </c>
-      <c r="D14" s="2" t="e" cm="1" vm="2">
+        <v>-3.8140000000000001E-3</v>
+      </c>
+      <c r="D14" s="2" cm="1">
         <f t="array" aca="1" ref="D14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, D$1,D$1,0,0,1))/$B14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E14" s="2" t="e" cm="1" vm="2">
+        <v>-4.0532511827483735E-2</v>
+      </c>
+      <c r="E14" s="2" cm="1">
         <f t="array" aca="1" ref="E14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, E$1,E$1,0,0,1))/$B14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F14" s="2" t="e" cm="1" vm="2">
+        <v>-5.8048190119925222E-2</v>
+      </c>
+      <c r="F14" s="2" t="e" cm="1" vm="35">
         <f t="array" aca="1" ref="F14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, F$1,F$1,0,0,1))/$B14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G14" s="2" t="e" cm="1" vm="2">
+        <v>#N/A</v>
+      </c>
+      <c r="G14" s="2" cm="1">
         <f t="array" aca="1" ref="G14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, G$1,G$1,0,0,1))/$B14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H14" s="2" t="e" cm="1" vm="2">
+        <v>0.29866872043129061</v>
+      </c>
+      <c r="H14" s="2" cm="1">
         <f t="array" aca="1" ref="H14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, H$1,H$1,0,0,1))/$B14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I14" s="2" t="e" cm="1" vm="2">
+        <v>0.43445923643965234</v>
+      </c>
+      <c r="I14" s="2" cm="1">
         <f t="array" aca="1" ref="I14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, I$1,I$1,0,0,1))/$B14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J14" s="2" t="e" cm="1" vm="2">
+        <v>0.47507976675101771</v>
+      </c>
+      <c r="J14" s="2" cm="1">
         <f t="array" aca="1" ref="J14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, J$1,J$1,0,0,1))/$B14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K14" s="2" t="e" cm="1" vm="2">
+        <v>0.56144790405985256</v>
+      </c>
+      <c r="K14" s="2" cm="1">
         <f t="array" aca="1" ref="K14" ca="1">($B14 - _xlfn.STOCKHISTORY($A14, K$1,K$1,0,0,1))/$B14</f>
-        <v>#VALUE!</v>
+        <v>0.6008361755968753</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" t="e" vm="35">
+      <c r="A15" t="e" vm="36">
         <v>#VALUE!</v>
       </c>
       <c r="B15" s="1" cm="1">
         <f t="array" aca="1" ref="B15" ca="1">_FV(A15,"Price")</f>
-        <v>78.790000000000006</v>
+        <v>75.83</v>
       </c>
       <c r="C15" s="2" cm="1">
         <f t="array" aca="1" ref="C15" ca="1">_FV(A15,"Change (%)",TRUE)</f>
-        <v>1.5361E-2</v>
-      </c>
-      <c r="D15" s="2" t="e" cm="1" vm="2">
+        <v>-2.2141000000000001E-2</v>
+      </c>
+      <c r="D15" s="2" cm="1">
         <f t="array" aca="1" ref="D15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, D$1,D$1,0,0,1))/$B15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E15" s="2" t="e" cm="1" vm="2">
+        <v>-0.13343004088091778</v>
+      </c>
+      <c r="E15" s="2" cm="1">
         <f t="array" aca="1" ref="E15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, E$1,E$1,0,0,1))/$B15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F15" s="2" t="e" cm="1" vm="2">
+        <v>-3.7979691415007191E-2</v>
+      </c>
+      <c r="F15" s="2" t="e" cm="1" vm="35">
         <f t="array" aca="1" ref="F15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, F$1,F$1,0,0,1))/$B15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G15" s="2" t="e" cm="1" vm="2">
+        <v>#N/A</v>
+      </c>
+      <c r="G15" s="2" cm="1">
         <f t="array" aca="1" ref="G15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, G$1,G$1,0,0,1))/$B15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H15" s="2" t="e" cm="1" vm="2">
+        <v>0.57333509165238028</v>
+      </c>
+      <c r="H15" s="2" cm="1">
         <f t="array" aca="1" ref="H15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, H$1,H$1,0,0,1))/$B15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I15" s="2" t="e" cm="1" vm="2">
+        <v>0.59868126071475669</v>
+      </c>
+      <c r="I15" s="2" cm="1">
         <f t="array" aca="1" ref="I15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, I$1,I$1,0,0,1))/$B15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J15" s="2" t="e" cm="1" vm="2">
+        <v>0.60879599103257287</v>
+      </c>
+      <c r="J15" s="2" cm="1">
         <f t="array" aca="1" ref="J15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, J$1,J$1,0,0,1))/$B15</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K15" s="2" t="e" cm="1" vm="2">
+        <v>0.68491362257681654</v>
+      </c>
+      <c r="K15" s="2" cm="1">
         <f t="array" aca="1" ref="K15" ca="1">($B15 - _xlfn.STOCKHISTORY($A15, K$1,K$1,0,0,1))/$B15</f>
-        <v>#VALUE!</v>
+        <v>0.71579849663721484</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" t="e" vm="36">
+      <c r="A16" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
       <c r="B16" s="1" cm="1">
         <f t="array" aca="1" ref="B16" ca="1">_FV(A16,"Price")</f>
-        <v>2106.5</v>
+        <v>1974.1</v>
       </c>
       <c r="C16" s="2" cm="1">
         <f t="array" aca="1" ref="C16" ca="1">_FV(A16,"Change (%)",TRUE)</f>
-        <v>-3.029E-3</v>
-      </c>
-      <c r="D16" s="2" t="e" cm="1" vm="2">
+        <v>-8.8859999999999998E-3</v>
+      </c>
+      <c r="D16" s="2" cm="1">
         <f t="array" aca="1" ref="D16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, D$1,D$1,0,0,1))/$B16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E16" s="2" t="e" cm="1" vm="2">
+        <v>-7.7098424598551374E-2</v>
+      </c>
+      <c r="E16" s="2" cm="1">
         <f t="array" aca="1" ref="E16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, E$1,E$1,0,0,1))/$B16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F16" s="2" t="e" cm="1" vm="2">
+        <v>-6.995592928423075E-2</v>
+      </c>
+      <c r="F16" s="2" t="e" cm="1" vm="35">
         <f t="array" aca="1" ref="F16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, F$1,F$1,0,0,1))/$B16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G16" s="2" t="e" cm="1" vm="2">
+        <v>#N/A</v>
+      </c>
+      <c r="G16" s="2" cm="1">
         <f t="array" aca="1" ref="G16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, G$1,G$1,0,0,1))/$B16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H16" s="2" t="e" cm="1" vm="2">
+        <v>0.49840433615318369</v>
+      </c>
+      <c r="H16" s="2" cm="1">
         <f t="array" aca="1" ref="H16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, H$1,H$1,0,0,1))/$B16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I16" s="2" t="e" cm="1" vm="2">
+        <v>0.52125018995998174</v>
+      </c>
+      <c r="I16" s="2" cm="1">
         <f t="array" aca="1" ref="I16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, I$1,I$1,0,0,1))/$B16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J16" s="2" t="e" cm="1" vm="2">
+        <v>0.45732232409705686</v>
+      </c>
+      <c r="J16" s="2" cm="1">
         <f t="array" aca="1" ref="J16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, J$1,J$1,0,0,1))/$B16</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K16" s="2" t="e" cm="1" vm="2">
+        <v>0.45955118788308591</v>
+      </c>
+      <c r="K16" s="2" cm="1">
         <f t="array" aca="1" ref="K16" ca="1">($B16 - _xlfn.STOCKHISTORY($A16, K$1,K$1,0,0,1))/$B16</f>
-        <v>#VALUE!</v>
+        <v>0.53128007699711266</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" t="e" vm="37">
+      <c r="A17" t="e" vm="38">
         <v>#VALUE!</v>
       </c>
       <c r="B17" s="1" cm="1">
         <f t="array" aca="1" ref="B17" ca="1">_FV(A17,"Price")</f>
-        <v>3.0129999999999999</v>
+        <v>3.0310000000000001</v>
       </c>
       <c r="C17" s="2" cm="1">
         <f t="array" aca="1" ref="C17" ca="1">_FV(A17,"Change (%)",TRUE)</f>
-        <v>6.642000000000001E-4</v>
+        <v>2.3986E-2</v>
       </c>
       <c r="D17" s="2" t="e" cm="1" vm="2">
         <f t="array" aca="1" ref="D17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, D$1,D$1,0,0,1))/$B17</f>
@@ -6772,29 +9579,29 @@
         <f t="array" aca="1" ref="E17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, E$1,E$1,0,0,1))/$B17</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F17" s="2" t="e" cm="1" vm="2">
+      <c r="F17" s="2" t="e" cm="1" vm="35">
         <f t="array" aca="1" ref="F17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, F$1,F$1,0,0,1))/$B17</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G17" s="2" t="e" cm="1" vm="2">
+        <v>#N/A</v>
+      </c>
+      <c r="G17" s="2" cm="1">
         <f t="array" aca="1" ref="G17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, G$1,G$1,0,0,1))/$B17</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H17" s="2" t="e" cm="1" vm="2">
+        <v>-9.9967007588254678E-2</v>
+      </c>
+      <c r="H17" s="2" cm="1">
         <f t="array" aca="1" ref="H17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, H$1,H$1,0,0,1))/$B17</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I17" s="2" t="e" cm="1" vm="2">
+        <v>6.8624216430221111E-2</v>
+      </c>
+      <c r="I17" s="2" cm="1">
         <f t="array" aca="1" ref="I17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, I$1,I$1,0,0,1))/$B17</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J17" s="2" t="e" cm="1" vm="2">
+        <v>0.1768393269548004</v>
+      </c>
+      <c r="J17" s="2" cm="1">
         <f t="array" aca="1" ref="J17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, J$1,J$1,0,0,1))/$B17</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K17" s="2" t="e" cm="1" vm="2">
+        <v>0.21610029693170579</v>
+      </c>
+      <c r="K17" s="2" cm="1">
         <f t="array" aca="1" ref="K17" ca="1">($B17 - _xlfn.STOCKHISTORY($A17, K$1,K$1,0,0,1))/$B17</f>
-        <v>#VALUE!</v>
+        <v>-1.6248762784559554</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
